--- a/examples/examples_test01.xlsx
+++ b/examples/examples_test01.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoseAntonioAlatorreS\code\ms-excel-win\examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Upwork\msms_xloil\uv_test\ms-excel-win\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C1F828-246F-4939-B9EE-1F113B97B19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005B933E-F3DA-4D5D-8EBE-065729EEB547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9075" yWindow="2130" windowWidth="25410" windowHeight="15195" activeTab="1" xr2:uid="{3A9BCFE7-D97F-4DB8-8393-A5035DFE7468}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3A9BCFE7-D97F-4DB8-8393-A5035DFE7468}"/>
   </bookViews>
   <sheets>
     <sheet name="data_from_identifier" sheetId="1" r:id="rId1"/>
@@ -21,30 +21,19 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -534,32 +523,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{185BAD8C-0881-43D2-8B06-DFBB5DEC5206}">
   <dimension ref="B3:AL260"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="34" width="9" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="9" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B3" t="str">
         <f>_xll.MS.SHOW_ENDPOINT()</f>
         <v>Backend: https://dev-tsorm.ngrok.app</v>
       </c>
     </row>
-    <row r="4" spans="2:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:38" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B5" t="str" cm="1">
         <f t="array" ref="B5">_xll.MS.MODULE_PATH()</f>
-        <v>C:\Users\JoseAntonioAlatorreS\code\ms-excel-win\src\ms_excel_win\ms_excel_wrappers.py</v>
-      </c>
-    </row>
-    <row r="8" spans="2:38" x14ac:dyDescent="0.25">
+        <v>D:\Upwork\msms_xloil\uv_test\ms-excel-win\src\ms_excel_win\ms_excel_wrappers.py</v>
+      </c>
+    </row>
+    <row r="8" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>0</v>
       </c>
@@ -567,7 +562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>2</v>
       </c>
@@ -578,7 +573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
@@ -591,11 +586,11 @@
         <v>44927</v>
       </c>
     </row>
-    <row r="12" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H12" t="str" cm="1">
+      <c r="H12" t="str">
         <f t="array" ref="H12:AL260">_xll.MS.GET_DATA_NODE(C8,C11,D11,B11:B12)</f>
         <v>time_index</v>
       </c>
@@ -690,7 +685,7 @@
         <v>open_time</v>
       </c>
     </row>
-    <row r="13" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H13" t="str">
         <v>2022-01-03T21:01:19.804Z</v>
       </c>
@@ -785,7 +780,7 @@
         <v>1.6412202013731489E+18</v>
       </c>
     </row>
-    <row r="14" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H14" t="str">
         <v>2022-01-03T21:02:33.529Z</v>
       </c>
@@ -880,7 +875,7 @@
         <v>1.6412202009238902E+18</v>
       </c>
     </row>
-    <row r="15" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H15" t="str">
         <v>2022-01-04T21:02:10.756Z</v>
       </c>
@@ -975,7 +970,7 @@
         <v>1.6413066010601411E+18</v>
       </c>
     </row>
-    <row r="16" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H16" t="str">
         <v>2022-01-04T21:03:33.344Z</v>
       </c>
@@ -1070,7 +1065,7 @@
         <v>1.6413066009083397E+18</v>
       </c>
     </row>
-    <row r="17" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>12</v>
       </c>
@@ -1168,8 +1163,8 @@
         <v>1.6413930010358661E+18</v>
       </c>
     </row>
-    <row r="18" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B18" t="str" cm="1">
+    <row r="18" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B18" t="str">
         <f t="array" ref="B18:C32">_xll.MS.GET_ASSET(B12)</f>
         <v>field</v>
       </c>
@@ -1270,7 +1265,7 @@
         <v>1.6413930009392709E+18</v>
       </c>
     </row>
-    <row r="19" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B19" t="str">
         <v>orm_class</v>
       </c>
@@ -1371,7 +1366,7 @@
         <v>1.6414794013827489E+18</v>
       </c>
     </row>
-    <row r="20" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B20" t="str">
         <v>id</v>
       </c>
@@ -1472,7 +1467,7 @@
         <v>1.6414794009698668E+18</v>
       </c>
     </row>
-    <row r="21" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B21" t="str">
         <v>unique_identifier</v>
       </c>
@@ -1573,7 +1568,7 @@
         <v>1.6415658010079089E+18</v>
       </c>
     </row>
-    <row r="22" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B22" t="str">
         <v>figi</v>
       </c>
@@ -1674,7 +1669,7 @@
         <v>1.6415658008651907E+18</v>
       </c>
     </row>
-    <row r="23" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B23" t="str">
         <v>composite</v>
       </c>
@@ -1775,7 +1770,7 @@
         <v>1.6418250009640678E+18</v>
       </c>
     </row>
-    <row r="24" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B24" t="str">
         <v>share_class</v>
       </c>
@@ -1876,7 +1871,7 @@
         <v>1.6418250012051464E+18</v>
       </c>
     </row>
-    <row r="25" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B25" t="str">
         <v>isin</v>
       </c>
@@ -1977,7 +1972,7 @@
         <v>1.6419114009031713E+18</v>
       </c>
     </row>
-    <row r="26" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B26" t="str">
         <v>security_type</v>
       </c>
@@ -2078,7 +2073,7 @@
         <v>1.6419114011713531E+18</v>
       </c>
     </row>
-    <row r="27" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B27" t="str">
         <v>security_type_2</v>
       </c>
@@ -2179,7 +2174,7 @@
         <v>1.6419978008487265E+18</v>
       </c>
     </row>
-    <row r="28" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B28" t="str">
         <v>security_market_sector</v>
       </c>
@@ -2280,7 +2275,7 @@
         <v>1.6419978010399552E+18</v>
       </c>
     </row>
-    <row r="29" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B29" t="str">
         <v>is_tradable</v>
       </c>
@@ -2381,7 +2376,7 @@
         <v>1.642084201045204E+18</v>
       </c>
     </row>
-    <row r="30" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B30" t="str">
         <v>is_custom_by_organization</v>
       </c>
@@ -2482,7 +2477,7 @@
         <v>1.6420842009086886E+18</v>
       </c>
     </row>
-    <row r="31" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B31" t="str">
         <v>current_snapshot</v>
       </c>
@@ -2583,7 +2578,7 @@
         <v>1.6421706010327306E+18</v>
       </c>
     </row>
-    <row r="32" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B32" t="str">
         <v>current_pricing_detail</v>
       </c>
@@ -2684,7 +2679,7 @@
         <v>1.6421706009242076E+18</v>
       </c>
     </row>
-    <row r="33" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H33" t="str">
         <v>2022-01-18T21:04:05.276Z</v>
       </c>
@@ -2779,7 +2774,7 @@
         <v>1.6425162010415283E+18</v>
       </c>
     </row>
-    <row r="34" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H34" t="str">
         <v>2022-01-18T21:05:36.008Z</v>
       </c>
@@ -2874,7 +2869,14 @@
         <v>1.6425162012108012E+18</v>
       </c>
     </row>
-    <row r="35" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B35" t="str">
+        <f t="array" ref="B35:C75">_xll.MS.GET_ASSET(B12)</f>
+        <v>field</v>
+      </c>
+      <c r="C35" t="str">
+        <v>value</v>
+      </c>
       <c r="H35" t="str">
         <v>2022-01-19T21:04:29.248Z</v>
       </c>
@@ -2969,7 +2971,13 @@
         <v>1.6426026008334369E+18</v>
       </c>
     </row>
-    <row r="36" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B36" t="str">
+        <v>orm_class</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Asset</v>
+      </c>
       <c r="H36" t="str">
         <v>2022-01-19T21:04:50.339Z</v>
       </c>
@@ -3064,7 +3072,13 @@
         <v>1.6426026010275041E+18</v>
       </c>
     </row>
-    <row r="37" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B37" t="str">
+        <v>id</v>
+      </c>
+      <c r="C37">
+        <v>29091</v>
+      </c>
       <c r="H37" t="str">
         <v>2022-01-20T21:00:46.718Z</v>
       </c>
@@ -3159,7 +3173,13 @@
         <v>1.6426890010421972E+18</v>
       </c>
     </row>
-    <row r="38" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B38" t="str">
+        <v>unique_identifier</v>
+      </c>
+      <c r="C38" t="str">
+        <v>BBG000BY29C7</v>
+      </c>
       <c r="H38" t="str">
         <v>2022-01-20T21:02:48.346Z</v>
       </c>
@@ -3254,7 +3274,13 @@
         <v>1.6426890008660436E+18</v>
       </c>
     </row>
-    <row r="39" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B39" t="str">
+        <v>figi</v>
+      </c>
+      <c r="C39" t="str">
+        <v>BBG000BY29C7</v>
+      </c>
       <c r="H39" t="str">
         <v>2022-01-21T21:00:16.353Z</v>
       </c>
@@ -3349,7 +3375,13 @@
         <v>1.6427754011696371E+18</v>
       </c>
     </row>
-    <row r="40" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B40" t="str">
+        <v>composite</v>
+      </c>
+      <c r="C40" t="str">
+        <v>BBG000BY29C7</v>
+      </c>
       <c r="H40" t="str">
         <v>2022-01-21T21:04:16.823Z</v>
       </c>
@@ -3444,7 +3476,13 @@
         <v>1.6427754010820531E+18</v>
       </c>
     </row>
-    <row r="41" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B41" t="str">
+        <v>share_class</v>
+      </c>
+      <c r="C41" t="str">
+        <v>BBG001SFH7D5</v>
+      </c>
       <c r="H41" t="str">
         <v>2022-01-24T21:00:23.028Z</v>
       </c>
@@ -3539,7 +3577,13 @@
         <v>1.6430346011142853E+18</v>
       </c>
     </row>
-    <row r="42" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B42" t="str">
+        <v>isin</v>
+      </c>
+      <c r="C42" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H42" t="str">
         <v>2022-01-24T21:03:59.024Z</v>
       </c>
@@ -3634,7 +3678,13 @@
         <v>1.6430346009574976E+18</v>
       </c>
     </row>
-    <row r="43" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B43" t="str">
+        <v>security_type</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Common Stock</v>
+      </c>
       <c r="H43" t="str">
         <v>2022-01-25T21:02:56.007Z</v>
       </c>
@@ -3729,7 +3779,13 @@
         <v>1.6431210008202399E+18</v>
       </c>
     </row>
-    <row r="44" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B44" t="str">
+        <v>security_type_2</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Common Stock</v>
+      </c>
       <c r="H44" t="str">
         <v>2022-01-25T21:04:05.255Z</v>
       </c>
@@ -3824,7 +3880,13 @@
         <v>1.6431210010281495E+18</v>
       </c>
     </row>
-    <row r="45" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B45" t="str">
+        <v>security_market_sector</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Equity</v>
+      </c>
       <c r="H45" t="str">
         <v>2022-01-26T21:03:06.793Z</v>
       </c>
@@ -3919,7 +3981,13 @@
         <v>1.6432074008034757E+18</v>
       </c>
     </row>
-    <row r="46" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B46" t="str">
+        <v>is_tradable</v>
+      </c>
+      <c r="C46" t="b">
+        <v>1</v>
+      </c>
       <c r="H46" t="str">
         <v>2022-01-26T21:03:54.675Z</v>
       </c>
@@ -4014,7 +4082,13 @@
         <v>1.6432074009946002E+18</v>
       </c>
     </row>
-    <row r="47" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B47" t="str">
+        <v>is_custom_by_organization</v>
+      </c>
+      <c r="C47" t="b">
+        <v>0</v>
+      </c>
       <c r="H47" t="str">
         <v>2022-01-27T21:05:28.090Z</v>
       </c>
@@ -4109,7 +4183,13 @@
         <v>1.6432938008276524E+18</v>
       </c>
     </row>
-    <row r="48" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B48" t="str">
+        <v>current_snapshot</v>
+      </c>
+      <c r="C48" t="str">
+        <v>{"orm_class": "AssetSnapshot", "id": null, "asset": 29091, "effective_from": "2025-08-03 00:00:00+00:00", "effective_to": null, "name": "TAPESTRY INC", "ticker": "TPR", "exchange_code": "US", "asset_ticker_group_id": "BBG001SFH7D5", "venue_specific_properties": null}</v>
+      </c>
       <c r="H48" t="str">
         <v>2022-01-27T21:06:03.108Z</v>
       </c>
@@ -4204,7 +4284,13 @@
         <v>1.6432938009097528E+18</v>
       </c>
     </row>
-    <row r="49" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B49" t="str">
+        <v>current_pricing_detail</v>
+      </c>
+      <c r="C49" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H49" t="str">
         <v>2022-01-28T21:02:51.128Z</v>
       </c>
@@ -4299,7 +4385,13 @@
         <v>1.6433802011032108E+18</v>
       </c>
     </row>
-    <row r="50" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C50" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H50" t="str">
         <v>2022-01-28T21:04:50.725Z</v>
       </c>
@@ -4394,7 +4486,13 @@
         <v>1.6433802010637522E+18</v>
       </c>
     </row>
-    <row r="51" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C51" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H51" t="str">
         <v>2022-01-31T21:04:06.339Z</v>
       </c>
@@ -4489,7 +4587,13 @@
         <v>1.6436394008408463E+18</v>
       </c>
     </row>
-    <row r="52" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C52" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H52" t="str">
         <v>2022-01-31T21:05:11.666Z</v>
       </c>
@@ -4584,7 +4688,13 @@
         <v>1.6436394009415506E+18</v>
       </c>
     </row>
-    <row r="53" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C53" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H53" t="str">
         <v>2022-02-01T21:05:40.529Z</v>
       </c>
@@ -4679,7 +4789,13 @@
         <v>1.6437258008288044E+18</v>
       </c>
     </row>
-    <row r="54" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C54" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H54" t="str">
         <v>2022-02-01T21:06:01.766Z</v>
       </c>
@@ -4774,7 +4890,13 @@
         <v>1.6437258010771105E+18</v>
       </c>
     </row>
-    <row r="55" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C55" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H55" t="str">
         <v>2022-02-02T21:03:23.603Z</v>
       </c>
@@ -4869,7 +4991,13 @@
         <v>1.6438122854400256E+18</v>
       </c>
     </row>
-    <row r="56" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C56" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H56" t="str">
         <v>2022-02-02T21:05:36.475Z</v>
       </c>
@@ -4964,7 +5092,13 @@
         <v>1.6438122010664323E+18</v>
       </c>
     </row>
-    <row r="57" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C57" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H57" t="str">
         <v>2022-02-03T21:05:15.723Z</v>
       </c>
@@ -5059,7 +5193,13 @@
         <v>1.6438986008560888E+18</v>
       </c>
     </row>
-    <row r="58" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C58" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H58" t="str">
         <v>2022-02-03T21:06:45.349Z</v>
       </c>
@@ -5154,7 +5294,13 @@
         <v>1.6438986010249306E+18</v>
       </c>
     </row>
-    <row r="59" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C59" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H59" t="str">
         <v>2022-02-04T21:03:24.246Z</v>
       </c>
@@ -5249,7 +5395,13 @@
         <v>1.6439850008720901E+18</v>
       </c>
     </row>
-    <row r="60" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C60" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H60" t="str">
         <v>2022-02-04T21:04:44.283Z</v>
       </c>
@@ -5344,7 +5496,13 @@
         <v>1.6439850009518057E+18</v>
       </c>
     </row>
-    <row r="61" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C61" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H61" t="str">
         <v>2022-02-07T21:03:30.665Z</v>
       </c>
@@ -5439,7 +5597,13 @@
         <v>1.6442442009041236E+18</v>
       </c>
     </row>
-    <row r="62" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C62" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H62" t="str">
         <v>2022-02-07T21:05:06.449Z</v>
       </c>
@@ -5534,7 +5698,13 @@
         <v>1.6442442010614776E+18</v>
       </c>
     </row>
-    <row r="63" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C63" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H63" t="str">
         <v>2022-02-08T21:02:52.499Z</v>
       </c>
@@ -5629,7 +5799,13 @@
         <v>1.6443306009363965E+18</v>
       </c>
     </row>
-    <row r="64" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C64" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H64" t="str">
         <v>2022-02-08T21:05:15.079Z</v>
       </c>
@@ -5724,7 +5900,13 @@
         <v>1.6443306010275185E+18</v>
       </c>
     </row>
-    <row r="65" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C65" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H65" t="str">
         <v>2022-02-09T21:03:04.406Z</v>
       </c>
@@ -5819,7 +6001,13 @@
         <v>1.6444170008643302E+18</v>
       </c>
     </row>
-    <row r="66" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C66" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H66" t="str">
         <v>2022-02-09T21:04:26.998Z</v>
       </c>
@@ -5914,7 +6102,13 @@
         <v>1.6444170009603891E+18</v>
       </c>
     </row>
-    <row r="67" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C67" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H67" t="str">
         <v>2022-02-10T21:02:37.984Z</v>
       </c>
@@ -6009,7 +6203,13 @@
         <v>1.6445034746933107E+18</v>
       </c>
     </row>
-    <row r="68" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C68" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H68" t="str">
         <v>2022-02-10T21:05:01.129Z</v>
       </c>
@@ -6104,7 +6304,13 @@
         <v>1.6445034010573596E+18</v>
       </c>
     </row>
-    <row r="69" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C69" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H69" t="str">
         <v>2022-02-11T21:03:10.451Z</v>
       </c>
@@ -6199,7 +6405,13 @@
         <v>1.6445898008485888E+18</v>
       </c>
     </row>
-    <row r="70" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C70" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H70" t="str">
         <v>2022-02-11T21:04:33.630Z</v>
       </c>
@@ -6294,7 +6506,13 @@
         <v>1.6445898010466094E+18</v>
       </c>
     </row>
-    <row r="71" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C71" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H71" t="str">
         <v>2022-02-14T21:02:35Z</v>
       </c>
@@ -6389,7 +6607,13 @@
         <v>1.6448490011218614E+18</v>
       </c>
     </row>
-    <row r="72" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C72" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H72" t="str">
         <v>2022-02-14T21:05:03.184Z</v>
       </c>
@@ -6484,7 +6708,13 @@
         <v>1.6448490009201157E+18</v>
       </c>
     </row>
-    <row r="73" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C73" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H73" t="str">
         <v>2022-02-15T21:03:14.122Z</v>
       </c>
@@ -6579,7 +6809,13 @@
         <v>1.6449354008535831E+18</v>
       </c>
     </row>
-    <row r="74" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C74" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H74" t="str">
         <v>2022-02-15T21:04:31.506Z</v>
       </c>
@@ -6674,7 +6910,13 @@
         <v>1.644935401008608E+18</v>
       </c>
     </row>
-    <row r="75" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C75" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="H75" t="str">
         <v>2022-02-16T21:03:15.128Z</v>
       </c>
@@ -6769,7 +7011,7 @@
         <v>1.6450218008985892E+18</v>
       </c>
     </row>
-    <row r="76" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H76" t="str">
         <v>2022-02-16T21:04:37.400Z</v>
       </c>
@@ -6864,7 +7106,7 @@
         <v>1.6450218009721846E+18</v>
       </c>
     </row>
-    <row r="77" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H77" t="str">
         <v>2022-02-17T21:03:02.018Z</v>
       </c>
@@ -6959,7 +7201,7 @@
         <v>1.6451082012015529E+18</v>
       </c>
     </row>
-    <row r="78" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H78" t="str">
         <v>2022-02-17T21:04:11.903Z</v>
       </c>
@@ -7054,7 +7296,7 @@
         <v>1.6451082011926868E+18</v>
       </c>
     </row>
-    <row r="79" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H79" t="str">
         <v>2022-02-18T21:04:45.447Z</v>
       </c>
@@ -7149,7 +7391,7 @@
         <v>1.6451946050084726E+18</v>
       </c>
     </row>
-    <row r="80" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.3">
       <c r="H80" t="str">
         <v>2022-02-18T21:05:13.301Z</v>
       </c>
@@ -7244,7 +7486,7 @@
         <v>1.6451946011087772E+18</v>
       </c>
     </row>
-    <row r="81" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="81" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H81" t="str">
         <v>2022-02-22T21:03:40.094Z</v>
       </c>
@@ -7339,7 +7581,7 @@
         <v>1.6455402009881459E+18</v>
       </c>
     </row>
-    <row r="82" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H82" t="str">
         <v>2022-02-22T21:04:58.272Z</v>
       </c>
@@ -7434,7 +7676,7 @@
         <v>1.6455402011336169E+18</v>
       </c>
     </row>
-    <row r="83" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="83" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H83" t="str">
         <v>2022-02-23T21:04:22.432Z</v>
       </c>
@@ -7529,7 +7771,7 @@
         <v>1.6456266008105454E+18</v>
       </c>
     </row>
-    <row r="84" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="84" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H84" t="str">
         <v>2022-02-23T21:04:46.391Z</v>
       </c>
@@ -7624,7 +7866,7 @@
         <v>1.6456266009526789E+18</v>
       </c>
     </row>
-    <row r="85" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="85" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H85" t="str">
         <v>2022-02-24T21:03:37.581Z</v>
       </c>
@@ -7719,7 +7961,7 @@
         <v>1.6457130009514191E+18</v>
       </c>
     </row>
-    <row r="86" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="86" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H86" t="str">
         <v>2022-02-24T21:04:57.704Z</v>
       </c>
@@ -7814,7 +8056,7 @@
         <v>1.6457130013446582E+18</v>
       </c>
     </row>
-    <row r="87" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="87" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H87" t="str">
         <v>2022-02-25T21:02:53.439Z</v>
       </c>
@@ -7909,7 +8151,7 @@
         <v>1.6457994008352566E+18</v>
       </c>
     </row>
-    <row r="88" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="88" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H88" t="str">
         <v>2022-02-25T21:04:30.403Z</v>
       </c>
@@ -8004,7 +8246,7 @@
         <v>1.645799400923586E+18</v>
       </c>
     </row>
-    <row r="89" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="89" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H89" t="str">
         <v>2022-02-28T21:04:42.600Z</v>
       </c>
@@ -8099,7 +8341,7 @@
         <v>1.6460586009161283E+18</v>
       </c>
     </row>
-    <row r="90" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="90" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H90" t="str">
         <v>2022-02-28T21:05:12.060Z</v>
       </c>
@@ -8194,7 +8436,7 @@
         <v>1.6460586011923548E+18</v>
       </c>
     </row>
-    <row r="91" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="91" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H91" t="str">
         <v>2022-03-01T21:03:37.554Z</v>
       </c>
@@ -8289,7 +8531,7 @@
         <v>1.6461450008107523E+18</v>
       </c>
     </row>
-    <row r="92" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H92" t="str">
         <v>2022-03-01T21:04:09.984Z</v>
       </c>
@@ -8384,7 +8626,7 @@
         <v>1.6461450009901238E+18</v>
       </c>
     </row>
-    <row r="93" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="93" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H93" t="str">
         <v>2022-03-02T21:02:56.999Z</v>
       </c>
@@ -8479,7 +8721,7 @@
         <v>1.6462314009054213E+18</v>
       </c>
     </row>
-    <row r="94" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="94" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H94" t="str">
         <v>2022-03-02T21:04:34.896Z</v>
       </c>
@@ -8574,7 +8816,7 @@
         <v>1.6462314009423483E+18</v>
       </c>
     </row>
-    <row r="95" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="95" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H95" t="str">
         <v>2022-03-03T21:02:59.471Z</v>
       </c>
@@ -8669,7 +8911,7 @@
         <v>1.6463178008899474E+18</v>
       </c>
     </row>
-    <row r="96" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="96" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H96" t="str">
         <v>2022-03-03T21:04:07.292Z</v>
       </c>
@@ -8764,7 +9006,7 @@
         <v>1.6463178010616461E+18</v>
       </c>
     </row>
-    <row r="97" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="97" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H97" t="str">
         <v>2022-03-04T21:02:59.212Z</v>
       </c>
@@ -8859,7 +9101,7 @@
         <v>1.6464042009293906E+18</v>
       </c>
     </row>
-    <row r="98" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="98" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H98" t="str">
         <v>2022-03-04T21:04:35.145Z</v>
       </c>
@@ -8954,7 +9196,7 @@
         <v>1.6464042010285714E+18</v>
       </c>
     </row>
-    <row r="99" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="99" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H99" t="str">
         <v>2022-03-07T21:04:00.308Z</v>
       </c>
@@ -9049,7 +9291,7 @@
         <v>1.6466634012070986E+18</v>
       </c>
     </row>
-    <row r="100" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="100" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H100" t="str">
         <v>2022-03-07T21:04:10.195Z</v>
       </c>
@@ -9144,7 +9386,7 @@
         <v>1.6466634009024932E+18</v>
       </c>
     </row>
-    <row r="101" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="101" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H101" t="str">
         <v>2022-03-08T21:03:40.230Z</v>
       </c>
@@ -9239,7 +9481,7 @@
         <v>1.6467498011673528E+18</v>
       </c>
     </row>
-    <row r="102" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="102" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H102" t="str">
         <v>2022-03-08T21:04:51.213Z</v>
       </c>
@@ -9334,7 +9576,7 @@
         <v>1.6467498008669883E+18</v>
       </c>
     </row>
-    <row r="103" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="103" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H103" t="str">
         <v>2022-03-09T21:03:35.075Z</v>
       </c>
@@ -9429,7 +9671,7 @@
         <v>1.6468362011278108E+18</v>
       </c>
     </row>
-    <row r="104" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="104" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H104" t="str">
         <v>2022-03-09T21:04:55.397Z</v>
       </c>
@@ -9524,7 +9766,7 @@
         <v>1.6468363567282463E+18</v>
       </c>
     </row>
-    <row r="105" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="105" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H105" t="str">
         <v>2022-03-10T21:02:46.384Z</v>
       </c>
@@ -9619,7 +9861,7 @@
         <v>1.6469226009602143E+18</v>
       </c>
     </row>
-    <row r="106" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="106" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H106" t="str">
         <v>2022-03-10T21:05:18.770Z</v>
       </c>
@@ -9714,7 +9956,7 @@
         <v>1.6469226008840328E+18</v>
       </c>
     </row>
-    <row r="107" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="107" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H107" t="str">
         <v>2022-03-11T21:03:04.135Z</v>
       </c>
@@ -9809,7 +10051,7 @@
         <v>1.6470090009359342E+18</v>
       </c>
     </row>
-    <row r="108" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="108" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H108" t="str">
         <v>2022-03-11T21:05:25.993Z</v>
       </c>
@@ -9904,7 +10146,7 @@
         <v>1.6470090007990438E+18</v>
       </c>
     </row>
-    <row r="109" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="109" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H109" t="str">
         <v>2022-03-14T20:02:58.078Z</v>
       </c>
@@ -9999,7 +10241,7 @@
         <v>1.6472646008065795E+18</v>
       </c>
     </row>
-    <row r="110" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="110" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H110" t="str">
         <v>2022-03-14T20:03:47.723Z</v>
       </c>
@@ -10094,7 +10336,7 @@
         <v>1.6472646009817313E+18</v>
       </c>
     </row>
-    <row r="111" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="111" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H111" t="str">
         <v>2022-03-15T20:02:38.917Z</v>
       </c>
@@ -10189,7 +10431,7 @@
         <v>1.6473510009420134E+18</v>
       </c>
     </row>
-    <row r="112" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H112" t="str">
         <v>2022-03-15T20:04:48.823Z</v>
       </c>
@@ -10284,7 +10526,7 @@
         <v>1.6473510008669949E+18</v>
       </c>
     </row>
-    <row r="113" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="113" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H113" t="str">
         <v>2022-03-16T20:02:30.323Z</v>
       </c>
@@ -10379,7 +10621,7 @@
         <v>1.6474374009310001E+18</v>
       </c>
     </row>
-    <row r="114" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="114" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H114" t="str">
         <v>2022-03-16T20:04:21.859Z</v>
       </c>
@@ -10474,7 +10716,7 @@
         <v>1.6474374008309322E+18</v>
       </c>
     </row>
-    <row r="115" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H115" t="str">
         <v>2022-03-17T20:03:46.912Z</v>
       </c>
@@ -10569,7 +10811,7 @@
         <v>1.6475238009655089E+18</v>
       </c>
     </row>
-    <row r="116" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="116" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H116" t="str">
         <v>2022-03-17T20:05:12.601Z</v>
       </c>
@@ -10664,7 +10906,7 @@
         <v>1.6475238008517335E+18</v>
       </c>
     </row>
-    <row r="117" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="117" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H117" t="str">
         <v>2022-03-18T20:03:37.849Z</v>
       </c>
@@ -10759,7 +11001,7 @@
         <v>1.6476102012701716E+18</v>
       </c>
     </row>
-    <row r="118" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="118" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H118" t="str">
         <v>2022-03-18T20:03:53.855Z</v>
       </c>
@@ -10854,7 +11096,7 @@
         <v>1.6476102009921288E+18</v>
       </c>
     </row>
-    <row r="119" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="119" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H119" t="str">
         <v>2022-03-21T20:03:03.978Z</v>
       </c>
@@ -10949,7 +11191,7 @@
         <v>1.6478694008721864E+18</v>
       </c>
     </row>
-    <row r="120" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="120" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H120" t="str">
         <v>2022-03-21T20:05:15.085Z</v>
       </c>
@@ -11044,7 +11286,7 @@
         <v>1.6478694010544758E+18</v>
       </c>
     </row>
-    <row r="121" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="121" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H121" t="str">
         <v>2022-03-22T20:02:51.556Z</v>
       </c>
@@ -11139,7 +11381,7 @@
         <v>1.6479558008467904E+18</v>
       </c>
     </row>
-    <row r="122" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="122" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H122" t="str">
         <v>2022-03-22T20:05:09.584Z</v>
       </c>
@@ -11234,7 +11476,7 @@
         <v>1.6479558009962399E+18</v>
       </c>
     </row>
-    <row r="123" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="123" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H123" t="str">
         <v>2022-03-23T20:04:09.158Z</v>
       </c>
@@ -11329,7 +11571,7 @@
         <v>1.648042200870828E+18</v>
       </c>
     </row>
-    <row r="124" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="124" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H124" t="str">
         <v>2022-03-23T20:04:58.470Z</v>
       </c>
@@ -11424,7 +11666,7 @@
         <v>1.6480422009656845E+18</v>
       </c>
     </row>
-    <row r="125" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="125" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H125" t="str">
         <v>2022-03-24T20:04:32.572Z</v>
       </c>
@@ -11519,7 +11761,7 @@
         <v>1.6481286008111439E+18</v>
       </c>
     </row>
-    <row r="126" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="126" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H126" t="str">
         <v>2022-03-24T20:05:23.715Z</v>
       </c>
@@ -11614,7 +11856,7 @@
         <v>1.6481286009171159E+18</v>
       </c>
     </row>
-    <row r="127" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H127" t="str">
         <v>2022-03-25T20:04:00.726Z</v>
       </c>
@@ -11709,7 +11951,7 @@
         <v>1.6482150008425224E+18</v>
       </c>
     </row>
-    <row r="128" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="128" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H128" t="str">
         <v>2022-03-25T20:05:18.895Z</v>
       </c>
@@ -11804,7 +12046,7 @@
         <v>1.648215001037366E+18</v>
       </c>
     </row>
-    <row r="129" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="129" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H129" t="str">
         <v>2022-03-28T20:03:55.967Z</v>
       </c>
@@ -11899,7 +12141,7 @@
         <v>1.6484742010723052E+18</v>
       </c>
     </row>
-    <row r="130" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="130" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H130" t="str">
         <v>2022-03-28T20:03:59.678Z</v>
       </c>
@@ -11994,7 +12236,7 @@
         <v>1.6484742008424535E+18</v>
       </c>
     </row>
-    <row r="131" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="131" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H131" t="str">
         <v>2022-03-29T20:03:25.470Z</v>
       </c>
@@ -12089,7 +12331,7 @@
         <v>1.6485606010301563E+18</v>
       </c>
     </row>
-    <row r="132" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="132" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H132" t="str">
         <v>2022-03-29T20:03:29.585Z</v>
       </c>
@@ -12184,7 +12426,7 @@
         <v>1.6485606009201144E+18</v>
       </c>
     </row>
-    <row r="133" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="133" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H133" t="str">
         <v>2022-03-30T20:03:43.503Z</v>
       </c>
@@ -12279,7 +12521,7 @@
         <v>1.6486470008638802E+18</v>
       </c>
     </row>
-    <row r="134" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="134" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H134" t="str">
         <v>2022-03-30T20:03:48.368Z</v>
       </c>
@@ -12374,7 +12616,7 @@
         <v>1.6486470010467305E+18</v>
       </c>
     </row>
-    <row r="135" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="135" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H135" t="str">
         <v>2022-03-31T20:03:40.632Z</v>
       </c>
@@ -12469,7 +12711,7 @@
         <v>1.6487334010226237E+18</v>
       </c>
     </row>
-    <row r="136" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="136" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H136" t="str">
         <v>2022-03-31T20:03:43.843Z</v>
       </c>
@@ -12564,7 +12806,7 @@
         <v>1.6487334009747259E+18</v>
       </c>
     </row>
-    <row r="137" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="137" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H137" t="str">
         <v>2022-04-01T20:04:17.582Z</v>
       </c>
@@ -12659,7 +12901,7 @@
         <v>1.6488205856927309E+18</v>
       </c>
     </row>
-    <row r="138" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="138" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H138" t="str">
         <v>2022-04-01T20:04:21.522Z</v>
       </c>
@@ -12754,7 +12996,7 @@
         <v>1.6488201980079962E+18</v>
       </c>
     </row>
-    <row r="139" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="139" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H139" t="str">
         <v>2022-04-04T20:03:28.319Z</v>
       </c>
@@ -12849,7 +13091,7 @@
         <v>1.6490790010273684E+18</v>
       </c>
     </row>
-    <row r="140" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="140" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H140" t="str">
         <v>2022-04-04T20:03:35.454Z</v>
       </c>
@@ -12944,7 +13186,7 @@
         <v>1.6490790009908767E+18</v>
       </c>
     </row>
-    <row r="141" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="141" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H141" t="str">
         <v>2022-04-05T20:04:24.806Z</v>
       </c>
@@ -13039,7 +13281,7 @@
         <v>1.6491654009770568E+18</v>
       </c>
     </row>
-    <row r="142" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="142" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H142" t="str">
         <v>2022-04-05T20:04:28.860Z</v>
       </c>
@@ -13134,7 +13376,7 @@
         <v>1.6491654008415145E+18</v>
       </c>
     </row>
-    <row r="143" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="143" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H143" t="str">
         <v>2022-04-06T20:03:46.832Z</v>
       </c>
@@ -13229,7 +13471,7 @@
         <v>1.6492518011513536E+18</v>
       </c>
     </row>
-    <row r="144" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="144" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H144" t="str">
         <v>2022-04-06T20:03:50.617Z</v>
       </c>
@@ -13324,7 +13566,7 @@
         <v>1.6492518098101238E+18</v>
       </c>
     </row>
-    <row r="145" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="145" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H145" t="str">
         <v>2022-04-07T20:04:07.229Z</v>
       </c>
@@ -13419,7 +13661,7 @@
         <v>1.6493382011492273E+18</v>
       </c>
     </row>
-    <row r="146" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="146" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H146" t="str">
         <v>2022-04-07T20:04:11.003Z</v>
       </c>
@@ -13514,7 +13756,7 @@
         <v>1.6493382008164006E+18</v>
       </c>
     </row>
-    <row r="147" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="147" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H147" t="str">
         <v>2022-04-08T20:03:16.394Z</v>
       </c>
@@ -13609,7 +13851,7 @@
         <v>1.6494246009828403E+18</v>
       </c>
     </row>
-    <row r="148" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="148" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H148" t="str">
         <v>2022-04-08T20:03:21.658Z</v>
       </c>
@@ -13704,7 +13946,7 @@
         <v>1.6494246008332995E+18</v>
       </c>
     </row>
-    <row r="149" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="149" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H149" t="str">
         <v>2022-04-11T20:02:28.874Z</v>
       </c>
@@ -13799,7 +14041,7 @@
         <v>1.6496838010965952E+18</v>
       </c>
     </row>
-    <row r="150" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="150" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H150" t="str">
         <v>2022-04-11T20:03:30.691Z</v>
       </c>
@@ -13894,7 +14136,7 @@
         <v>1.6496838009817318E+18</v>
       </c>
     </row>
-    <row r="151" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="151" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H151" t="str">
         <v>2022-04-12T20:03:00.827Z</v>
       </c>
@@ -13989,7 +14231,7 @@
         <v>1.6497702010467154E+18</v>
       </c>
     </row>
-    <row r="152" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="152" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H152" t="str">
         <v>2022-04-12T20:03:02.536Z</v>
       </c>
@@ -14084,7 +14326,7 @@
         <v>1.6497702007914435E+18</v>
       </c>
     </row>
-    <row r="153" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="153" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H153" t="str">
         <v>2022-04-13T20:03:42.963Z</v>
       </c>
@@ -14179,7 +14421,7 @@
         <v>1.6498566009085985E+18</v>
       </c>
     </row>
-    <row r="154" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="154" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H154" t="str">
         <v>2022-04-13T20:03:46.285Z</v>
       </c>
@@ -14274,7 +14516,7 @@
         <v>1.6498566007854961E+18</v>
       </c>
     </row>
-    <row r="155" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="155" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H155" t="str">
         <v>2022-04-14T20:03:33.606Z</v>
       </c>
@@ -14369,7 +14611,7 @@
         <v>1.6499430010383552E+18</v>
       </c>
     </row>
-    <row r="156" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="156" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H156" t="str">
         <v>2022-04-14T20:03:37.852Z</v>
       </c>
@@ -14464,7 +14706,7 @@
         <v>1.6499430008783698E+18</v>
       </c>
     </row>
-    <row r="157" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="157" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H157" t="str">
         <v>2022-04-18T20:02:09.359Z</v>
       </c>
@@ -14559,7 +14801,7 @@
         <v>1.6502886009220009E+18</v>
       </c>
     </row>
-    <row r="158" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="158" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H158" t="str">
         <v>2022-04-18T20:02:51.325Z</v>
       </c>
@@ -14654,7 +14896,7 @@
         <v>1.6502886011135311E+18</v>
       </c>
     </row>
-    <row r="159" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="159" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H159" t="str">
         <v>2022-04-19T20:03:18.654Z</v>
       </c>
@@ -14749,7 +14991,7 @@
         <v>1.6503750009208581E+18</v>
       </c>
     </row>
-    <row r="160" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="160" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H160" t="str">
         <v>2022-04-19T20:03:22.095Z</v>
       </c>
@@ -14844,7 +15086,7 @@
         <v>1.6503750007850199E+18</v>
       </c>
     </row>
-    <row r="161" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="161" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H161" t="str">
         <v>2022-04-20T20:03:08.116Z</v>
       </c>
@@ -14939,7 +15181,7 @@
         <v>1.6504614009782948E+18</v>
       </c>
     </row>
-    <row r="162" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="162" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H162" t="str">
         <v>2022-04-20T20:03:11.190Z</v>
       </c>
@@ -15034,7 +15276,7 @@
         <v>1.6504614426021673E+18</v>
       </c>
     </row>
-    <row r="163" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="163" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H163" t="str">
         <v>2022-04-21T20:03:28.108Z</v>
       </c>
@@ -15129,7 +15371,7 @@
         <v>1.6505478009709038E+18</v>
       </c>
     </row>
-    <row r="164" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="164" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H164" t="str">
         <v>2022-04-21T20:03:31.960Z</v>
       </c>
@@ -15224,7 +15466,7 @@
         <v>1.6505478788369587E+18</v>
       </c>
     </row>
-    <row r="165" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="165" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H165" t="str">
         <v>2022-04-22T20:03:40.963Z</v>
       </c>
@@ -15319,7 +15561,7 @@
         <v>1.6506342008258363E+18</v>
       </c>
     </row>
-    <row r="166" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="166" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H166" t="str">
         <v>2022-04-22T20:04:04.952Z</v>
       </c>
@@ -15414,7 +15656,7 @@
         <v>1.6506342009679795E+18</v>
       </c>
     </row>
-    <row r="167" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="167" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H167" t="str">
         <v>2022-04-25T20:03:34.512Z</v>
       </c>
@@ -15509,7 +15751,7 @@
         <v>1.6508934010462036E+18</v>
       </c>
     </row>
-    <row r="168" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="168" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H168" t="str">
         <v>2022-04-25T20:03:37.964Z</v>
       </c>
@@ -15604,7 +15846,7 @@
         <v>1.6508934008536604E+18</v>
       </c>
     </row>
-    <row r="169" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="169" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H169" t="str">
         <v>2022-04-26T20:03:22.470Z</v>
       </c>
@@ -15699,7 +15941,7 @@
         <v>1.6509798010452029E+18</v>
       </c>
     </row>
-    <row r="170" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="170" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H170" t="str">
         <v>2022-04-26T20:03:26.012Z</v>
       </c>
@@ -15794,7 +16036,7 @@
         <v>1.6509798010418094E+18</v>
       </c>
     </row>
-    <row r="171" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="171" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H171" t="str">
         <v>2022-04-27T20:03:41.423Z</v>
       </c>
@@ -15889,7 +16131,7 @@
         <v>1.6510662008929275E+18</v>
       </c>
     </row>
-    <row r="172" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="172" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H172" t="str">
         <v>2022-04-27T20:03:46.698Z</v>
       </c>
@@ -15984,7 +16226,7 @@
         <v>1.6510662008057449E+18</v>
       </c>
     </row>
-    <row r="173" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="173" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H173" t="str">
         <v>2022-04-28T20:04:56.994Z</v>
       </c>
@@ -16079,7 +16321,7 @@
         <v>1.6511526007753413E+18</v>
       </c>
     </row>
-    <row r="174" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H174" t="str">
         <v>2022-04-28T20:05:08.141Z</v>
       </c>
@@ -16174,7 +16416,7 @@
         <v>1.6511526008870218E+18</v>
       </c>
     </row>
-    <row r="175" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="175" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H175" t="str">
         <v>2022-04-29T20:04:29.084Z</v>
       </c>
@@ -16269,7 +16511,7 @@
         <v>1.6512390008594383E+18</v>
       </c>
     </row>
-    <row r="176" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="176" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H176" t="str">
         <v>2022-04-29T20:04:36.876Z</v>
       </c>
@@ -16364,7 +16606,7 @@
         <v>1.6512390007695393E+18</v>
       </c>
     </row>
-    <row r="177" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="177" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H177" t="str">
         <v>2022-05-02T20:03:59.978Z</v>
       </c>
@@ -16459,7 +16701,7 @@
         <v>1.6514982008976061E+18</v>
       </c>
     </row>
-    <row r="178" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="178" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H178" t="str">
         <v>2022-05-02T20:04:02.103Z</v>
       </c>
@@ -16554,7 +16796,7 @@
         <v>1.6514982007929572E+18</v>
       </c>
     </row>
-    <row r="179" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H179" t="str">
         <v>2022-05-03T20:03:06.194Z</v>
       </c>
@@ -16649,7 +16891,7 @@
         <v>1.6515846008827681E+18</v>
       </c>
     </row>
-    <row r="180" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="180" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H180" t="str">
         <v>2022-05-03T20:03:09.882Z</v>
       </c>
@@ -16744,7 +16986,7 @@
         <v>1.6515846007559616E+18</v>
       </c>
     </row>
-    <row r="181" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="181" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H181" t="str">
         <v>2022-05-04T20:03:56.963Z</v>
       </c>
@@ -16839,7 +17081,7 @@
         <v>1.6516710008483622E+18</v>
       </c>
     </row>
-    <row r="182" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="182" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H182" t="str">
         <v>2022-05-04T20:04:00.528Z</v>
       </c>
@@ -16934,7 +17176,7 @@
         <v>1.6516710007529101E+18</v>
       </c>
     </row>
-    <row r="183" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="183" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H183" t="str">
         <v>2022-05-05T20:04:14.488Z</v>
       </c>
@@ -17029,7 +17271,7 @@
         <v>1.6517574008502436E+18</v>
       </c>
     </row>
-    <row r="184" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="184" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H184" t="str">
         <v>2022-05-05T20:04:19.888Z</v>
       </c>
@@ -17124,7 +17366,7 @@
         <v>1.651757400749569E+18</v>
       </c>
     </row>
-    <row r="185" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="185" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H185" t="str">
         <v>2022-05-06T20:04:17.057Z</v>
       </c>
@@ -17219,7 +17461,7 @@
         <v>1.6518438008811886E+18</v>
       </c>
     </row>
-    <row r="186" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="186" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H186" t="str">
         <v>2022-05-06T20:04:19.144Z</v>
       </c>
@@ -17314,7 +17556,7 @@
         <v>1.6518438007372465E+18</v>
       </c>
     </row>
-    <row r="187" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="187" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H187" t="str">
         <v>2022-05-09T20:03:40.943Z</v>
       </c>
@@ -17409,7 +17651,7 @@
         <v>1.6521030009835407E+18</v>
       </c>
     </row>
-    <row r="188" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="188" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H188" t="str">
         <v>2022-05-09T20:03:44.844Z</v>
       </c>
@@ -17504,7 +17746,7 @@
         <v>1.6521030008488653E+18</v>
       </c>
     </row>
-    <row r="189" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H189" t="str">
         <v>2022-05-10T20:03:12.769Z</v>
       </c>
@@ -17599,7 +17841,7 @@
         <v>1.6521894010957338E+18</v>
       </c>
     </row>
-    <row r="190" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="190" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H190" t="str">
         <v>2022-05-10T20:03:17.595Z</v>
       </c>
@@ -17694,7 +17936,7 @@
         <v>1.6521894007277937E+18</v>
       </c>
     </row>
-    <row r="191" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="191" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H191" t="str">
         <v>2022-05-11T20:04:40.566Z</v>
       </c>
@@ -17789,7 +18031,7 @@
         <v>1.6522758010848466E+18</v>
       </c>
     </row>
-    <row r="192" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="192" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H192" t="str">
         <v>2022-05-11T20:04:44.812Z</v>
       </c>
@@ -17884,7 +18126,7 @@
         <v>1.6522758007917645E+18</v>
       </c>
     </row>
-    <row r="193" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="193" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H193" t="str">
         <v>2022-05-12T20:04:50.118Z</v>
       </c>
@@ -17979,7 +18221,7 @@
         <v>1.6523622010581005E+18</v>
       </c>
     </row>
-    <row r="194" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="194" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H194" t="str">
         <v>2022-05-12T20:04:53.965Z</v>
       </c>
@@ -18074,7 +18316,7 @@
         <v>1.6523622311381786E+18</v>
       </c>
     </row>
-    <row r="195" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="195" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H195" t="str">
         <v>2022-05-13T20:03:08.208Z</v>
       </c>
@@ -18169,7 +18411,7 @@
         <v>1.6524487405199629E+18</v>
       </c>
     </row>
-    <row r="196" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="196" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H196" t="str">
         <v>2022-05-13T20:03:57.910Z</v>
       </c>
@@ -18264,7 +18506,7 @@
         <v>1.6524486008539479E+18</v>
       </c>
     </row>
-    <row r="197" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="197" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H197" t="str">
         <v>2022-05-16T20:04:04.203Z</v>
       </c>
@@ -18359,7 +18601,7 @@
         <v>1.6527078010225393E+18</v>
       </c>
     </row>
-    <row r="198" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="198" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H198" t="str">
         <v>2022-05-16T20:04:08.321Z</v>
       </c>
@@ -18454,7 +18696,7 @@
         <v>1.6527078010319721E+18</v>
       </c>
     </row>
-    <row r="199" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="199" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H199" t="str">
         <v>2022-05-17T20:03:45.391Z</v>
       </c>
@@ -18549,7 +18791,7 @@
         <v>1.6527942007521897E+18</v>
       </c>
     </row>
-    <row r="200" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="200" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H200" t="str">
         <v>2022-05-17T20:04:14.427Z</v>
       </c>
@@ -18644,7 +18886,7 @@
         <v>1.6527942008469901E+18</v>
       </c>
     </row>
-    <row r="201" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="201" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H201" t="str">
         <v>2022-05-18T20:04:17.553Z</v>
       </c>
@@ -18739,7 +18981,7 @@
         <v>1.6528806010381143E+18</v>
       </c>
     </row>
-    <row r="202" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="202" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H202" t="str">
         <v>2022-05-18T20:04:21.688Z</v>
       </c>
@@ -18834,7 +19076,7 @@
         <v>1.6528807637526746E+18</v>
       </c>
     </row>
-    <row r="203" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="203" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H203" t="str">
         <v>2022-05-19T20:04:36.087Z</v>
       </c>
@@ -18929,7 +19171,7 @@
         <v>1.6529670009359037E+18</v>
       </c>
     </row>
-    <row r="204" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="204" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H204" t="str">
         <v>2022-05-19T20:04:37.808Z</v>
       </c>
@@ -19024,7 +19266,7 @@
         <v>1.6529670007554744E+18</v>
       </c>
     </row>
-    <row r="205" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="205" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H205" t="str">
         <v>2022-05-20T20:04:34.984Z</v>
       </c>
@@ -19119,7 +19361,7 @@
         <v>1.6530534010681014E+18</v>
       </c>
     </row>
-    <row r="206" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="206" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H206" t="str">
         <v>2022-05-20T20:04:59.674Z</v>
       </c>
@@ -19214,7 +19456,7 @@
         <v>1.6530534008314534E+18</v>
       </c>
     </row>
-    <row r="207" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H207" t="str">
         <v>2022-05-23T20:03:57.468Z</v>
       </c>
@@ -19309,7 +19551,7 @@
         <v>1.6533126009769994E+18</v>
       </c>
     </row>
-    <row r="208" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="208" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H208" t="str">
         <v>2022-05-23T20:03:58.930Z</v>
       </c>
@@ -19404,7 +19646,7 @@
         <v>1.6533126007945101E+18</v>
       </c>
     </row>
-    <row r="209" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="209" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H209" t="str">
         <v>2022-05-24T20:04:59.605Z</v>
       </c>
@@ -19499,7 +19741,7 @@
         <v>1.6533990009480742E+18</v>
       </c>
     </row>
-    <row r="210" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="210" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H210" t="str">
         <v>2022-05-24T20:05:01.280Z</v>
       </c>
@@ -19594,7 +19836,7 @@
         <v>1.6533990007391324E+18</v>
       </c>
     </row>
-    <row r="211" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="211" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H211" t="str">
         <v>2022-05-25T20:04:33.132Z</v>
       </c>
@@ -19689,7 +19931,7 @@
         <v>1.6534854008731781E+18</v>
       </c>
     </row>
-    <row r="212" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="212" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H212" t="str">
         <v>2022-05-25T20:04:38.116Z</v>
       </c>
@@ -19784,7 +20026,7 @@
         <v>1.6534854007469678E+18</v>
       </c>
     </row>
-    <row r="213" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="213" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H213" t="str">
         <v>2022-05-26T20:04:54.319Z</v>
       </c>
@@ -19879,7 +20121,7 @@
         <v>1.6535718009114611E+18</v>
       </c>
     </row>
-    <row r="214" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="214" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H214" t="str">
         <v>2022-05-26T20:04:57.593Z</v>
       </c>
@@ -19974,7 +20216,7 @@
         <v>1.6535718007284106E+18</v>
       </c>
     </row>
-    <row r="215" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="215" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H215" t="str">
         <v>2022-05-27T20:04:19.442Z</v>
       </c>
@@ -20069,7 +20311,7 @@
         <v>1.6536582007953144E+18</v>
       </c>
     </row>
-    <row r="216" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="216" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H216" t="str">
         <v>2022-05-27T20:04:22.664Z</v>
       </c>
@@ -20164,7 +20406,7 @@
         <v>1.653658200750282E+18</v>
       </c>
     </row>
-    <row r="217" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="217" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H217" t="str">
         <v>2022-05-31T20:04:13.533Z</v>
       </c>
@@ -20259,7 +20501,7 @@
         <v>1.6540038009148411E+18</v>
       </c>
     </row>
-    <row r="218" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="218" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H218" t="str">
         <v>2022-05-31T20:04:17.253Z</v>
       </c>
@@ -20354,7 +20596,7 @@
         <v>1.6540038008707909E+18</v>
       </c>
     </row>
-    <row r="219" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="219" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H219" t="str">
         <v>2022-06-01T20:04:13.907Z</v>
       </c>
@@ -20449,7 +20691,7 @@
         <v>1.6540902008946404E+18</v>
       </c>
     </row>
-    <row r="220" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="220" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H220" t="str">
         <v>2022-06-01T20:04:15.080Z</v>
       </c>
@@ -20544,7 +20786,7 @@
         <v>1.6540902007702093E+18</v>
       </c>
     </row>
-    <row r="221" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="221" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H221" t="str">
         <v>2022-06-02T20:04:07.067Z</v>
       </c>
@@ -20639,7 +20881,7 @@
         <v>1.654176600905546E+18</v>
       </c>
     </row>
-    <row r="222" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="222" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H222" t="str">
         <v>2022-06-02T20:04:09.177Z</v>
       </c>
@@ -20734,7 +20976,7 @@
         <v>1.6541766007434504E+18</v>
       </c>
     </row>
-    <row r="223" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="223" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H223" t="str">
         <v>2022-06-03T20:05:02.262Z</v>
       </c>
@@ -20829,7 +21071,7 @@
         <v>1.6542630010376781E+18</v>
       </c>
     </row>
-    <row r="224" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="224" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H224" t="str">
         <v>2022-06-03T20:05:04.504Z</v>
       </c>
@@ -20924,7 +21166,7 @@
         <v>1.6542630007625741E+18</v>
       </c>
     </row>
-    <row r="225" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="225" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H225" t="str">
         <v>2022-06-06T20:04:03.117Z</v>
       </c>
@@ -21019,7 +21261,7 @@
         <v>1.654522200980373E+18</v>
       </c>
     </row>
-    <row r="226" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="226" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H226" t="str">
         <v>2022-06-06T20:04:07.488Z</v>
       </c>
@@ -21114,7 +21356,7 @@
         <v>1.6545222008192197E+18</v>
       </c>
     </row>
-    <row r="227" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="227" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H227" t="str">
         <v>2022-06-07T20:04:51.984Z</v>
       </c>
@@ -21209,7 +21451,7 @@
         <v>1.6546086008637286E+18</v>
       </c>
     </row>
-    <row r="228" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="228" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H228" t="str">
         <v>2022-06-07T20:04:54.462Z</v>
       </c>
@@ -21304,7 +21546,7 @@
         <v>1.6546086425584317E+18</v>
       </c>
     </row>
-    <row r="229" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="229" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H229" t="str">
         <v>2022-06-08T20:03:54.934Z</v>
       </c>
@@ -21399,7 +21641,7 @@
         <v>1.6546950010194186E+18</v>
       </c>
     </row>
-    <row r="230" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="230" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H230" t="str">
         <v>2022-06-08T20:03:58.620Z</v>
       </c>
@@ -21494,7 +21736,7 @@
         <v>1.6546950008120804E+18</v>
       </c>
     </row>
-    <row r="231" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="231" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H231" t="str">
         <v>2022-06-09T20:03:48.583Z</v>
       </c>
@@ -21589,7 +21831,7 @@
         <v>1.6547814009732803E+18</v>
       </c>
     </row>
-    <row r="232" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="232" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H232" t="str">
         <v>2022-06-09T20:03:51.272Z</v>
       </c>
@@ -21684,7 +21926,7 @@
         <v>1.6547814008161265E+18</v>
       </c>
     </row>
-    <row r="233" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="233" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H233" t="str">
         <v>2022-06-10T20:03:54.905Z</v>
       </c>
@@ -21779,7 +22021,7 @@
         <v>1.6548678008490949E+18</v>
       </c>
     </row>
-    <row r="234" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="234" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H234" t="str">
         <v>2022-06-10T20:03:58.103Z</v>
       </c>
@@ -21874,7 +22116,7 @@
         <v>1.654867801030306E+18</v>
       </c>
     </row>
-    <row r="235" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="235" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H235" t="str">
         <v>2022-06-13T20:05:29.339Z</v>
       </c>
@@ -21969,7 +22211,7 @@
         <v>1.6551270010495345E+18</v>
       </c>
     </row>
-    <row r="236" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="236" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H236" t="str">
         <v>2022-06-13T20:05:31.937Z</v>
       </c>
@@ -22064,7 +22306,7 @@
         <v>1.6551270008857249E+18</v>
       </c>
     </row>
-    <row r="237" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="237" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H237" t="str">
         <v>2022-06-14T20:04:48.800Z</v>
       </c>
@@ -22159,7 +22401,7 @@
         <v>1.655213400937514E+18</v>
       </c>
     </row>
-    <row r="238" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="238" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H238" t="str">
         <v>2022-06-14T20:05:06.670Z</v>
       </c>
@@ -22254,7 +22496,7 @@
         <v>1.6552134010097208E+18</v>
       </c>
     </row>
-    <row r="239" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H239" t="str">
         <v>2022-06-15T20:03:57.195Z</v>
       </c>
@@ -22349,7 +22591,7 @@
         <v>1.6552998009664868E+18</v>
       </c>
     </row>
-    <row r="240" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="240" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H240" t="str">
         <v>2022-06-15T20:04:00.467Z</v>
       </c>
@@ -22444,7 +22686,7 @@
         <v>1.6552998007547935E+18</v>
       </c>
     </row>
-    <row r="241" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="241" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H241" t="str">
         <v>2022-06-16T20:03:30.892Z</v>
       </c>
@@ -22539,7 +22781,7 @@
         <v>1.6553862008134449E+18</v>
       </c>
     </row>
-    <row r="242" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="242" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H242" t="str">
         <v>2022-06-16T20:04:19.534Z</v>
       </c>
@@ -22634,7 +22876,7 @@
         <v>1.65538620093105E+18</v>
       </c>
     </row>
-    <row r="243" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="243" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H243" t="str">
         <v>2022-06-17T20:05:20.028Z</v>
       </c>
@@ -22729,7 +22971,7 @@
         <v>1.6554726012034657E+18</v>
       </c>
     </row>
-    <row r="244" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="244" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H244" t="str">
         <v>2022-06-17T20:05:32.851Z</v>
       </c>
@@ -22824,7 +23066,7 @@
         <v>1.6554726009903135E+18</v>
       </c>
     </row>
-    <row r="245" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="245" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H245" t="str">
         <v>2022-06-21T20:04:21.062Z</v>
       </c>
@@ -22919,7 +23161,7 @@
         <v>1.6558182010024174E+18</v>
       </c>
     </row>
-    <row r="246" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="246" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H246" t="str">
         <v>2022-06-21T20:04:23.799Z</v>
       </c>
@@ -23014,7 +23256,7 @@
         <v>1.6558182007952102E+18</v>
       </c>
     </row>
-    <row r="247" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="247" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H247" t="str">
         <v>2022-06-22T20:04:22.187Z</v>
       </c>
@@ -23109,7 +23351,7 @@
         <v>1.6559046010467346E+18</v>
       </c>
     </row>
-    <row r="248" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="248" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H248" t="str">
         <v>2022-06-22T20:04:26.643Z</v>
       </c>
@@ -23204,7 +23446,7 @@
         <v>1.6559046006995983E+18</v>
       </c>
     </row>
-    <row r="249" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="249" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H249" t="str">
         <v>2022-06-23T20:04:00.471Z</v>
       </c>
@@ -23299,7 +23541,7 @@
         <v>1.6559910008743424E+18</v>
       </c>
     </row>
-    <row r="250" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="250" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H250" t="str">
         <v>2022-06-23T20:04:01.776Z</v>
       </c>
@@ -23394,7 +23636,7 @@
         <v>1.6559910372999649E+18</v>
       </c>
     </row>
-    <row r="251" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="251" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H251" t="str">
         <v>2022-06-24T20:04:30.414Z</v>
       </c>
@@ -23489,7 +23731,7 @@
         <v>1.6560774007502354E+18</v>
       </c>
     </row>
-    <row r="252" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="252" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H252" t="str">
         <v>2022-06-24T20:04:32.635Z</v>
       </c>
@@ -23584,7 +23826,7 @@
         <v>1.6560774008948803E+18</v>
       </c>
     </row>
-    <row r="253" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="253" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H253" t="str">
         <v>2022-06-27T20:04:07.115Z</v>
       </c>
@@ -23679,7 +23921,7 @@
         <v>1.6563366009252616E+18</v>
       </c>
     </row>
-    <row r="254" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="254" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H254" t="str">
         <v>2022-06-27T20:04:10.789Z</v>
       </c>
@@ -23774,7 +24016,7 @@
         <v>1.6563366008678953E+18</v>
       </c>
     </row>
-    <row r="255" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="255" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H255" t="str">
         <v>2022-06-28T20:04:14.009Z</v>
       </c>
@@ -23869,7 +24111,7 @@
         <v>1.656423000883649E+18</v>
       </c>
     </row>
-    <row r="256" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="256" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H256" t="str">
         <v>2022-06-28T20:04:17.550Z</v>
       </c>
@@ -23964,7 +24206,7 @@
         <v>1.6564230575265677E+18</v>
       </c>
     </row>
-    <row r="257" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="257" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H257" t="str">
         <v>2022-06-29T20:03:32.600Z</v>
       </c>
@@ -24059,7 +24301,7 @@
         <v>1.6565094008781266E+18</v>
       </c>
     </row>
-    <row r="258" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="258" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H258" t="str">
         <v>2022-06-29T20:03:36.389Z</v>
       </c>
@@ -24154,7 +24396,7 @@
         <v>1.6565094007447037E+18</v>
       </c>
     </row>
-    <row r="259" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="259" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H259" t="str">
         <v>2022-06-30T20:05:36.687Z</v>
       </c>
@@ -24249,7 +24491,7 @@
         <v>1.656595800778718E+18</v>
       </c>
     </row>
-    <row r="260" spans="8:38" x14ac:dyDescent="0.25">
+    <row r="260" spans="8:38" x14ac:dyDescent="0.3">
       <c r="H260" t="str">
         <v>2022-06-30T20:05:39.603Z</v>
       </c>
@@ -24353,15 +24595,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4053D4E5-42C1-4DE5-B169-B8D18212659F}">
   <dimension ref="C4:J160"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>17</v>
       </c>
@@ -24369,7 +24611,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>8</v>
       </c>
@@ -24377,7 +24619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>14</v>
       </c>
@@ -24386,7 +24628,7 @@
         <v>45837</v>
       </c>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>15</v>
       </c>
@@ -24401,7 +24643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
       <c r="H10" t="str" cm="1">
         <f t="array" ref="H10:I24">_xll.MS.GET_ASSET(H8)</f>
         <v>field</v>
@@ -24414,7 +24656,7 @@
         <v>90_CDMXCB_19</v>
       </c>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
       <c r="H11" t="str">
         <v>orm_class</v>
       </c>
@@ -24422,7 +24664,7 @@
         <v>Asset</v>
       </c>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
       <c r="H12" t="str">
         <v>id</v>
       </c>
@@ -24430,7 +24672,7 @@
         <v>119564</v>
       </c>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.3">
       <c r="H13" t="str">
         <v>unique_identifier</v>
       </c>
@@ -24438,7 +24680,7 @@
         <v>90_CBPF_48</v>
       </c>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
       <c r="H14" t="str">
         <v>figi</v>
       </c>
@@ -24446,7 +24688,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
       <c r="H15" t="str">
         <v>composite</v>
       </c>
@@ -24454,7 +24696,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
       <c r="H16" t="str">
         <v>share_class</v>
       </c>
@@ -24462,7 +24704,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H17" t="str">
         <v>isin</v>
       </c>
@@ -24470,7 +24712,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H18" t="str">
         <v>security_type</v>
       </c>
@@ -24478,7 +24720,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H19" t="str">
         <v>security_type_2</v>
       </c>
@@ -24486,7 +24728,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H20" t="str">
         <v>security_market_sector</v>
       </c>
@@ -24494,7 +24736,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H21" t="str">
         <v>is_tradable</v>
       </c>
@@ -24502,7 +24744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H22" t="str">
         <v>is_custom_by_organization</v>
       </c>
@@ -24510,7 +24752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H23" t="str">
         <v>current_snapshot</v>
       </c>
@@ -24518,7 +24760,7 @@
         <v>{"orm_class": "AssetSnapshot", "id": null, "asset": 119564, "effective_from": "2025-09-09 13:14:01.208650+00:00", "effective_to": null, "name": "90_CBPF_48", "ticker": "90_CBPF_48", "exchange_code": null, "asset_ticker_group_id": "MSI7MPRAT9AE", "venue_specific_properties": null}</v>
       </c>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H24" t="str">
         <v>current_pricing_detail</v>
       </c>
@@ -24526,7 +24768,7 @@
         <v>{"orm_class": "AssetPricingDetail", "instrument_dump": {"instrument": {"spread": 0.00213427, "calendar": {"name": "Mexican stock exchange"}, "schedule": {"dates": ["2025-08-24", "2025-09-15", "2025-10-14", "2025-11-14", "2025-12-15", "2026-01-12", "2026-02-10", "2026-03-13", "2026-04-13", "2026-05-12", "2026-06-12", "2026-07-13", "2026-08-11", "2026-09-11", "2026-10-12", "2026-11-10", "2026-12-11", "2027-01-11", "2027-02-09", "2027-03-12", "2027-04-12", "2027-05-11", "2027-06-11", "2027-07-12", "2027-08-10", "2027-09-10", "2027-10-11", "2027-11-09", "2027-12-10", "2028-01-10", "2028-02-08", "2028-03-10", "2028-04-10", "2028-05-09", "2028-06-09", "2028-07-10", "2028-08-08", "2028-09-08", "2028-10-09", "2028-11-07", "2028-12-08", "2029-01-08", "2029-02-06", "2029-03-06", "2029-04-06", "2029-05-07", "2029-06-05", "2029-07-06", "2029-08-06", "2029-09-04", "2029-10-05", "2029-11-05", "2029-12-03", "2030-01-02", "2030-02-01", "2030-03-04", "2030-04-02", "2030-05-03", "2030-06-03", "2030-07-02", "2030-08-02", "2030-09-02", "2030-10-02", "2030-11-01", "2030-12-02", "2030-12-31", "2031-01-31", "2031-03-03", "2031-04-01", "2031-05-02", "2031-06-02", "2031-07-01", "2031-08-01", "2031-09-01", "2031-09-30", "2031-10-31", "2031-12-01", "2031-12-30", "2032-01-30", "2032-03-01", "2032-03-30", "2032-04-30", "2032-05-31", "2032-06-29", "2032-07-30", "2032-08-30", "2032-09-28", "2032-10-29", "2032-11-29", "2032-12-28", "2033-01-28", "2033-02-28", "2033-03-29", "2033-04-29", "2033-05-30", "2033-06-28", "2033-07-29", "2033-08-29", "2033-09-27", "2033-10-28", "2033-11-28", "2033-12-27", "2034-01-27", "2034-02-27", "2034-03-28", "2034-04-28", "2034-05-29", "2034-06-27", "2034-07-28", "2034-08-28", "2034-09-26", "2034-10-27", "2034-11-27", "2034-12-26", "2035-01-23", "2035-02-23", "2035-03-26", "2035-04-23", "2035-05-22", "2035-06-22", "2035-07-23", "2035-08-21", "2035-09-21", "2035-10-22", "2035-11-20", "2035-12-18", "2036-01-18", "2036-02-18", "2036-03-18", "2036-04-15", "2036-05-16", "2036-06-16", "2036-07-15", "2036-08-15", "2036-09-15", "2036-10-14", "2036-11-14", "2036-12-15", "2037-01-12", "2037-02-10", "2037-03-13", "2037-04-13", "2037-05-12", "2037-06-12", "2037-07-13", "2037-08-11", "2037-09-11", "2037-10-12", "2037-11-10", "2037-12-11", "2038-01-11", "2038-02-09", "2038-03-12", "2038-04-12", "2038-05-11", "2038-06-11", "2038-07-12", "2038-08-10", "2038-09-10", "2038-10-11", "2038-11-09", "2038-12-10", "2039-01-10", "2039-02-08", "2039-03-11", "2039-04-11", "2039-05-10", "2039-06-10", "2039-07-11", "2039-08-09", "2039-09-09", "2039-10-10", "2039-11-08", "2039-12-09", "2040-01-09", "2040-02-07", "2040-03-09", "2040-04-09", "2040-05-08", "2040-06-08", "2040-07-09", "2040-08-07", "2040-09-07", "2040-10-08", "2040-11-06", "2040-12-07", "2041-01-07", "2041-02-05", "2041-03-08", "2041-04-08", "2041-05-07", "2041-06-07", "2041-07-08", "2041-08-06", "2041-09-06", "2041-10-07", "2041-11-05", "2041-12-06", "2042-01-06", "2042-02-04", "2042-03-07", "2042-04-07", "2042-05-06", "2042-06-06", "2042-07-07", "2042-08-05", "2042-09-05", "2042-10-06", "2042-11-04", "2042-12-05", "2043-01-05", "2043-02-03", "2043-03-03", "2043-04-03", "2043-05-04", "2043-06-01", "2043-06-30", "2043-07-31", "2043-08-31", "2043-09-29", "2043-10-30", "2043-11-30", "2043-12-29", "2044-01-29", "2044-02-29", "2044-03-29", "2044-04-29", "2044-05-30", "2044-06-28", "2044-07-29", "2044-08-29", "2044-09-27", "2044-10-28", "2044-11-28", "2044-12-27", "2045-01-27", "2045-02-27", "2045-03-28", "2045-04-28", "2045-05-29", "2045-06-27", "2045-07-28", "2045-08-28", "2045-09-26", "2045-10-27", "2045-11-27", "2045-12-26", "2046-01-26", "2046-02-26", "2046-03-27", "2046-04-27", "2046-05-28", "2046-06-26", "2046-07-27", "2046-08-27", "2046-09-25", "2046-10-26", "2046-11-26", "2046-12-26", "2047-01-25", "2047-02-25", "2047-03-26", "2047-04-26", "2047-05-27", "2047-06-25"], "calendar": {"name": "Mexican stock exchange"}, "business_day_convention": "Following"}, "day_count": "Actual360", "face_value": 100.0, "issue_date": "2008-01-31", "maturity_date": "2047-09-26", "settlement_days": 1, "coupon_frequency": "31D", "main_sequence_asset_id": 119564, "business_day_convention": "Following", "floating_rate_index_name": "TIIE_28"}, "instrument_type": "FloatingRateBond"}, "pricing_details_date": "2025-08-27 00:00:00+00:00"}</v>
       </c>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
         <v>13</v>
       </c>
@@ -24534,8 +24776,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D30" t="str" cm="1">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D30" t="str">
         <f t="array" ref="D30:F160">_xll.MS.GET_DATA_NODE(D6,D7,D8)</f>
         <v>time_index</v>
       </c>
@@ -24546,7 +24788,7 @@
         <v>curve</v>
       </c>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D31" t="str">
         <v>2025-06-30T04:15:30Z</v>
       </c>
@@ -24556,7 +24798,7 @@
       <c r="F31" t="str">
         <v>H4sIAAe6B2kC/02OQQoDMQwD/5JzKLLkOFa/Vvr3LptCq5sYRug1hPHEA8ntX5hzOA7IwF88h2rdRPYuFi0BxT3H/o6pw6sIERW1OEc0j5QhNFZ1JtJi3XtHWzSbV4vFhq4PAR8WwXJvKyil6/0BtVJFW7kAAAA=</v>
       </c>
-      <c r="H31" t="str" cm="1">
+      <c r="H31" t="str">
         <f t="array" ref="H31:I38">_xll.MS.DECOMPRESS_CURVE(F31)</f>
         <v>days_to_maturity</v>
       </c>
@@ -24564,7 +24806,7 @@
         <v>rate</v>
       </c>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D32" t="str">
         <v>2025-07-01T00:00:00Z</v>
       </c>
@@ -24581,7 +24823,7 @@
         <v>4.2799999999999241E-2</v>
       </c>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D33" t="str">
         <v>2025-07-01T04:15:30Z</v>
       </c>
@@ -24598,7 +24840,7 @@
         <v>4.4100000000000091E-2</v>
       </c>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D34" t="str">
         <v>2025-07-02T00:00:00Z</v>
       </c>
@@ -24615,7 +24857,7 @@
         <v>3.9976262933006268E-2</v>
       </c>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D35" t="str">
         <v>2025-07-02T04:15:30Z</v>
       </c>
@@ -24632,7 +24874,7 @@
         <v>3.8195620320616519E-2</v>
       </c>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D36" t="str">
         <v>2025-07-03T00:00:00Z</v>
       </c>
@@ -24649,7 +24891,7 @@
         <v>4.1308056844049326E-2</v>
       </c>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D37" t="str">
         <v>2025-07-03T04:15:30Z</v>
       </c>
@@ -24666,7 +24908,7 @@
         <v>5.2928265015280342E-2</v>
       </c>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D38" t="str">
         <v>2025-07-04T00:00:00Z</v>
       </c>
@@ -24683,7 +24925,7 @@
         <v>0.1126987931233496</v>
       </c>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D39" t="str">
         <v>2025-07-05T00:00:00Z</v>
       </c>
@@ -24694,7 +24936,7 @@
         <v>H4sIAOW5B2kC/0VRuXEEMQzrRfGOhj/Ba83j3g3uBVagAMJH6ufo+cyV/+Mi9Ryz88FFzLjBNdTR/RzkwqEzmIKFIIts7VrcRoEOx9Cn9Tluvu46RttKpI8tnFi6B2l0tpawxnMqbemtSa43ChBnakGWnzkzPRKJqkjiE+ejcqVhmRLeVr3tlXFv0WlLpW4DYvGeV1E15k7fCc2hlVrp+9IB69rszH41vW3nIicquiKGitmHZl3VCwXts7in8u863hi9XJ4SAV4ptxrrpX5NolQ4ugfzaGYs8kp6P8C5Q2nGG4f0oZnlZYp38ZrJtO+UygZVt1TpZBb8AMHvHy7jJbbVAQAA</v>
       </c>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D40" t="str">
         <v>2025-07-07T00:00:00Z</v>
       </c>
@@ -24705,7 +24947,7 @@
         <v>H4sIAOW5B2kC/0WPSY4YMQwD/+JzoyGKWudrwfw9dOcQHym5VPxzcH763f+vIuM5Hjee2EYMLZjDfc70+ZnXxswWxfXu4HPQdnOtOhgz6bv9HHp+cUdtB8Yy/VKYvDlTGPTsRKVpPxf/cpCTnY6gS6b645SoK3gvh/TnND6dMWrTgQhs5XO29tpXpRYFV6llSdNGB/ZlNWVfjZKwPsDN7iATxoV7I5F3IPHvh2Pcb2Es86IaQsFeC9AQ6yanwTeZbyJ507cKW+sVTN0FA1747OaUVVe2iviM7oOvkdHrWeUc150S9Px4vznTadD9Ms7cMp5SiH7dacysYI3t718nBQoO0wEAAA==</v>
       </c>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D41" t="str">
         <v>2025-07-07T04:15:30Z</v>
       </c>
@@ -24716,7 +24958,7 @@
         <v>H4sIAAe6B2kC/0WNSQ4DQQwC/+JzK4K28ZKvRfl7RuksXIuChznsjhvCC79wa9nwgOD8U7XMU4dwwzMxORr1XlbfMZAcqUtEB5ex90dyd2Rkh0cR+Z47luSqypmrIOB6IuYwshtN+LSQmf18Ad1+50S5AAAA</v>
       </c>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D42" t="str">
         <v>2025-07-08T00:00:00Z</v>
       </c>
@@ -24727,7 +24969,7 @@
         <v>H4sIAOW5B2kC/0WRO3IAMQhD7+J6xwOI714tk7tHbBMXLiSQH/jn6Hnrzv9JD3+O9coZlVkwg7s4njNfdYWmhjrgNd3P0bbV29kvbebWsHwOQr70DhGNYrhhZvU6b18EulgdDTXT50TK6swXZIendQxzSj4dJjwp4WHKmFrKJnyETFf5uILlg9U9L/vInvAIwqt8OJEXTQGqBABzVHPOmzU02oQawWbnyszzejGJtaU2Im5e67SsY7dcJloneK/RChroK6lKOcGF9K4UGwbETfYENLJJurt2Pm/FwTP5JOfR4PWchHBRanHHfLE6xXs3ohxsh+FnqDSZHErG3z9DiId40AEAAA==</v>
       </c>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D43" t="str">
         <v>2025-07-08T04:15:30Z</v>
       </c>
@@ -24738,7 +24980,7 @@
         <v>H4sIAAe6B2kC/03MSw5CQQhE0b0w7hgKKD5uzbh3O7YvT4ac1H2Jqzz1oeGc+8yXDA4E/qBqiSePgNAKpjWUnUvqiik0zXyapjQuQdtv5LUxyNSxpse3d2b7ydyp7KrwyG3QOQhM7WmOaXsQ8/4ApFMOe7sAAAA=</v>
       </c>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D44" t="str">
         <v>2025-07-09T04:15:30Z</v>
       </c>
@@ -24749,7 +24991,7 @@
         <v>H4sIAAe6B2kC/02MSwrDUAwD7+L1o1iWv71a6d2b5AVSMbth9BGqvPWlzphnxiWDLRx/omoJM7YBFIR1anrySOo+42QbowcNc/claLsj69CDNDLNNK6/nYVzSgs+k6VxOuhsCWR0NfPEKur7A+lg4NS7AAAA</v>
       </c>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D45" t="str">
         <v>2025-07-10T00:00:00Z</v>
       </c>
@@ -24760,7 +25002,7 @@
         <v>H4sIAOW5B2kC/z1RS24FMQy6S9ajkf/gd7Xq3b12KjW7YIKB/Bw9H7wp/0cV9hzzhYNRUVYQyVbkc5gX98jsKMCFOnRF/fFHwOEotFiNTF88adFK8xak+3Pm/cU7RZupZuoRz4nu8+ErSSFGySwJPqf68rk+h8kuUvAciF2+MMdnlkighk9g+Q0PLzGBp87a5pWPDh+PIlVdNTLq5A4aNVYkZ23XxiqZvf1GtYcqtRDJ3Lxpd2AxhhAyntS3N9XaAadGpbRMbdw6V0hlnbbRzBgXxy5WncTNaHQ5rUonscUImb1Q0dRpWzJkPc11UqS/BZ2+oPM/U+T3F2WaumXLAQAA</v>
       </c>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D46" t="str">
         <v>2025-07-10T04:15:30Z</v>
       </c>
@@ -24771,7 +25013,7 @@
         <v>H4sIAAe6B2kC/03MWwoDQQhE0b30dxMsLV+ztZC9R9IDGT/rcnwvk3XJS2je/1Pbq3EC8QiZe1n4KYDAoBUSDBuS9zPrKDWvRkFJ7oXSG2kny5JJd1X9vTvKZ7FUEQwZ6sOkTwS8Zg5hE2zLzxerABUfugAAAA==</v>
       </c>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D47" t="str">
         <v>2025-07-11T04:15:30Z</v>
       </c>
@@ -24782,7 +25024,7 @@
         <v>H4sIAAe6B2kC/02NQQ4CMQwD/9LzCtlx3CZ8DfF3KipW+Dqa8WsI44kHUgv3GL5G84Ak/tbX0PQhFKZmdLtUnnmN9auBRHBKpfYGrPD9E9XJhhArv7kjeWfQoLcpa20LfRgDtapMu8NGvj90QTJSuQAAAA==</v>
       </c>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D48" t="str">
         <v>2025-07-14T04:15:30Z</v>
       </c>
@@ -24793,7 +25035,7 @@
         <v>H4sIAAe6B2kC/0WNSQ4CQQwD/5JzC8VZ23wN8Xcimhms3Cplv8RVnvrQ8NY7sFxCHBDgP91LvPIQmHqVspjMbUv6KlMAzNyd0B1Ygm0/ybNpFbQMbrVv3bHmP4rgzAerOZbyMBgyZgnwUM69P3dQiz+5AAAA</v>
       </c>
     </row>
-    <row r="49" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D49" t="str">
         <v>2025-07-15T04:15:30Z</v>
       </c>
@@ -24804,7 +25046,7 @@
         <v>H4sIAAe6B2kC/03NSw5CMQxD0b1kXKF87YStobd3CgVBpkfXeUio3PWmGTW/81gydiDtD8glgTpisDBXeE1YAEv4XVPsjmmKyugt1v6pMr2NHO8kGe+9UxUmdb+ocO18RTqHzH0A9jipVajrCWDVzWG5AAAA</v>
       </c>
     </row>
-    <row r="50" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D50" t="str">
         <v>2025-07-16T04:15:30Z</v>
       </c>
@@ -24815,7 +25057,7 @@
         <v>H4sIAAe6B2kC/02OQQ4DMQgD/5JzVNkYCPRr1f69abNS64MPjMbiNYTxxAOu6F9MczQPcOIvPYcyDqHBgWVlQpJzrHtMXZ2yWhmei4w5WHZb2oflAoUKKb+Dx4vcX8RuUu7lvj30gbSPWEjzBMN0vQGRdyyWvAAAAA==</v>
       </c>
     </row>
-    <row r="51" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D51" t="str">
         <v>2025-07-17T04:15:30Z</v>
       </c>
@@ -24826,7 +25068,7 @@
         <v>H4sIAAe6B2kC/02NSw7CUAwD75L1E4rjfLka6t0pfUXg7WjGL6HKUx/qjPnNuGSwgUP/NkuYsQlcuyyciGFNLqlvTQ1p9EpvB8uXoO3WOF6AVXSE4uptK9LHYs4XotPmY+lsCGNon7AYTVMcb5tpxl27AAAA</v>
       </c>
     </row>
-    <row r="52" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D52" t="str">
         <v>2025-07-18T04:15:30Z</v>
       </c>
@@ -24837,7 +25079,7 @@
         <v>H4sIAAe6B2kC/02NMQ4DQQgD/7L1KcILGJyvRfl7UPaKc4dGM3yW23rby8JDj+FawgFhjwXiWs48CHu8dJpcfa26W3OIkwPA7gHofRvu3pSJWfKsf+tIScsqKMpAMMcyHYbtAQvtJoPz6/sDXnzfbrcAAAA=</v>
       </c>
     </row>
-    <row r="53" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D53" t="str">
         <v>2025-07-21T04:15:30Z</v>
       </c>
@@ -24848,7 +25090,7 @@
         <v>H4sIAAe6B2kC/02NMQ4DQQgD/0K9ijBgFvK16P4ekr3iXDIe8xFXeetLw6MfwZLGAQF9pJd48hCdoiPVlJVlS/Y95s2dc98gkzkEZbdk27GzwhLGxH/uWCRmMyI6QO+fpX0YTGNeVDdRPvj6AvP8sKe5AAAA</v>
       </c>
     </row>
-    <row r="54" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D54" t="str">
         <v>2025-07-22T04:15:30Z</v>
       </c>
@@ -24859,7 +25101,7 @@
         <v>H4sIAAe6B2kC/02MSQ4CQQwD/5JzCzlxVr6G+Ds99Ajho8vllxDyxAPOwi9qsWT0AFf8ZZYw4xD05DS8tDi+pO4vDtPGylMNLG6kbbdkzEEQ1yTp8f07XniyIzvLurP78jAHqvZW1Zy6G/V8fwDpWSrguwAAAA==</v>
       </c>
     </row>
-    <row r="55" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D55" t="str">
         <v>2025-07-23T04:15:30Z</v>
       </c>
@@ -24870,7 +25112,7 @@
         <v>H4sIAAe6B2kC/02NSw5CQRAC7zLrFwP0b9qrGe9ux3kxsmBDqngtw3riAbfCL1Rcq3kGJ/7S17KMs1BwoLRlSPJadcusd6dpV4ZnkWPj1k0ZGqoyJZUeX9/BIqyd0aqBpodCn22uqmSq+UoI8f4AiwAl/7oAAAA=</v>
       </c>
     </row>
-    <row r="56" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D56" t="str">
         <v>2025-07-24T04:15:30Z</v>
       </c>
@@ -24881,7 +25123,7 @@
         <v>H4sIAAe6B2kC/0WOSQ4CMRAD/5JzhOx2euNriL8TEWbwtVQlv4YwnnhgKXGP5nM0D1js/zLnUPghXChlyq3bWdvJqwZjIKxrM9LmYNnPkm9D0goK7G/vWO61LArJRKp3j+jDaKjeT9yjPYPx/gDaDLVsugAAAA==</v>
       </c>
     </row>
-    <row r="57" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D57" t="str">
         <v>2025-07-25T04:15:30Z</v>
       </c>
@@ -24892,7 +25134,7 @@
         <v>H4sIAAe6B2kC/0WOSQ4CQQwD/5JzC9nZw9cQf6dFM4MPPqRUVl5ikCcecCvcocaS4QHO+adqiWUcQkOC0YBmF31JXWtQ1tSg07h7CVt/limYuU3UHjT7Dh4twnK89t0znPsJYg4ju9WoGnRPnXh/ANp8Cea7AAAA</v>
       </c>
     </row>
-    <row r="58" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D58" t="str">
         <v>2025-07-28T04:15:30Z</v>
       </c>
@@ -24903,7 +25145,7 @@
         <v>H4sIAAe6B2kC/02Nyw1DQQgDe+G8igzGC6S1KL3ns4n0fB3N+GGE3XFDci6LWDZ+QOKy9FzGrYOc2OUIqKOUe1n9cwhvRuwpasBl3vGzyNC0KE5J/e0dSyrgo3Rwj95XjjnMw1Fd6T2S0M8XV7gTKroAAAA=</v>
       </c>
     </row>
-    <row r="59" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D59" t="str">
         <v>2025-07-29T04:15:30Z</v>
       </c>
@@ -24914,7 +25156,7 @@
         <v>H4sIAAe6B2kC/03Muw3DMBRD0V1UGwHJ989qQXaPArkw24vDzzKsN15wm8ekaw1PcDzm9GtZxkkkBFhZQGN1rbrfbLKVU1l/YdqIrVspYWoqxeqMc3hcuKtg2bkPpxDbYU4kE4gEYdux+/sDwVlgP70AAAA=</v>
       </c>
     </row>
-    <row r="60" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D60" t="str">
         <v>2025-07-30T04:15:30Z</v>
       </c>
@@ -24925,7 +25167,7 @@
         <v>H4sIAAe6B2kC/2WOQRJCMQhD78K64xASSvFqjne336ob2b7khYfR7e43l+C/Q+Swxj9w72GceQgmqHIVvJkaVl+ZJyfDV0SnumsYVnxaJKAsNBUo6C08vSu7Mqorp6C9tc2HYUfX9YyoSfbzBWwgfn26AAAA</v>
       </c>
     </row>
-    <row r="61" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D61" t="str">
         <v>2025-07-31T04:15:30Z</v>
       </c>
@@ -24936,7 +25178,7 @@
         <v>H4sIAAe6B2kC/02MSQ7CQBDE/jLnEarq6pWvofydiASEr5b9WsJ64gH3wQ+a9hregvhj9lLGZejosnAxRjW5V31vCAc7rDM0vRfb7kiiDFlWbjXMz++qwtsqs1020ZCfHeaSZImdXqFEne3xBgfe1Li7AAAA</v>
       </c>
     </row>
-    <row r="62" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D62" t="str">
         <v>2025-08-01T00:00:00Z</v>
       </c>
@@ -24947,7 +25189,7 @@
         <v>H4sIAOW5B2kC/0VQx20EMRDrZd8HgRM44Voz3LupswHrJ1Ji+nrseRsO/o+x4vW4/+HMXngusTGvZ/i898xEFpJkcKZej9V+cA4qB/TMnH09EX3xzRpjhqW1pWQi81e/OiRVXawSTv7iO0yvnW12jIhCiKjcI/EJhWn5yLmmPz9MHmkLBGKFN+Z5ZziPERWe3dNNRQXF+GyeCLpuqngrxEC425xd6EOqmXqLocnc4XFW6jXK2w0X01fLOu1MLaN3k/AWM3uXLdujiUJtYObbd9m62wbjdKk/tUn2aPNA4XYBTrteaxvIQT5Fu21KC0POi7Fq+6SGVlW4jcPqGXWMQPr3DxwWtVHaAQAA</v>
       </c>
     </row>
-    <row r="63" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D63" t="str">
         <v>2025-08-01T04:15:30Z</v>
       </c>
@@ -24958,7 +25200,7 @@
         <v>H4sIAAe6B2kC/0XMQRLDMAhD0bt47elICAz0ap3cvWmcSdk+vj5DGG+84N54jqY5mhsUf8APtOISNaIQK8FSlc2R95iyGg5mpySuOVi2IyeK6HS3jl55ze0qrMBIU1hUimeF3kZ60uz8MJPC+/gC+HsvSLkAAAA=</v>
       </c>
     </row>
-    <row r="64" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D64" t="str">
         <v>2025-08-04T00:00:00Z</v>
       </c>
@@ -24969,7 +25211,7 @@
         <v>H4sIAOW5B2kC/0WQS5IkMQhD75LrCgeIn6irdfTdR85ZtJcSPCH/PP5899jfC7P+PMDz5WEE0DmNCbZk9pVHUzWYZiy2Po/PXL1yd72QhS6PzxNu/+djiTVOr2OkF995gSy3vEEUP0/zvWY2txWrmChhxvbFXPzQ0ts7r454vm7Hyys9fZ21l+9WeJ2KGRuDK0es1xHL0XEycqGlzqvrvLsRc4RZtCe6B7cbVW5S+WB0GNJYKYPm18BRM6/oUk7zNXgNOxZOHV2z1FXIS9JJZ8ma1L9y22XsKDzLTu6UBbTLGf13J4SC8XgykkVasd4ikX6b7AnBVMvctYfff2pQgLrTAQAA</v>
       </c>
     </row>
-    <row r="65" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D65" t="str">
         <v>2025-08-04T04:15:30Z</v>
       </c>
@@ -24980,7 +25222,7 @@
         <v>H4sIAAe6B2kC/0WMSQ7DQAzD/uLzoLAtL3K+VvTvHWQCRFeK/ApULv1oRM87tyVjByD1nWMJKm8CZrRmDzLcikv6iaE5Ezqk9SazxOhHCiVm39lOsuzOHSu9Chw03Azh29I5zCy8rRNguavO7w94kiUFuQAAAA==</v>
       </c>
     </row>
-    <row r="66" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D66" t="str">
         <v>2025-08-05T00:00:00Z</v>
       </c>
@@ -24991,7 +25233,7 @@
         <v>H4sIAOW5B2kC/0WQQW7FQAhD75J1FGHABv7Vqt69TFqpszTDs/HXheszj/2/MNN9eV+ffugzRTFiZLyvwVGzICo1JVP5faF4dO+hWVeKXRH3Fe4HDlYpTGo6Z+HBOv+jFdlR7bZ63pf4htEkkZZtjGKvXvOmmay1FTOptdXE9YE9xpJAAX1wm8f8dyEOIsEZxwHBqt8V0ZizmjfUaw2X7QQPbEWGZqKCeI+rk2q2gwyfZlYdVhXejb2txY3aCxXfSb+Trl73DeGxDayL52EhtpIR0nNcaXYmk/ZHa1kJmo7m0hSzNOeDTR8GgJY4NcICG0F6rDBbZdWEcb5/AMJs+gPVAQAA</v>
       </c>
     </row>
-    <row r="67" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D67" t="str">
         <v>2025-08-05T04:15:30Z</v>
       </c>
@@ -25002,7 +25244,7 @@
         <v>H4sIAAe6B2kC/0WNwQ0CQQwDe8l7hZw4cTa0huid0y0Cf8djv4ywJx7IHPziwWXjB5Dzj3oZVTfhlKaq1Nxi72X9HeMOJII5HFRHLfMdx0qHak+2Xy8l3ntHq1A4EC5BTOjSMAde7Zku9CSjhXp/AP4XydW7AAAA</v>
       </c>
     </row>
-    <row r="68" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D68" t="str">
         <v>2025-08-06T04:15:30Z</v>
       </c>
@@ -25013,7 +25255,7 @@
         <v>H4sIAAe6B2kC/0XMSwrDQAwD0LvMOhTZ8jdXK7l73UwgWhjDQ/ouYp34wCz7jcqxWjZQ8YYDDL+FPV9qKSHzjeQzxqxyK4ZBW8OPJaW7ZIJBtsKrQd5zu+UanGMVhSjNfw29UcTKxpmcRYu4fizDtMC6AAAA</v>
       </c>
     </row>
-    <row r="69" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D69" t="str">
         <v>2025-08-07T00:00:00Z</v>
       </c>
@@ -25024,7 +25266,7 @@
         <v>H4sIAOW5B2kC/0VQOXIEIAz7CzXDWL69X8vk7xFsEehsWdfPwvrUmf+XHr6X2h37OLQyRqA22KtzffqIzvQopNCSuRdy7hwWVVaFqDStvUz9zUnZkUa8aBBvoXduJnyo5OfRXhT6zi1GHUJcTe+V9XgSQXxCulOa/IXnpybMW8uy4YRP9nWf6TkRQ24PIT0PyT/HIkg019NYMy0wcxfhgvAaTVHpeMHyXTitmMDVmYASYJT1gRwxUaKqmKO+i3oLmIsxLetzu4VeJuBQi+QBAdu5GtpFcdhBGHrSUsBWlbHNyKUsnKYCbulM/oJoUN7rtDDssBQFzH7/AE5mPR7PAQAA</v>
       </c>
     </row>
-    <row r="70" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D70" t="str">
         <v>2025-08-07T04:15:30Z</v>
       </c>
@@ -25035,7 +25277,7 @@
         <v>H4sIAAe6B2kC/0WMQQ4CMQzE/tJzhTIzSZrwNbR/p2wR+GrZryEbT3uYe9sPUHM0jhD/woQ5lHEbdSwjTSyoLOdY35mKu/MmIoo1B4qncQi00FJujPftRMGVWNtx4ZPuH6yPBDyjO5PycHRfb/LLjzi5AAAA</v>
       </c>
     </row>
-    <row r="71" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D71" t="str">
         <v>2025-08-08T00:00:00Z</v>
       </c>
@@ -25046,7 +25288,7 @@
         <v>H4sIAOW5B2kC/zWQS27FMAwD75L1g6G/yHe1oncvHaDJKqN4RPPn8ee7Z4v/D+D5eWJfbBMoH2fOXkx7cQJmYDpjMj6P47XoV0JvExnJz5PFy9kdjR3KhirxnueLY1UeKznSU7ibF1dLC1pzfWUZvjjLzGIx7VSCz7M3JM5AXx13mlfOFJ7D6swVxRi3FdLq9bAxyrdeyczRwAfPl0cZVnsRBeM1+UzfE0Ck1epM29LvYHlPYOGBDWkYO28RcQdcIBtqbWvt9plX5XYmMozhm3LtnaC03eO0DIZaladEkk2aaoo56plwJatux11j4QpQfcrFmdRlfGt+/wDKt6iH0AEAAA==</v>
       </c>
     </row>
-    <row r="72" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D72" t="str">
         <v>2025-08-08T04:15:30Z</v>
       </c>
@@ -25057,7 +25299,7 @@
         <v>H4sIAAe6B2kC/0WOSQ4CQQwD/9LnEYoTZzFfQ/ydhkYaX0tV8muFrac9jGzdc1xLOCDc7sUGUfkjoWpnF5NIoa/V/1hMhQ8znTKYeC2MH4sQnIN279J82Q4eLyOyGmqfHlltzXQYUBSmLPdRm9H7A+quYBe7AAAA</v>
       </c>
     </row>
-    <row r="73" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D73" t="str">
         <v>2025-08-09T00:00:00Z</v>
       </c>
@@ -25068,7 +25310,7 @@
         <v>H4sIAOW5B2kC/zWQy20EMQxDe/F5YIj6a1sLtvdQE8THR4uk9HNwPnXL5/91w56jvjhmLFLKkYaq53QtTnePaD5E4DmofnGrc1htXAX9HNNYPoquFDGqKcs939DomER5ICPpHkqfvlZjU6Wjk7mpmS+H8Kl1eEqEkk8uT7QoYXWOBv+PvDyklBnNBZDj7MlWK7RJlRdEO8K4LWBcbK5YjCqZAzorpPkKbIS1ExSXegWn1WjajUjwDrHXeG/Bi3YUbrUgK3JMGK62Vhkut70ZIZbWwxFtMD0cc41WbCDeO5Ksfz7qprdbx70KzkZ/mzAfPn09V/LmxRzfX2o+kOLRAQAA</v>
       </c>
     </row>
-    <row r="74" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D74" t="str">
         <v>2025-08-10T00:00:00Z</v>
       </c>
@@ -25079,7 +25321,7 @@
         <v>H4sIAOW5B2kC/z2QS27EMAxD7+J1EFB/aa5W9O6lPEC1yOIpJkX+HDmfegP/I1L6HNUvDvXiuHnAn9O+2K1UyhtQTavnSMXlFdGt8NGsbKrM5REygnRXH2nKmF+dGE5HuILq5D59Pv3CetzUohMIe07O/b+pitLmhShIPIffXUyNUMk7qAbyrrw8dTCNDoeuwfQ18ObdMCao4gkMYF27mMwwoBFtVXSWBK2HTZBVSBdm5CaW5c6XdE9x9pR0UJHYRdOwmB/CC1ZJ7au0kVW8RsM3gtZai7wIQTU7KsnCplanlOqbMxsapjFbnzA7c4S/Qcz3PgnW9fsHHAMg4c4BAAA=</v>
       </c>
     </row>
-    <row r="75" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D75" t="str">
         <v>2025-08-11T04:15:30Z</v>
       </c>
@@ -25090,7 +25332,7 @@
         <v>H4sIAAe6B2kC/0WNSQoDQQwD/9LnIViWFzlfC/l7munA6CYKlT6Ltt72soiyJ1nXGhxAzpPqa7HyJtwNghk1ZF6r/y6q6IkcsGU1Wwb5GQVaGvcyhdRz684sycYWekYgfD/B5jAgJcUELRUJfH8dti+8uQAAAA==</v>
       </c>
     </row>
-    <row r="76" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D76" t="str">
         <v>2025-08-12T04:15:30Z</v>
       </c>
@@ -25101,7 +25343,7 @@
         <v>H4sIAAe6B2kC/02MQQoDMQwD/5JzKJZlO3K/Vvr3hs3CVifBMPMZtPG2l0Wwn7nP0TiA/gdaMQcrL8Tej70qK0XrOdZdo9yW0KlkhGxLkB8rIKuStRctV+cVPF5yebqchSBhm8H6QEAIgEKqd6C+P6T1ELO9AAAA</v>
       </c>
     </row>
-    <row r="77" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D77" t="str">
         <v>2025-08-13T04:15:30Z</v>
       </c>
@@ -25112,7 +25354,7 @@
         <v>H4sIAAe6B2kC/0WOSQoDQQwD/9LnIdiWFylfC/l7munA6FpUoc+Crbe9LBN6FnEt+QEhewZeC103AVVDK7KRQOa15l/D9DDaJfcabckZx0o3irarEWYVeQePVqGZFgl3ZrK3ZzpwhxgZ3fL9iYXvD9ayMGG8AAAA</v>
       </c>
     </row>
-    <row r="78" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D78" t="str">
         <v>2025-08-14T04:15:30Z</v>
       </c>
@@ -25123,7 +25365,7 @@
         <v>H4sIAAe6B2kC/02NSwpCQRAD7zLrQTqd/sWriXf36QiaVaCo5LFo6243i2j94thLOID2n9qLlR9CRU2RU3M1Re7V3zVOOApNdlg6Yy+MHy1QnXAVWPKZs3i85KUIqrquQm8G04HAIL0BubJC/nwBUyWesr0AAAA=</v>
       </c>
     </row>
-    <row r="79" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D79" t="str">
         <v>2025-08-15T04:15:30Z</v>
       </c>
@@ -25134,7 +25376,7 @@
         <v>H4sIAAe6B2kC/02MSQ4CMAzE/tJzhZJJJgtfQ/ydqEUCXy37tUzWUx7inv0DulfrFSb/xF4WPMY60tTR8EQw98rvzIrgYGxp+sy0cCPHdG1ZkKQoeX43o1tKVFl1qLMnm/w4hUgpDGBpFuP9AW2aPru6AAAA</v>
       </c>
     </row>
-    <row r="80" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D80" t="str">
         <v>2025-08-18T04:15:30Z</v>
       </c>
@@ -25145,7 +25387,7 @@
         <v>H4sIAAe6B2kC/02MQQpCQQxD7zLrj7Rp2mm8mnh3yx9Bswq8vLxW2Hraw8jSL911LfkhAf0jXisqbxSqDZ/BFLT2SPv7F71pgfJKTbOxvHE0wjOLuYXoKN2HR0smfKeczQKVo5kOdDhs5giwcr7fH1pKPAW+AAAA</v>
       </c>
     </row>
-    <row r="81" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D81" t="str">
         <v>2025-08-19T04:15:30Z</v>
       </c>
@@ -25156,7 +25398,7 @@
         <v>H4sIAAe6B2kC/02NQQpCQQxD7zLrjyRN22m9mnh3yx9Bs3rwSPJawnriAffEL5HXah4h/GeEMm6j9qyUKmuoPa61v2uqsDbDiAGva7HstJy5qVAZIwfiHjy1UMPQe7vSG6OIPo5sK4HzRd8Ivj9iu0rFuwAAAA==</v>
       </c>
     </row>
-    <row r="82" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D82" t="str">
         <v>2025-08-20T04:15:30Z</v>
       </c>
@@ -25167,7 +25409,7 @@
         <v>H4sIAAe6B2kC/02MSwpCQRAD7zLrQbo76U+8mry7+3BELLIrKq8FW097GJn2w4N7yY+A/VN7ofJjIFRhRJ97rr36e4ZhgKS6J8Yj9/KJU9Ezo4TIRoTO38kSTQVFSVk+fWemI91nbGQREKPR1xv/gwlnuwAAAA==</v>
       </c>
     </row>
-    <row r="83" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D83" t="str">
         <v>2025-08-21T04:15:30Z</v>
       </c>
@@ -25178,7 +25420,7 @@
         <v>H4sIAAe6B2kC/0XOyw0DQQgD0F44jyLA5pfWovSe0c5qw/XJxh+ByltfSo4+Z44lYwfgf1DYEmRcgukq1e60HqCX1F2GnnCLTG2N4hJrPxm6MVFOVAQ8r7YTCoLYr7erM/YC0zlmewLRzIzC0Of7A8BOT924AAAA</v>
       </c>
     </row>
-    <row r="84" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D84" t="str">
         <v>2025-08-22T04:15:30Z</v>
       </c>
@@ -25189,7 +25431,7 @@
         <v>H4sIAAe6B2kC/0WNSQoDQQwD/9LnIciWN+VrIX9PMx0YnWSKkj+LWG+8EFF6MlPXkh3ijSfGuBYrb0ShUAOy1bnrtfq/x+4Jd9VklmlLNn6sgMojtR9yHH7vHStJl6OtFWk224IO21dbwkRlF/T9AZdJT1C7AAAA</v>
       </c>
     </row>
-    <row r="85" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D85" t="str">
         <v>2025-08-25T04:15:30Z</v>
       </c>
@@ -25200,7 +25442,7 @@
         <v>H4sIAAe6B2kC/0XNyw0CQQwD0F7mPEJx/qY1RO8EZrXk+mzntUzWUx7iHnIf1PciDij/INZ7WcZPjEhVZ2jAhvaqa8zawCxE04U5gtZTcrg5GSgYLb+PZu/UwoKlGjJhjdHpCQ8CzXJ0ehd6Uu8PXtzsRrsAAAA=</v>
       </c>
     </row>
-    <row r="86" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D86" t="str">
         <v>2025-08-26T04:15:30Z</v>
       </c>
@@ -25211,7 +25453,7 @@
         <v>H4sIAAe6B2kC/0WOSQoDQQwD/9LnJsiWvOVrIX/PMB0YXYsq9FnEeuMFyfEsaq+xA7zmWdtezLgJuyPGwbJQTexV/xgLTEzGJIJ7WftRhM6CVRVUKtddO1KQKZUJdKr90jCH2fVNrQQ1LRt+f60jbz24AAAA</v>
       </c>
     </row>
-    <row r="87" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D87" t="str">
         <v>2025-08-27T04:15:30Z</v>
       </c>
@@ -25222,7 +25464,7 @@
         <v>H4sIAAe6B2kC/0WNSQ4DQQgD/9LnVsRmA/laNH8PmY40PlJ28Vku6y0viTB5gtyr9QBDPwH3cuImXoQpp4B0R++Vf5mzDKGcaQRZM9K5HJ9ozAerknZk3b4zg6smAQqj9CdU6cPUdFgKK+jlEdcXpFh1jboAAAA=</v>
       </c>
     </row>
-    <row r="88" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D88" t="str">
         <v>2025-08-28T04:15:30Z</v>
       </c>
@@ -25233,7 +25475,7 @@
         <v>H4sIAAe6B2kC/0WNXQoDQQiD7+LzUIwaf3q1snfvdKeweTDgR5KPuMpbXxph+oi1ZHCAcR4xl3jyJt7NZFkXoMzcqP5tXgjP6f2v7bYEbScVCivaJJypirvvpGiVNch9dIK/LegcCEwEOqwaVOD6AmQkJgm6AAAA</v>
       </c>
     </row>
-    <row r="89" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D89" t="str">
         <v>2025-08-29T04:15:30Z</v>
       </c>
@@ -25244,7 +25486,7 @@
         <v>H4sIAAe6B2kC/0WNxw3DQBADe7n3weAGbnBrhnv3QifIfDIMP8uw3njBXfBIlHu1nEC1/wrby4JXYhU0sSwDlfC98oZZlLIqvMokpIcm4xze4LOQnBNQ2i/g2VF72l0p0AHkzNAnE50q0GOIF1nfH3HoKGW7AAAA</v>
       </c>
     </row>
-    <row r="90" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D90" t="str">
         <v>2025-09-01T00:00:00Z</v>
       </c>
@@ -25255,7 +25497,7 @@
         <v>H4sIAOW5B2kC/0VQS3IFQQi6y6ynuhTFz7taKncPnSziEhSBr8efj9ux/3FWvA/m+ezZpiONa/AZvs/6hYfwHLNmY1qwDy7eubvITASz8T6R8SePzmBxkJJZEZW/+tCBnqB28wqRfwdbEghdpSH7fcr0wCv6eLJsXUa1XlO/686r462F8fT3aevnIx97EL5DggnhbhSBLRzuTHcHmSUiekWg7cgkYbk9lmrCVYEYaz/WZdVhnBoRfbW8BwejjpQjwNpbx9q1yzpTNozJrE0VAtQtXMBRU5Y0W31SIRK4URCnZrsRO4G40ek3y9ihqY/0qa3B9Sx/+hNmSlmURCHL8/sHW7cJ3NYBAAA=</v>
       </c>
     </row>
-    <row r="91" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D91" t="str">
         <v>2025-09-02T04:15:30Z</v>
       </c>
@@ -25266,7 +25508,7 @@
         <v>H4sIAAe6B2kC/03OQQoDQQhE0bv0egilVrWaq4W5eySdxbiThx8/K7DeeIHRj3G/VtsBe0KC14qtH0VJ1uawCrFG8l+LVDbDJNKpfS0rP0dEeuVsuyWUnd45UyR6isAeGDH0IXNG0qc1D1Ge9xf8d4lvugAAAA==</v>
       </c>
     </row>
-    <row r="92" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D92" t="str">
         <v>2025-09-03T04:15:30Z</v>
       </c>
@@ -25277,7 +25519,7 @@
         <v>H4sIAAe6B2kC/02OSQoDQQwD/+JzEyzLa74W8vc00wMTHVVo+QhV3vpSp8+fsGRwAFof0X0JMy7E3jSDXZ6VnFhSdx1LA+UdNaMD5BK0nZgr2KiG2vaacTWeXFhVKiwxY4x9AzqHwbT2Rw8jck/O9wdQZS++vQAAAA==</v>
       </c>
     </row>
-    <row r="93" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D93" t="str">
         <v>2025-09-04T00:00:00Z</v>
       </c>
@@ -25288,7 +25530,7 @@
         <v>H4sIAOW5B2kC/0WQQW4FMQhD7zLrrwgMGPhXq3r3OrNpFiPFJm9sfh5/vnvs/4QZPw8kzxlwnMhZ58R8nqkrNzY51pMBH8nevHrFmm8Uk27ozxO2V2dEN5yxtVOaj+p3vhAsT+G6qz6PoDdNN8uqIifbSmna5uVwdzkdkH35DTxft+ORlSJ7wyKhQFb+OoXMFYiV5h2vI5Yj9kwof4OUI5hj9r7xPky9C/Ma4q036teRJ2sLw43tvbAxBW5oJUrKkmEgXqOvUWeRWoWubnv3mhel8If6JFhiY2Us9fdMP+PB1DjqNmFCJFge2zUutBxVzdsk0m4VnqH7evgqmtfvHzr2XtvVAQAA</v>
       </c>
     </row>
-    <row r="94" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D94" t="str">
         <v>2025-09-04T04:15:30Z</v>
       </c>
@@ -25299,7 +25541,7 @@
         <v>H4sIAAe6B2kC/02NQQ7DQAgD/7LnqMJmYXG/VuXvJZuoqi8cxmM+w2287WXT3X4B8xjCDZD2F8UxPGMjX5rdVYUv07yk9cx5lovMyRlc4cdA8bGUseBWTCKo3IO3FpBY/bKPUNUM/XJDoBTFy+5KuM4vhDCeHb0AAAA=</v>
       </c>
     </row>
-    <row r="95" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D95" t="str">
         <v>2025-09-05T00:00:00Z</v>
       </c>
@@ -25310,7 +25552,7 @@
         <v>H4sIAOW5B2kC/0VQyY0DMQzrxe+BIVL3tBZs7ys7j+hlWDz1WVhvb/mNisSzmOutbS3hHSXeBvBZLffbVRCVVsxWexbSzj+zgqUBKYl8lvKKg6rGER4dcuDqceA6wqxMD7PQwYfLwUc6jZCMYz2ukXXw3jPVoePTMTrRXC9ki3ai0wte0Tp5RvfL8JRqdzsJ8iwyLyUUHJ+KUlVMYdB7NtiYEwDtQteQPuVO3GMj6Y6eGqlXLFMuJc3AuZEPVS/jumCXlysqdFKJTTDa1dINw9QuBHoeI8bWr3914xwxU926puW0Wy99u1aFkFBLNk8bxSSI3JSJMDcn6cDfP6S16IrWAQAA</v>
       </c>
     </row>
-    <row r="96" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D96" t="str">
         <v>2025-09-05T04:15:30Z</v>
       </c>
@@ -25321,7 +25563,7 @@
         <v>H4sIAAe6B2kC/0WOSw5CQQgE78J6YhoYPu3VzLu76LwoYUFSqaZf4pAnHthG/EatllAPQP0BXJd4xpd4tjLSkYXuHKXuME/AUBkRDm7sJdp2W800hjrmp9mHTeDxAjSq0Xt7zeZ44IGqMb0CRau54noDrtkTsbsAAAA=</v>
       </c>
     </row>
-    <row r="97" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D97" t="str">
         <v>2025-09-06T00:00:00Z</v>
       </c>
@@ -25332,7 +25574,7 @@
         <v>H4sIAOW5B2kC/0VQSW4AMQj7S86jCJt9vlb174W5NAcUGbCNfw7OW9f6/6U+h7aoZEdlqos0gOdULgyGaIhDYIaZRg5J3m5lItqs1XXwqTvPEhFUmDL6OYFetCulY6nFszh48bx96aaIiIQ6y5+T8rE4ivMlxMLHyxj9PMZMhZUxu8rGzPSXpz6BhiNq6jTIOi/kqsTcZNrRqFr79N3wULEipQxpu5Ha30aFtGOSIbx9RXJFprMBgd4LIGOTWzLwQtLaRNKDnsPGltXXK5Vku9R0NCan0Bg25mZiAmJ3gt8xc9Z5La+pZYsl0WX6+wc98VgquAEAAA==</v>
       </c>
     </row>
-    <row r="98" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D98" t="str">
         <v>2025-09-07T00:00:00Z</v>
       </c>
@@ -25343,7 +25585,7 @@
         <v>H4sIAOW5B2kC/0WQOZIDMQwD/6JYNcULPPw11/59wUmsECQBqL9Hz6ee+b0MxD1mKzfMWidVw7v6nsb59CMq1jZZGPF7NHtVhezritEQvcfNX10RLeUdxhvuO3R19xCrSke65tyDntVtCrueXGDGPVmvT3pa2GhaJs/uKX3bVE2XIFXCmXAPj7Z8WnmiGN9loI9KMWAej2CqOCSmk0aq0zuAi9Is6GZstT8b7MBAMSZ4FRhwUEIrFaLIHs9KNOAbUprvRIkI1sEQJUci9TVTXSBVTjrMxSxssuXEnukZhDmZVCdvyIBuVg/tuQuPbjVf6GLBCpFsHdXhaHbz+PsHkyYwR9IBAAA=</v>
       </c>
     </row>
-    <row r="99" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D99" t="str">
         <v>2025-09-08T04:15:30Z</v>
       </c>
@@ -25354,7 +25596,7 @@
         <v>H4sIAAe6B2kC/02NSQ7DMAwD/6KzUZCSteVrRf5eww7Q8MLDYMivGOTCB1MD/3jHkOYhfAHo9CEWvpFFMnxWOR3ZPSSfOfOspinhTK8cwtJHqtRE1LSiRljsvaM5qL1eGoU+2urNSKhOy2an9ZLvH/9ymte8AAAA</v>
       </c>
     </row>
-    <row r="100" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D100" t="str">
         <v>2025-09-09T00:00:00Z</v>
       </c>
@@ -25365,7 +25607,7 @@
         <v>H4sIAOW5B2kC/zWQWw7lSAxC91LfUeQnxndrrd77UBl1fiIdY1Pw5/j5zTu1/z7S8zmRF8PM3BbbMUg+h/gf92C6gpWbeI7PfJzal1hLC9/nZNTlXAc2l5EcybP6M80gPCO20zb6ObI5P74JeXYzjB4jW+DjhkXuZMnbXHj7YlisLN08qyKes/bxjgRRFhVTlF6K7w6dsys07XYX3FPB9rXQQ9YN9JJCA2TeAb0DEY6umb6JUTeyfm+pHQ1izO6poZ0fEPv6qKfcShpuo/dUC73MwLhNs6HUQZd7+dqbnkMYoZzKp3efn5P2DlqoLMmOLwnl795qK73Vdmdh8Pc/YP+JjtEBAAA=</v>
       </c>
     </row>
-    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D101" t="str">
         <v>2025-09-09T04:15:30Z</v>
       </c>
@@ -25376,7 +25618,7 @@
         <v>H4sIAAe6B2kC/02NSQ4CMRAD/5JzhNru9GK+hvg7YTJC+Giryq/hNp72sMWwX8CaQzgD7C9cMYdnXJMXuOTdpswqzlG3zdNRgqyZrK8NzRvatYdTCkjEpTtUWESTyH1DKDdlOhuAWDKxCrvq9wc8rypSuQAAAA==</v>
       </c>
     </row>
-    <row r="102" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D102" t="str">
         <v>2025-09-10T00:00:00Z</v>
       </c>
@@ -25387,7 +25629,7 @@
         <v>H4sIAOW5B2kC/z2QS44YQQhD71LrVgubj2GuFuXuoXqkVO2w9bD5c3B+9Kb9f4D4HPYdR5lVoEcs5DxnPnf4zGjawyOZz4Him6spNkqlAFZYx4dvrtNzHJPWO9fHv8bqNA95XFCMzk+/RrOeAugI+HNqPk5nqBKUuTz1HJldvytnjLHL9z+nlb92ZQcxaOuLgXVe/6azIjXSkpcD77rCJNRj082w2sIo283z+oAdcRtyTbdy2hWW1BB6AR0XRSCuoPExhLAH7VgU/Rc1A5s9nsONtaWpuxz2jkV1+2S1uKhiLIp8PYqgkaxwu3kNuZdKfzeVcjMote3//gOoYhQy0AEAAA==</v>
       </c>
     </row>
-    <row r="103" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D103" t="str">
         <v>2025-09-10T04:15:30Z</v>
       </c>
@@ -25398,7 +25640,7 @@
         <v>H4sIAAe6B2kC/02OQQ7EMAgD/5JztAKDCd6vrfr3jdoc6qMHRv6NsPG1jyWgV2IO+QOsX32tOaJ4kyjBN/fd92LOsY4sKuAEupKpZZzDG+erRae3p+0L9e07GyQgKCyojL2Nbnqgu0G5dWSmCrz+XuJok7sAAAA=</v>
       </c>
     </row>
-    <row r="104" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D104" t="str">
         <v>2025-09-11T04:15:30Z</v>
       </c>
@@ -25409,7 +25651,7 @@
         <v>H4sIAAe6B2kC/02OSQoDMRAD/+KzCVIvcne+FubvMTOGREcVJfQZjvHGC2GGX4Sco/kQrP6P5nDljVxioiyqgbTYaJ09F7n7WIyUy+dg2bGqhfZGBc2Z99550eG+trMLUhsR/TCinPQlU1hX8voC7qgmY7wAAAA=</v>
       </c>
     </row>
-    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D105" t="str">
         <v>2025-09-12T04:15:30Z</v>
       </c>
@@ -25420,7 +25662,7 @@
         <v>H4sIAAe6B2kC/02MSQoDQQwD/+JzEyTvztfC/D3N9ECik6BU+ohB3njB1eYXjSXDA1Dzn1xiGTeyHKUFgC7triX1vO2FJTf0VuXYErY+0rgptQZeStp9d6wAxxvcSjnDt4U5bBcrzwgjigpeX1cly2S6AAAA</v>
       </c>
     </row>
-    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D106" t="str">
         <v>2025-09-15T04:15:30Z</v>
       </c>
@@ -25431,7 +25673,7 @@
         <v>H4sIAAe6B2kC/0WNWwrDQAwD77LfS5Ffsp2rld69JhuIfgfNfJdhXfjAVfGOiL1aDkH0uxxgjJsYUzJL0IXKSu6Vj85oGm4pCHhV+l5S+txams1JQhI8wnOLSauDNkIWbNjYDxSUkdXW4+5y/f0Bh5nMr70AAAA=</v>
       </c>
     </row>
-    <row r="107" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D107" t="str">
         <v>2025-09-16T04:15:30Z</v>
       </c>
@@ -25442,7 +25684,7 @@
         <v>H4sIAAe6B2kC/02OSw5CQQgE78J6YppfM3g1493l+SZRWLDorgovccgTD4T23xiXtN7B7G+8lzjzm8zVMDfUNhI9TB2bEygyoFWmxlii2w62m5nguFJ5USM6T3S7jclzjFE6FPrOFHXVMzRr+qz3B1j/61K7AAAA</v>
       </c>
     </row>
-    <row r="108" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D108" t="str">
         <v>2025-09-17T04:15:30Z</v>
       </c>
@@ -25453,7 +25695,7 @@
         <v>H4sIAAe6B2kC/02OSQ4CQQwD/5JzC9nZw9cQf6eZHiF8LZfllxjkiQechV+os2R4ABR/xJdYxkUsjSjo+FTnkrqnLMmO0Irg7losYevtjO2+OwZbBK+1owVU9Xuj0I3obWEOI1qtcjATW+58fwCumiR6uAAAAA==</v>
       </c>
     </row>
-    <row r="109" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D109" t="str">
         <v>2025-09-18T04:15:30Z</v>
       </c>
@@ -25464,7 +25706,7 @@
         <v>H4sIAAe6B2kC/02MOQ7DQAzE/rL1IhgdI43ytcB/j2G7MFuC/K3A+uKDtHnhtdfYLeAvIeNeUbxUVJpnEd5savbq5xZVdLWnSgF47mXypzr31gUTh4G8fndGTLuqIjli91lhbmdmYGoc3e0jHX9fSaLUuwAAAA==</v>
       </c>
     </row>
-    <row r="110" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D110" t="str">
         <v>2025-09-19T04:15:30Z</v>
       </c>
@@ -25475,7 +25717,7 @@
         <v>H4sIAAe6B2kC/02MyQ3DQAzEetn3ItCM7rQWuPcIXj+slzAE+Vsq6ysfMVS/zvZqHCB87QXfS8NvpKEQ7VLOZ4W98qlphFvAvKBMTg1Ff3pi1tXB8GbctSM5RklkzuxWOpL0YQDNu9OTMmHl9Qd8O7umuQAAAA==</v>
       </c>
     </row>
-    <row r="111" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D111" t="str">
         <v>2025-09-22T04:15:30Z</v>
       </c>
@@ -25486,7 +25728,7 @@
         <v>H4sIAAe6B2kC/02MSQoDMRDE/uKzCVVdvTlfC/P3mHgYoquQPkMYb7zgLDzQ1hyLP6H1T2+hjGPSKTWjrFCec9Q9U6GtOhSLTGoOtp3I97AiLTxg1NmdKvYpQwSLYiN2hnUkKa9EtKVtJ15f7IhVHboAAAA=</v>
       </c>
     </row>
-    <row r="112" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D112" t="str">
         <v>2025-09-23T04:15:30Z</v>
       </c>
@@ -25497,7 +25739,7 @@
         <v>H4sIAAe6B2kC/02NSQ4CQQwD/5JzC8VxVr6G+Ds900jgY8rlvIQqT32oI+YXyyWDG3D+07OEGYekg2xEWWn5Vuo7xjRzUtOmuxNL0HYkV43rVEHuTt5zxwqA2cMxgzcuS+cwAGH7F417oL3eH+E0Q065AAAA</v>
       </c>
     </row>
-    <row r="113" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D113" t="str">
         <v>2025-09-24T04:15:30Z</v>
       </c>
@@ -25508,7 +25750,7 @@
         <v>H4sIAAe6B2kC/03MQQ4CMQxD0bt0PUJx0tgJV0PcnTJlNHj75P8aYeNpD5sou0fMYzS2mP/JF4J5SpBge5Z3sLPzGPrlFs3OmWg6ONcJ5Xn1SnIaGAGeuX1KiOo0q1KIWCfrbYCLJbjTk4p+fwC7Ri2RugAAAA==</v>
       </c>
     </row>
-    <row r="114" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D114" t="str">
         <v>2025-09-25T04:15:30Z</v>
       </c>
@@ -25519,7 +25761,7 @@
         <v>H4sIAAe6B2kC/0WMyQ3DQAwDe9F7EVCizrQWuPcsvAZM/TTk/ISQLz5w47yxWDJ6wL43nCXMuAlLLRtNMPbPl9QjY3EMMeQ0m7lE2+LRdWkh3XfDuv32nVkY1DQGBnZl7RnmMFWt7sw9oaebXn+9QXkbugAAAA==</v>
       </c>
     </row>
-    <row r="115" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D115" t="str">
         <v>2025-09-26T04:15:30Z</v>
       </c>
@@ -25530,7 +25772,7 @@
         <v>H4sIAAe6B2kC/03MQQ7DMAhE0bt4bVXAwAC9WpW7F8WRWjYsPrzPgqy3vMTN5DeU2Kv1FPkv6nuBcRekWEDZ7QIhuVc+HNKKKVlRZrOH07J4wO4GKwhwzuIWz18YUMSA2q7R8yZ9mqrlWJ6tQ1Xx+gL03M5KvQAAAA==</v>
       </c>
     </row>
-    <row r="116" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D116" t="str">
         <v>2025-09-29T04:15:30Z</v>
       </c>
@@ -25541,7 +25783,7 @@
         <v>H4sIAAe6B2kC/0WMSwrDQAxD7zLrodjyV71ayd1rMoHIG6OH3m+ZrK98xAF5kxJ7UQ+Ze2PcyzJuYtkQb7IaqY296rFZYWpLl4JKzWZwPLoKZxqlDUbcurMKDWQp0jwB+qyEh83TqoVidLNUrz+XKBlWugAAAA==</v>
       </c>
     </row>
-    <row r="117" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D117" t="str">
         <v>2025-09-30T04:15:30Z</v>
       </c>
@@ -25552,7 +25794,7 @@
         <v>H4sIAAe6B2kC/02NQQoDMQwD/5JzKJIdW3a/VvbvDZuFVkcNGn2GY7zxwmL/xXKO5gEw/MI1h2fcxEXTcoaYucs59Mg8O00Zjm6CW8ayeHRKF5al15Li1p1VUECBBWxqvVfow0iUGtmVzv3I6wu3LQKyuQAAAA==</v>
       </c>
     </row>
-    <row r="118" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D118" t="str">
         <v>2025-10-01T00:00:00Z</v>
       </c>
@@ -25563,7 +25805,7 @@
         <v>H4sIAOW5B2kC/0VQSY4EIQz7C2eEsjlLfa3Vfx9Tc2iONvH2WboelSO/p0jfy2o9c6arLEPVpSKw18iFGy0lFt1wzF7aeuEKeEM8ekak9vKwf5VBWFiplzfFPf3FzZBRqgC6Yy/A3jQT4ommSCOctik3ZradYRSFpEWFkWi8F1pMbnQIpVvvVZLroSnFJLQZTe3iKiBh7TgUCuZhM6ESszUJLTtVwgSEE0oCes2n9cBU2gYmgyRTV4vWOFQV9miPibiD9JBBk+FS/NE1zqXMkguqW5xWDzeRUTOeOP9wlJojk6OctLkVCYa4VTAnJp0NA5X5Vgmb26V4oikobjKh+f0DbXvz69YBAAA=</v>
       </c>
     </row>
-    <row r="119" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D119" t="str">
         <v>2025-10-01T04:15:30Z</v>
       </c>
@@ -25574,7 +25816,7 @@
         <v>H4sIAAe6B2kC/0WMyQ3DMAwEe+FbCLi8VkxrgXuPbMXO8sFjwPmIq7z1pQHqE1gPaWyg2v8kh3jlRVbHWYYI0mIIfzKv8Jqd0RURakMwLW9dKhOuk4yyunz7LbHOvTYWvP00QntDrAnVZsnsGczjC2ZAeZa7AAAA</v>
       </c>
     </row>
-    <row r="120" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D120" t="str">
         <v>2025-10-02T00:00:00Z</v>
       </c>
@@ -25585,7 +25827,7 @@
         <v>H4sIAOW5B2kC/z1RSW7EMAz7i8+BIZHaPF8r5u+lU6A5+CCJa36Wr8/Zcf6/wcyzEO843VFkk2WIZ02/4y6Mn/FBNPpZ3nPn7EPrHANIfxb9JQcyWDHECQ40L3tpzCtO6r5hFHtC924CDDsqpw3lclOdf4ukVaSdLEH5rPaXKTN0517H3SSs9wjgmwVKpVFFT9yN1/pkYx9ySpYqym4EhrJFx64xb7GNmTDazCVj8tbRLGmbvZAJtcSo3UFLHqTk3kXOXcR2GtPKlTzkC4CoMLUnEVMKc0bdqBKD5CHLMkyEKtCtEqo3ZT+z8+SUEJcsry3jkUq5fp7qk6kaqp7vL2qGgqrTAQAA</v>
       </c>
     </row>
-    <row r="121" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D121" t="str">
         <v>2025-10-02T04:15:30Z</v>
       </c>
@@ -25596,7 +25838,7 @@
         <v>H4sIAAe6B2kC/02NSw7DQAhD7zLrqLKBAdyrVb17aRKp9Qak589rOdYTD4SZ/uTHEi8Aw0+MY3nuk8xldESbj+dL6i7zDM8K0NFpA9h2ZyQbv28k201n2xXaaKKspQKZNSnoYvMEtpqzVNOl9wdPoG5NuAAAAA==</v>
       </c>
     </row>
-    <row r="122" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D122" t="str">
         <v>2025-10-03T00:00:00Z</v>
       </c>
@@ -25607,7 +25849,7 @@
         <v>H4sIAOW5B2kC/z2QS24kMQxD71LrhiGK+vbVgtx96BoghhfGkyWS+nnwfPfE/p3xmc/jcbH3phG1ZDnj80xfDEcKRTHStj4Pei630F/2TheC4uRezsZu+NLX9RQve/+3LTLMUtNb42v8lU3Lqcp2CXl+njY+X9jhlmu6O20IcdjLE3Az7wnH5jVko1zAoTEnCuiuebmcgslT4fLaGDdSFWJvB+pkZypEIet/No0ar7O0GIkwNmUWg1JB8ru+kbptfUWGsjUWp2fKh14hh1pq3o6cPDK1ctverFZBe3++sTgmmIOdZLTU1amVu48qaoB1xw7yRmHf9OHH7pquyETw9x9veFXj0wEAAA==</v>
       </c>
     </row>
-    <row r="123" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D123" t="str">
         <v>2025-10-03T04:15:30Z</v>
       </c>
@@ -25618,7 +25860,7 @@
         <v>H4sIAAe6B2kC/03NyQ3DQAxD0V7mbASkdqW1wL1H9hhIdH3g12cp1hsvmGj/TvxYzQ2QPyiOaPhNGslKuDGVncfKJzbg1o6rKh0zYYk/OZfyMiES1rxre+UU1YA2qMm8VuhtJEgNcQ7YvDy/Yl4gpbkAAAA=</v>
       </c>
     </row>
-    <row r="124" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D124" t="str">
         <v>2025-10-04T00:00:00Z</v>
       </c>
@@ -25629,7 +25871,7 @@
         <v>H4sIAOW5B2kC/0VRWW7FQAi7S76jCLPY8K5W9e5l0kqdT4w35uvC9ZnH/l+Y8b68r08/Y2COYNFk3dfgTGXD8qhOK/MdQ3XmFZkWwqhLxH1F2RF3qMVJg6dbnDnf/Vm7XB1WwOe+qDn7SjGkQJbK+75k+vOdDTMwrM7qyzcP7IE1hFBilugbyEpHCR6sEtqUsUKA8WWQhvUex7jrIN7bGHiA2fSzJtMjnXJdvxyrHHKTTgMHmHkpKmNEhXl4Y/utH1+kazRZC23q08TzFYsHlJNCkXuUtfHhCeBPerv2fFpq934F01fNub+RzA29YMnemhEbQXzkZUHQ1yvq+wcG+C1m1gEAAA==</v>
       </c>
     </row>
-    <row r="125" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D125" t="str">
         <v>2025-10-06T00:00:00Z</v>
       </c>
@@ -25640,7 +25882,7 @@
         <v>H4sIAOW5B2kC/0WQS44EMQhD75J1qYTNv6/WmrsPZNNZGsd+8D04n3qtfy/1OdRVJaMo1g6Mgc+pWBkp4d6K8kzz54xw7ezs8PEW1UdX5+oKEbESQToNzwnU6uOdshbMnDFyDUu/VCs3zzKWRT0n5ca4EhIjGcZhz+m+OLLQ2lrtSzA4Yr5BVVBOkKsHOEEg83wgL5ueTFZaqthuQNsvgSHy8Ggge3Wt+6Ns2kNVUKnKnWzJTKa1ytA1gbpr0DYLHDAIM4KaGdvClu3XF3O/MNF7YAxZaEwa883O7IZNfIXeZZiDYDnnGi9tmT3x9w+jJb6OugEAAA==</v>
       </c>
     </row>
-    <row r="126" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D126" t="str">
         <v>2025-10-06T04:15:30Z</v>
       </c>
@@ -25651,7 +25893,7 @@
         <v>H4sIAAe6B2kC/03MWwoDQQhE0b343YSyfLRma2H2HpkeSPTzUucjBnnjBSfxu0QsaT0F/0V9iWXcxbJpRKvNh/aS/WhTMrl71ERWjabFeLyqYlfAzbbz9s4sCDrDK1W7c0bok1TpiNZyxwajri+WGpO4ugAAAA==</v>
       </c>
     </row>
-    <row r="127" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D127" t="str">
         <v>2025-10-07T00:00:00Z</v>
       </c>
@@ -25662,7 +25904,7 @@
         <v>H4sIAOW5B2kC/0WQS25FMQhD93LHTxHmY6Bbq7r3OleqGmVko2PD94Pnq8/+P2bl5/H5k9NIMK13Ps9qeo7B9BNda8XPg/ErA1KCsKrZ9c8T/uo23RtTQ1RB8Ci7eriVScpsbGi+Zq7eHQ2wdwsRSmW/HIbqdFkXkVBuI9/5FBlCGWu61JK87Wm+LcfDsi3U01oBeyLIbNIzzLNlYPsaZSIxQNqMQQY3r+Ht0idGEZuKQJtQsOPTSjV3Yt+l0ajnq6LqDHPN1pWhLTwuSxCeMZHC1xN7b91KD6wfcnQn13qqywiRkLlnVbTbsgI3Qq3vpZZHenkPJnT9n1+TARl5zgEAAA==</v>
       </c>
     </row>
-    <row r="128" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D128" t="str">
         <v>2025-10-07T04:15:30Z</v>
       </c>
@@ -25673,7 +25915,7 @@
         <v>H4sIAAe6B2kC/02OOQ7EMBDD/uLaWEhzT762yN9j2CnClhCh/1CMCz8Y+4PEHM0jgI/wnEPDt9EooTEBq3b4HPnGNMJCWIHoKupSLPG3Z6hSa8kSy7YdPDvfuTBZBxyUNUMfx0WXqJKaVLsfI7AsUboAAAA=</v>
       </c>
     </row>
-    <row r="129" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D129" t="str">
         <v>2025-10-08T04:15:30Z</v>
       </c>
@@ -25684,7 +25926,7 @@
         <v>H4sIAAe6B2kC/03NSQ7DMAxD0bt4bRSkZGro1YrcvUacRbT90ONvOMYXHyz26yzmaJ4AvIJyDg/dxaPNxYaDxCrNkY/mkWImrMMXag6W6eFkiQ6ZkVVxc+dJNDdZy1mk1vaIPnEPJKTy1Ruk6voDV1APDboAAAA=</v>
       </c>
     </row>
-    <row r="130" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D130" t="str">
         <v>2025-10-09T00:00:00Z</v>
       </c>
@@ -25695,7 +25937,7 @@
         <v>H4sIAOW5B2kC/zVRSY4gMQj7S86liNVAf63Vfx8TaSo3A97q9+j5qVsx/79u9e+YLZwpinKtDFQR7lwYMg1M2rinzne08PAUkVLLNMd33HzRhtsELOAhsnjE0xTN0CleRLt9J40sfT1sxFKAtEZ/B3i4WGRbRqjXVBCfWDy7p4UcNKQg/8jDA5pYg2X2TDLL4k33kY7KUVXqqjpjzaUfjXLrEljtgM53UAyszbvskK1BEdgBepTrEWBL2B5q3sGEtxWXR4TS5kukciPZTqkEF40K1kpp1Wvk8B5HC+MUw1mxPbMtG3Tm2GcvRlM8/eYIf1C1RGd7/v0DHSbrEMwBAAA=</v>
       </c>
     </row>
-    <row r="131" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D131" t="str">
         <v>2025-10-09T04:15:30Z</v>
       </c>
@@ -25706,7 +25948,7 @@
         <v>H4sIAAe6B2kC/02NyQ3DQAwDe9n3IhBFnWktSO9RvH6Y0G841GdR1lteYuhHNPZqHCD6AAXfi+EXYrRqTduclayR8p4bFAFF/CVr2F4o9XsxwzUdXSSrr8GjORgTUboFrOYZpA8ExJlanAOy8/sDzlvNw70AAAA=</v>
       </c>
     </row>
-    <row r="132" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D132" t="str">
         <v>2025-10-10T00:00:00Z</v>
       </c>
@@ -25717,7 +25959,7 @@
         <v>H4sIAOW5B2kC/z2QS47EQAhD75J1FJX5GOirjebuY9LSZJGFyxjzfi5cn3ry/H9A2X1ZrRxBjhkNWU7e15xXdgtGHp+KgNwof/X0nqTlsMm8Lw9709PdrBmVTgvp9cYzjaQefDC7NYbXpx+VSER0shHW96US6+8DanVnYubk6rN+r2g3B1NxkL8r1l89sx390AylAZyOnSgVylXDYSXdO1cfXaW2GovDVBJ4tHoe+ZnQT73G9+KY1WU71YZw12niBvjqu1pH0Mo6tpL5N2haJG0KBdaX9K7GeRpi1GIiQagFSklmz+Isq8wW1uIegRSntCc4wTO9DDG/f0jyVUDNAQAA</v>
       </c>
     </row>
-    <row r="133" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D133" t="str">
         <v>2025-10-10T04:15:30Z</v>
       </c>
@@ -25728,7 +25970,7 @@
         <v>H4sIAAe6B2kC/02OSQ4CQQwD/5JzC9nZw9fQ/J2GHgl8LbvklxjkiQecPX/xJcMDoPiFG1jGl1gaUdDxqc4ldassyY7QiuDuWixh672ZnBhVhY93+9GdXWx9qqaGVfODiDmMyCi0Wu5v4OT1BpFCoFK5AAAA</v>
       </c>
     </row>
-    <row r="134" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D134" t="str">
         <v>2025-10-14T04:15:30Z</v>
       </c>
@@ -25739,7 +25981,7 @@
         <v>H4sIAAe6B2kC/02OSQoDQQwD/+JzEyTvztfC/D3NTEOia6GSPmKQN15w9vzFlwwfAMUv3MAybmJJZHSN5hQ4S+rILHLMQ1WrMpVL2HpKQ5ANmicj5tadC1Np7e3hpVm7hHnQ3jFzBKH7m/H6Apv8c023AAAA</v>
       </c>
     </row>
-    <row r="135" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D135" t="str">
         <v>2025-10-15T04:15:30Z</v>
       </c>
@@ -25750,7 +25992,7 @@
         <v>H4sIAAe6B2kC/03MsQ0DMQxD0V1cGwFFmZSV1YLsnuB8xbF94P+MxHjjhRX9GD1HxwHwATs0R1oXpVdwWWCptHuOumupBrOLTqUdc8TmfeqlKvuf6qBO7rwErLJUZPPqBfpYoGKbVmwUgfz+ANfyW1q6AAAA</v>
       </c>
     </row>
-    <row r="136" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D136" t="str">
         <v>2025-10-16T04:15:30Z</v>
       </c>
@@ -25761,7 +26003,7 @@
         <v>H4sIAAe6B2kC/02OSQ4CQQwD/9LnFoqzOnwN8XfCTEvgQy4Vl/xaJuspD3H0XzT3atxAVH6B72UZF7HIphtddX6yY686NvMOgFTL6dSUQD0tBprlzMog6/KdDY2eY+khUP2OgPQNIZ4jU6ONISPeHwSiO+q7AAAA</v>
       </c>
     </row>
-    <row r="137" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D137" t="str">
         <v>2025-10-17T04:15:30Z</v>
       </c>
@@ -25772,7 +26014,7 @@
         <v>H4sIAAe6B2kC/02OSw7EMAxC75J1NIIS/3q1Ue8+VhtpysryA8R3COPEB4uJv5xrjuJNVG9lzSG3h1hBxNHHEizmiN3WjxQY0VZP6wzz2KGsTNDKqGDlXbc3lDMl0rL70BOIehhhkoWWm/XQ5dcP884PPboAAAA=</v>
       </c>
     </row>
-    <row r="138" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D138" t="str">
         <v>2025-10-20T04:15:30Z</v>
       </c>
@@ -25783,7 +26025,7 @@
         <v>H4sIAAe6B2kC/02OOQ7DQAwD/7K1EZCSqCNfC/z3LGwXZjuYAX/Lsb74IBjzWhxreAGffIM8lqduogYni8p0dm6nnporWpRgJY3Zsdj2WN1bKRqi2wVdwefEOEyFwVDVO0jMzYgIRdQGYkbZ+Qf6bWN9uwAAAA==</v>
       </c>
     </row>
-    <row r="139" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D139" t="str">
         <v>2025-10-21T04:15:30Z</v>
       </c>
@@ -25794,7 +26036,7 @@
         <v>H4sIAAe6B2kC/0XOyw3EQAgD0F7mHK0wHwNpbZXeg5KR4usTxv9lsk75iQP9RfNYjQesKV+0jmWMV6LFTZihTvWR3GUWloxOwCqyRlC6j4rKkEgiJulP397Q80CILAHIIUi/BrFZUhbOVA+t6wYu1+8MugAAAA==</v>
       </c>
     </row>
-    <row r="140" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D140" t="str">
         <v>2025-10-22T04:15:30Z</v>
       </c>
@@ -25805,7 +26047,7 @@
         <v>H4sIAAe6B2kC/02OQQ4CMQwD/9JzhRKncRy+hvg7ZbcS+DqakV8jbDztYcut/5ZztF8gmvYbNEcwb5IygLWqLeXYTp1aZJRQyZYYxTlcOJaIgowyc6y8eueDFMoFJ5glbrZf3dAN2d/WtoLt/f4AQPNAfbsAAAA=</v>
       </c>
     </row>
-    <row r="141" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D141" t="str">
         <v>2025-10-23T04:15:30Z</v>
       </c>
@@ -25816,7 +26058,7 @@
         <v>H4sIAAe6B2kC/02OSwoDQQgF79LrJjyf/1wtzN0jMw2JLssq/CzFeuMFE+nfMPdquYG2/YGUvTT8IUFBRs2Kq42SJ6YezSLNJBEWe0nxSE2y3CfCDt6180EboRQL5LjqY6EfKDAWci7CzVB6fQEzYnCZuQAAAA==</v>
       </c>
     </row>
-    <row r="142" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D142" t="str">
         <v>2025-10-24T04:15:30Z</v>
       </c>
@@ -25827,7 +26069,7 @@
         <v>H4sIAAe6B2kC/02OSQ7DMAwD/+JzUEiiqCVfK/L32omBhhceBkPwOyDjlI+4Sr/CY7TeAA35B5wEwQfFlKC+Gi5+jNxrYLSXSTKUYTElLdtWmyGLWhr0zHtvn2gWC4JaH3JZ0g9T8bTWzECpm/P6AQW09wu7AAAA</v>
       </c>
     </row>
-    <row r="143" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D143" t="str">
         <v>2025-10-27T04:15:30Z</v>
       </c>
@@ -25838,7 +26080,7 @@
         <v>H4sIAAe6B2kC/0WOSw7CUAwD7/LWFUrs/MzVEHfn0VbgXTLKxK9FW097WJjsF+ex5OeeM/pn6lisvEjBkXKNJ8ozjtW3jFliM2bY1eMb+eA+E0C0hJjIsTiNdwkFrL5SGIP7mZsu5sbGnryZwxHeH7H2jUm7AAAA</v>
       </c>
     </row>
-    <row r="144" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D144" t="str">
         <v>2025-10-28T04:15:30Z</v>
       </c>
@@ -25849,7 +26091,7 @@
         <v>H4sIAAe6B2kC/02OyQ3DQAwDe9F7EYg6qbQWpPds7H2YTw444Edc5a0vDa15pJYMLuDko+cGXnmTMlgOhkgrZCzpY/NMVhUzsklGLwHtzAYadKjvWPUlPCc26gCQKI3aQujcDGp/G8In2sL4/QGv8SQ5uwAAAA==</v>
       </c>
     </row>
-    <row r="145" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D145" t="str">
         <v>2025-10-29T04:15:30Z</v>
       </c>
@@ -25860,7 +26102,7 @@
         <v>H4sIAAe6B2kC/03NUQ6CMQgD4LvseTGFwihezfx3dzqN9rFfKI9BjDtuCHj/Zc3R9gY28Qsz5+DKQ0VGwuGGkscc9VnjUm6zUviScZPJ8/upcteUq1U6g+cuEe7R2l+R4ssMfdAQvZq1C1WHresJllyIK70AAAA=</v>
       </c>
     </row>
-    <row r="146" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D146" t="str">
         <v>2025-10-30T04:15:30Z</v>
       </c>
@@ -25871,7 +26113,7 @@
         <v>H4sIAAe6B2kC/0WNyQ0DMQzEevHbCGZ0K60F23uEdQ5+9CDEeS3FeuIBg+MHlXs1b6HN/pNle2n4UalqRXdLpHXslZ+aJqJYY6JMJsYS/+5QHVqEcM5dO0+OGtrVrCKa0yP6SE5vFkY6HZJyvQG7yf+NugAAAA==</v>
       </c>
     </row>
-    <row r="147" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D147" t="str">
         <v>2025-10-31T00:00:00Z</v>
       </c>
@@ -25882,7 +26124,7 @@
         <v>H4sIALO5B2kC/0ydW7Ltqo5E+7K/T1SYN1TXqvOlkSKZ656PG1uey7YwiESP1P/9K//+9/ufb61zzrf2aHOX//7VFO7v69+3Sm+r/fevWVjGWaeN/fX4o//+dcvrnuPUL678929Y2Hbc+JTWQjgt7GucvVft879/y8IR0q/GLeIF9hPuPUu8wl7//TsWzl7rN2Y7/b9/5XvSPeoZX6nr++IWpfjC+uJJtfde9L7labdKvEeNeyNtP+nsc9dWQ+fSfzdpZ6zv7J53fwpOfj1mvH1In4azhYYnhhXpT8Wz40Kd38yb/NTs5es1Rpo3Ob9hqrUX3ic+ydOznYoy8cyQPiXbV+L2YxY+39Ow7LbjA4TmIX0afmvyrL64b38TYMYr9FMlHZbu2uOFy/zi+9Vp6Vyrjy8+BNJl6SinnL5P4x22pa2fNXY8jt8eS8vos7bV+bDt6rb2mTse1wrTzTNzx7Na7fFV4watWjpmzLT27RGv25qlrcU7nbhtDE6zartoGu42eZhVW/EtZonbcANrtuKf6/TKn1uv1casMebty2/frNqKIa+ntcY8blYtVKg9XiSGLhaHVZtjjckaqywZ6zabpn05H7+1bqFZjakcywmpdRsrPlhc4u+tWfxxi/+re9dci1YubhnTpJ3Z44W7teunxPeMVV1C5279OuPQS9Vy7Faux+jWb8anjmHvVq4jOT3WQaxx69b4HPHf4VsM68Z3b6XseI+QWrdWS0yU+BRfPGxYtxjFztNiQENq7cIYlFKY1FsDP6xdDTM14tNVpsSwdvGvGcMck4hbW7t43NljtIPOw9qVUfW4b3Bfa1diCM7XYrrGRJlW7wuNG8ZtxstNqxcD0bBMJ7Sb1i5GNr78bh8TaFq7r/RQpC/N1Xm1m2ELtkxCfLc5LAzLMBk6zOW0sLUhZfWsZSlv0Ev5UGxexXTLmJVzY0bnsXSEdYmPvJCuz9K666hh9BEWC7+wraFs70eDvq5useRnLI74mhNps3TEXWM+rRFrdlm3+HQxYjHbDlIrx0CUEa/3hcrL2s24EEMWUz70WNYu5n6YtDA7Ydf0GlYwTFfMhm9XpsqygqyLecaZLK9tBdmjmHGlxOfY1nCEHQ8zEUMSw7mt3ojvFvMSE62ltK3hKF8YhC8MfzxwW8POkmMnWjFVtjXsTBKJQ5dtDXtvscRi8ejlrGGvMbXjww6W3bZ6sTrb1kyMkdtWry020V3iFWMftHrswVPTNWbLsXqtYQ9KfMP8gMcatoLq8d+I1zhWrx7ercUyiQceqxezpceqjs0xhNaujhlrPz6MdmNrF1acKbDiT0Jq7WKZ71bZqdMyHStYzg6LU+KJMfrHCsbjY+6PmPf58/jovhJbWmxLMfHYjz9rWXpM3lgq8ckQW0dWcIkPvvniYfYtjm26xJbZe0VsLb8dXzEGanXdxHp+DH+tMVL6tRX9Ah3Fe8ST9WtrGnMpTHN89DoQW8+voFGLr/xdjazr98XMwZIOwIEBjLBB/CiWDb82fIkpHbtG2H12tGLsEjt9mMDYlbAIxdhlnJgLYdVm1W+7pfEt4l+xWSZgKwYvzNTSWNdTgOkqGoY83u0bWKti8BImcYS1aX1s/XZbPMNehDkvVW9yLI5pEh8zpiGDYvASH+uL7bIhv1jMaoYk3oMFwe2NYGKCl1h3JcZRv7aiAQpKWOTYgNHUGGbE9vJhc8bciK0migZeiXdkwI1i4qPF7h3QiH26GMWMmJhggphc+rH1DAhaeky3qo9vHBOWJCZmZ7Pn1wYysdPH9F+B1HRvQ5kRe+mOwerCioYysaj49mHdwzAKFhrODIxSGImwECeHy5BmhJ2IR4OtGV9jmtgkAvD1WMwaF6OawZTobN2s8WJgg5qF7S4fak1jvtT42DFv+f6GNSM+RUyAsESg0WJcE/tSjHdMTrC1XtHYJgxbmPXYRUaV2NqGMjHLw6ou3tzoJjboUH4AkL4cBGOcEfYGNcMY6cFWdcSwctg4S7+2qnGEiHNBmJ8h+G5VQT7x5VfhHFIMckYPYSyasH37PtXq9phbFaMRX1F6Ge3E+8cijYV3NCUNd0bg4bDR8Rl5S8OdMDhhhMIQpz0y3hnxiZrQNrtHMeCJHYmVGubn4+UNd+JwEHY4trgP61+Md0aPExcWZmqhGvAE0mngysZ5IN/c2sbn4EQxh6TWlP2jbI5vudMWA58wMesDZh2ZByOf+FKBcOPAsTQAxj4D0BKbT+w9vKXBD0YDUxBL+1ofA6CBJYiNbdRPYmvbApPEB+wfe08xCAqQwrYWS6pfezqfwrE/x3qInUav+bT9SmBCtJbY6rLkwxKEcpzMrCrGJL5KvCY/NhgaNc4Ch4MfB6hiKBTiGguz5amoGAsF6oq7x7Y7tHIMhkbsMDElY37o/YyGQhzvMQ8WB7H1jIV6YjBiYeoFrWRsumEIwQt6k/3ENXaTOIM2PfIpGZtXaNNkB/dTMmxJoJCwzcy6/ZQM+xEzKRYx99hPSW0+OxCmbvKUjGGN3+d5rhgPxftiNOMrFb6+ARFqxFksljxvbUA04nocQmMvuSeqYlA0wAGAwUBL98p+V3oLGxAfA5NqZBRjGItxsKG0/AOjo7jSwUu7a0UaHsV8jv0QQ6YJYHAU4jCQcUrcWnpGRwFu4wAUm0PRRzpPW716HK31Nc7Tlr0qpkm5oLWcp3EceHZMxql94jx1Y1bHSHbZ5fNUjTP4CYwq2FrOUzUmXWwqRYeL+j09C0fs2LBOehXq91QNpcKYxGzJJVO/p21cCrRQ25Br4WkrX0QgfN6yfk/b2CfCggmK5xOewmGzOWrGqkdsbb/DoWnGgtft1xPHXhNjNj4psJ9Y9+8BahBb3W/HiS40CEyOo+N74hj4D/smcXniGPSQ7RRbUblu5G1AoweUtHJ4fdBGfUgJR1HAzZhpDbG1jI2TQ1gMom7ytIyZAeCsCJ+Ok+N0GMetWzwdY0cK6dTuWR9M4vgXU0PYtj6U9IHRWxwPWb71QaRc/owWw/cgUmzLcR4GtegmT0UmRtii9Oc8iAReaZw9qsRPRc5JAR90Sq4PIn09nhmTfUvzh5G+3na815Sprw8jfdq/wuh8epOnZKyKmA2sYLxQT8sW+2X8H66P+iBSwBHOv2HUckeuDybFPlpPHB1Wl/jpGcABS/zh3KkPIAXO3LErBGDX7Z+ejbWMm0A3eXrGHWKvP0sKPYD08cU0W3Tvp2e8x8RQ62M+hBQ7KF6mHRMoX/2BJPbWhutPL/MQ0hffJsxOQF454p6isf5qfI+OX7I+hBTiOE/FKWPrJk/RCuxd7AK5yB9CiiuN7XtpFT6E9AE7YvPVDlgfQvrwfeCw1FzsP13DOoWVjsMc4p+useOE8Ypxz6eOn669homNrZShHOWPGOfI4axaR/0j5ujUmm7S/tw+DEKXF6OOn66xdVWQKa8+foqGkYibbC3y8VMUgxy7gD7G+CkaJgv7n/f+KRr2J/ZbuUrHT8/ZMbwVrFPnT8kY7DA+k+NNnX8+6ESqA3KdPyV3LM+RS27+dAxUGy89NYvmT0fcVT1v/Ju2nEkDjx4Un3+nbbxr3F1v95u2nF3PEjSuDxDFkuAYGcBJ934qxkQL01nlG6rrtzzxhsTmqem2/qzPD8/Mx1mqrt/i3Lh84ibce/0W58HBEUYBHdfPCIVxj80g3h7xzwiFLQlw3TRQ62eEWkzwODZpFa6fEcJTHCcdzhd1/YwQnpaAzPnrnxGKQ2qA0ar33j9T++FwCTQvn/XP1IY9YFuTOvuPqQ30GdOPw0XdP1OrPTD2fd7kQaIw4wFKR9dBoT5IREwjbHh8Nt37t5vEtsavCZ/U/dtPYnwCOVScmnX/9pOO2zUdbPWhoW/GETPAVgFq1geFvrDUm9+mD/5pGQeNuNTS6p3fngnWji+p5XT+7JmB1msexev57Zk4hsKQLd37ablOjGocRqru/bTceNJn/S7yqw8Kxb4+8UzPvP3+oYDYIeLopqDC+YGDQNQ6kCfSag8OxfeJw3cc6qsiC0/X+H3jHLUkfrripIlvvRVceEAojBou47jRdfn/wUKcxXZ8Cd3nB4RipWBYgB/tAaGi80y8Cya4PSAUZ7yKIVP8pD0gVOJQWDhHNd37/GDc2vFZwzoRFvnhPn3pWCw88gGh0LHH4tqp6ANCOBRxL8f5SQa7PSwUaJP9LI7qRDEeFop30UYRljyH4MGhEoc8zMVYus8fiBtjHsfUcj9J+aHcE+szluSnP3jqdpBIeljzD84PXndQQGVXaA8X4cELDDYnW0urP0TPPhRasXO1+gfRH6BbZ+a0h4uAiHFSxVWM+Kkb2/+H+Vn69fgdIgIMx5mh6d5P19hUA4qz5yL+nV4CgsaGppXT6p+jS6xLnZoQPy0V4ouDpGbqw0U4mhrxyuuIbg8bxWkr3gVnCPo/YBRnpNjMdOpH/BQl2BMIN8eGK7+zWkzKiWtNf/A7qwWeC21b0+3fgTTmQfkCp34SvwNpgLoVprkoWPewUXzjmK196SDdHjYK6B3zMgZTn67/TqR4MYmasD4eMCK8q3CQpO9AilM2VnHVJ3q4iE2nhX2bnEHaw0UVd3fcfeoTPVDEkSdehhN/jsrDRTHZKlO0NMUOn549FiWhtKU3f3rGvIgvE6Oomzw9ORXgvcBctweKwq4PYgCfopUPFMkzEKamjDxYtYeLAjyEXQjQoFU8fh4GHCOckZm8DxfFro17i6BWKvWgUSU288VpTGP2oFEsx8LRfLJ9tAeNwlIVPLMETvJ99s8/Eh8aYKfb/5wpGKyGCz3/4CGksHgVcNKnxE/jMMx7KKsg3/TnPgpYEQe+jEq3n/uInY6Zpjf9+Y7wbhExkBn++Y5KYI0wZaece/uf+wiLyM4g8fMdxTBPkLXG+ec7CpsYLwLGvfd53jKOQx/zij94aCnGAMBQlUvQHlpqcl0WfGCIf64yXBOx62z9+ucqw0jG2bytfOoDTI1PrDAoc/wBpvhyH15ghWPbA0wx3GFLGzka9z5P3VgSXXEWpE9bDE1cqLKU6+cY7BzElt79Iab4szgibCLvNxr+lN2YMrwu+oOnLJEDOWR56ANNAb8PIfwti/BAEyHrD3Qg+/FAEycQPMHVQ7N/XlAcgPFWReLn8I0xibmZB4v2cFOshtj5BmEsxM/biw0NLLg4jLaHm2JE4s3D8sm0PNzUwcqB4MqQ+Pl6m05tcU5NR0w7P3fv+pREoM/3oFPMAtBULC7m9oNOnUNeqD6PXmb+HMxbWQvl7uAPOsVhIXakQETKenjQKfAU7uQwIRI/XQN1xKDFHphrpH8/z3ZsmGRxgNn6g06xECoB3n5d8/2hp74CU8avw4zcWz2NA21PQv9Lt3oa7830wJ2C+Gl8Aiw0InFKmXgaxxEmHrHlwugPPXHMwiA39uT+0NPI5RyYSL9+cYtStR6+axL6A1Bs1wHzpjyZ/QEodp/4BEsfqz8AFbYXFymoC/EvbqFITxxCeJmHnmLGx//IzWDAHnSKiRao6eA9QTx/MZF4TWaV7v0UlZ8RU8kgPtzEK4Mfh3789Jw4ktb6sGS9/uIzsxE/Y4PtDzKNACqNRBAN+INMg5jyh0a89YNMQ4FngqW8x4NM8bk6Bv5rEj8dT+C0jwNYmvj+UNOQ5Tk13/AXhSocxmNm5KbTH26aeNg2dka3OS+aVWJ2xTzt6PSLueFMD8Ot80n/xdwqe1ojSQvxC7rFHOLmgW7yqb+gWyzjeAdO5ohfxC3sa+yPcfs0qv0XdItfk93Rm9J1XtAt9CGnIDN+fkE3NhfCvPrWDzfFTgZOxrGJ+Ok6OeWFYeZI3B9uir0mDss7QBmP7L/4Yif+sg8muz/gFGCVCOASFOoPOLFPNr75SvzdH3aKu+vEOXD994edJqk4A/+WXubFUeP7kGUhM9YfcIoNq5GmNrSO+i+QWshZqqPe9fiw08JaAQ94lwedYqnHnhNbKPCzP+jEATUQdezRvMvDTQFeY1kFjtc9Xrg4NoB4aJ9E//qDTdrgO0aSF3+YaSkLAXX4Qg8zaa3HPrZlXx5mIouApaRwVX+AKQY75mgcNzkK9AeY8C/FoTA+ML9+aGmRhUXgQylYDy0t4uUB35Ul1x9UWiRFnsBcWngPKpG3FqgIbwTip+XhMPzlEaY/qETSYRie7thyf1ApPvCnzJSlP3gJAHHoIT0whh7xSwDIHMXTpzR6CQB4cg5uIsTrlwCAJycsgfLSHk4iQEYkLMf24SSyCHCQDcBWfzhpjy9DXjIkDyTFjqko/ZApfiApVnLsRiuQKu/9QBKH+Al09Xpev0yH2LAG26GvPF3j1EcmQG4NDyjp2BQbRJGJeUiJZViJZ+s1H0zaMW8JKIT5yts/pBSrPxDOJEh3r7zEDrxOMUQjb/UyOzjJsve2a8QeXjpki634NvroDywdXMtxnilaqg8sxd+zHcYhQRmA+4l3HCziDCn7+8DSiTkzA/8ogtYfWOKwjZnNvMcHlsJmEFKJ48Y17w8vxQkcZ+T8buC5P7x0Al+Tx6CIZH946egcTXRKv366kp17QPd6n/nLpyFbbGgkH1YCo+N12DhT+sNKsUaYrN8n6S9TZ3wE0QZZteOlJIWMtIGt2TpeSlIYEs553dG/8bKSPmBoHGQPDx0vK+nDU0DCKXZ5/LKSwqwV3C7gv/HLSgKk1pj2TTd5WUkx4ZS9/ellXlZSoFQ8rO0O+/glJsW1mDex65Jr+ctKmixvsAxPLU/X2L7InFVwbpSnK57A+N4VEDLKU5RlQGok9neUpyiuCPLG0bM8Pdm+Dg4rPXG8XC2MEvFMPdF6khex2CBapjUMwyTNrgCoRfngo7xEs0oEBaevXvFlmsURNAxWV9bjqC/NrHHibkNZiKP+STMDPxWZsVFfmlmMXyfdj5Ux6kszw9fd8C/pJv2XwoZXgdTH/Bb16TpJSg6Flfdan64r1I8RGZI+PQOGfYFB69ZDn56b+C5pX+nnGfWpiu9rHvlchnESvleShLZQ5TBOCvGKkyizsSGuL4+PfHM8HWmTRnuJg1V5/KQ/pVbtJQ/GFACOyx8+2ksfDIMRq+WT02G0lz8ImG1xt7bufV4OYVgTDtX4HfLZ+2Uiki4UE0dS6xszMoyqsoDJIn4Kx8yOA0bX4utP30ByYUywuIifvpwaqTdQunB/ym4sfJzgNWv605Rcs5h9B0/aMFAK3B9Lu/ah0MQwUOI48HH6/JbuvV5eZmC8uM03dRPrGDado2BMAr3gSwWt+B17SVsyXi5oI4N7JNAf4yWDxkEoXoVDQA7heNmgnXxwZekhbi+ntLNJx3mfpxoqKUMcVKXJMZ6eOMLJvdUSG09PHKST06p+/fQkZ7dzmObzjKcnaRSxSfR7Hh3jqXpixyWxe9y5Z7zE+SdEcRRhgxjGSyGOvRWLB4waxkuzE8whB0mJ4cZL+Dt0SNMqe2nZHY/T6cQ6EL/MXhLfgEbaCuYvtbcrn3jKDr7c7C4PcSwdTa6XnN3RJ6bWp2/3srPjFixWQj0krj8lVyWsGbOeN3kJ2mHUMAIx8IzuS89Od3FsDnrky88OVcrXOEjrJtaSOpk4GI2eufLjiYGgZJzq1/OlQBPFAizeT/TStEkWITqhkA4j8/K0cfWRgrX1LV6i9iDdMNapQqTjl6kdp5U4pe1cGn9StZXnu5R/MH652hw9l2pQ8n1+ydqT7NWYMCCZ8bK1yeoMixe2ksF56drkhxeykTRRX752fCVAWJcneLyE7QA+B3SjmNt4GduxjZOXkK55vcwvKf1wVj3K2xsvbZuDqvbfcqf1S92ecjaPa4Nf4jaZ29pq89ftiQMw7kH+QI79y96OGRXna0ph9ODxcupjCZ4wy6j18rcnO+Up6aoZL4F7Tpy6IQdyjpe+PdlvyQQ6uslTdXMWi1lPDGY+pDTxk4UdJBTKK84HlgIijKqqIIoqHlJaeGNxtRxVYLwqA1LU8Pay3uf3KzMoH0fS8unXr84gLEzM+HgiVRgPKS2M2OHgRBnFQ0rklZVOJCMn03xIidgY25sSMeZDSgD+AKexR1Ok8ZASw845Q6eS+ZBSzNJ4SVJjuMlDSitsaQe+F93kKboB3WFWOGTNB5UWoRY2rKqbjFerEb+LEVP233xQKWBVj4UUO6rE65V7fHjB6sk6llcxQjCAQ+LSr1/JSNhFcoXk5JwPJ+HlOABXDfnDSZsIKKnQQ+Uw9Yn3Jk9XWHM+nMQOHYfazblU0+JBpXgJEj/iz5hHDyfFL3HVVYUx5sNJsbQ+ogwqSZkPKHHyGXonvfp+BTMxCxdFCQziQ0lhpkMe+y7H5vlg0iHFcVEEpVKe8sSHUpWl0+R8MInofywunLyIrejpyjfcYd1ybj2MdPBaA/z2HYL2KwEKg03iJEP2UNLhMBpvo6PwfBAJTyq1h3tI/FTd2OuFgUD8VCVrecroUYj0CpzigEfq17wVI/PVpwVUJIzPgRXxK3MqSwBH+9h8FWqxckGnJV/mFakFPCDAVZR7PV+J2ifAQsYd7/hq1L44BjIthuqiXpHaR0Jra5RSId6vCov8kkMJHGIXcn28cQCNj7PSfIVqJDE2pX8ifUoeYHkcHzWlX6Uax5PF/ittXqla4NdGXtlHDsh8tWoUWAAET0uMP1+xGpY17AXxPMTWM13S5G6i0K9crZFiEQZBCv3q1XoGS1UsNH8Fa0POIOAJ9WLWsxBWx3ukBfBK1uJ8SqlevCj6v6K1MOeowyLISfoK19i7YrPiPJpKzacuzjemmUzjfIV5Hz9l+CV+lXnEIBupbnpN60oqCBlQ2kumUdJipALUE1xAfJ74EBWNmZqBp2mgRKiOulGK4RBb3UrFB5VesqUGSouMrslxv+vXrwQxvnXd/FG6ZeZ6ZYi7KDM0pU9VZs2HrW3390/b2No+5eXpudYW9I9qSlbUo60wyWHYn/WVe6vzqiVj8yDDke+4X71l2KRA7D1n1P4VXMZUO9RsMWF3/dVhbnIBVNk9jZQWnq+wqWFVdRMry3E0QGRsHnwTI6U4GuLGCSOhb2KkRIFHHJoJn6oG8al68GzgA9QjX0npR0SYd9ELvprSQrECEEIli98TH5LEY8XeFWWYtCi6KwybQIJhUtiHSY13UfnwNEwKZEZWOeWbuokV7eQmYf1x809jJIBs/GaCRRG/yllWYNjXkzd5pbP7089nPvIpGuuGI5nyreZ5ih6KUwm1VqowrSgpA0SVVcexjJDIVFEW3wCiLyMkFQjE4oi1ql+/6uB4WgH63PL39f1qhCtne+V0r+8VCJMD/skuIbaeg+o0crSOHrqemFT39kqUljESrms+01FC7TJGkns1EFNYsUygWuVpS/VvGPeWVaevEpqSK2Y7jpZVXil0IVZGiRpvb5iEi4EQENnNiPsrp46vSRR36ybWlXMh8VdZpWWYxNnoTKLqRzdZr1IbP6wySrUal5ESKLfE4m3a+1d5Bd8YuDDjjFh99d6bOBJHJ9XQPjUPhbUHhxBiqxlfK04l+Op5ceMkdgPKj6iXQ2w14+8OxcA4d/SGr1w/DAZ+35g5eplX1R6WITBIVkWuV7CvbHCcXqrdfRX7TDrmXq369Xml8VuYTUUv69XsUyVK3p6OuutV7etMGDaU8Md6VfswB6C/dqD1K9tXGWtp8iOsP3X7GLkwDUMVx1Zyk10Tx984jubcetX7mQdV77d4BfxhpMjA6PcV96MQqCQwdW2169Xvk5CEG1QpgeuBJDxCuAuyhPohJAr6yB5sM63UeiCJc2gctwgN3ytP3TjdUMNwb/UYGOK0NeQ+YcweTsJCyUtE8vh6OOmQqzao5mEGPJxECSj+iIo7eD2cFLsppVwxI6mafjgpTNEYzCVg+3o46cypU3bg7ZxgDysdhV/ZgPQH9dFEgHPJotWv2+OU6ESGmlgI1ug/WpFKPV7XsIxHpYFTAO/AzThc49Fp4MqNabOL3+dRagQk3HUEjG73bx6nRuwSqqTDkK/xSDUG04OFcy3Z/BGIFEXmPw3oLH/4QJRyAJZa81FrbCAahAwJF9Z89BqHknyyE/QHVrp8epuhbWgZMRFro9RYOYDLgClAxUdEOZbgvndf78qJsxFZAXxfY6Z4mYMfcQsv6AFWmFc5FGirFN+YiQLcGGiOxBJbW6WRxCGZlJFlyLRJcSC7VZuCERNFg4REiwLuaz1Fz+a+TW6GZbxEzIyMvqL0jGWwBFr5slaF0TJYwuafj7U2dG+rCX4lwWtpOzBM2jK08AJo+hkn7aogXhg5nmiYtKtMEJUaElvHCvbphJgktpJAwsOoEGtdhklyo4BLcj0ZJm3S9PEDqDhpGSZtqrzkRp96PytJJmOg0Jk7vGESIVJ4Zg4JyPr4RkqbTP3Tq46ky0BpC57Hmjykly6jJAILMaqiL0FsPcknIMFIMYpllLRj6RXQgPZCg6Q4LEGdg+nQE60maP4jLj10a6vZC1YzTHPexGrGDTDY8d10E6vZwZT13P3EICm2KTb7Tj4ETA5WMg4tTEIqqBBbyc4cIZNs5QF7GyfFyUTkGmGXYXkwTtrwNsSUnQpCbIOkGG0mLelnG7EVHfDLcCK/MGYbKOFbgPEgwJZe07qSVkq+EVH+/AOrS8Ib1ZEqgNkGSptdCRKX0nP/2I/QKJZbmHeFcRFbY84uhfgTBmA/MiMyNgdW/hYf7UdoBJwpZHpOia0xwU0SQApH5P34jGZR/CQGOo81+3EaUdmi7EEsxn6kRlPQlU3zavxYjcLq4xX7VN60H61RrNTAZwHbOVfvx2uE87NQbaUv8IiNJiW8sR/V6yraj9yI8wIpT62JxsPqQopCQoGSm7cx0w6kTMxryAmxDZjY1MkADdV4RwMmUVNRWquMp23AFKBgUNER26huYkWp4sJ2aEltA6atDKmCJURRA6aNmxenvCJM24BpLzkoN/5ixNaSV8Qks08nLYkVXRShEVVv/V6xrmxOtXxZqr+Nm6gAmTjp5in3D6wuVCaEyz/93trG6qci4+gotA2byMcqRdQbuoe13YSDG640Fqhh047XL8Ssm55o2EQ5iuIAB1fMNmbaZAziGJucJrYBk5BUoXwU1LENmLZoxTqF1GJmsZ4qPoN9SD+2jjhaNFxbt7aSeOi6cArTxXiJiBTG4CgKtI2XoBYiSTlGkJsYL0H0xV4w0tYYLO2zCZExUvq1lSQfh2rVA+zeBksHXxuF2F1fwWDp8Du2fJ1qt8ESiWLkcpDdiHha3EngJAtfb7IsppChK/MI8bZ4AobYqe8UMkw6GPhBHYle3RgpkGJjP8l6+G2MdNgJVELGtryNkU4R2FqKCWzjoyMbSB1O3tp6ws5AIZbSGrfx0SFV/1NQFoUMkEgx5Jesx3xzAyQQA75CpWNt46PYwQ/5heSwIbaauL4UeWIP2gZH7CidAtyDb2AbHJ0aiz/OMvEy96EGSLgUP508LkDdBkki4YrDR7/cP9aWcVlyvTEIBkmKGQNkd97E2uKU2mTvaO4aJB1GLLbJeITe3rpWlckDfBkygySIZQqBdJVPbIMk+StjAIYCctso6YiKhhRkLTmjpFARSjl4PZBayUb+EO4hwobbIAlOL3J1SAVN222cFPO8U9eGxwqx9Ww4W+MoKY/dNk6isiWOIiAxPdV6xhuTj7aV37wNkgLtqvB3kcS8DZKgLFPBWJH2BklkzImLo+WvrWZn+6B4UdobJMUdam9Kh+WJRkkEi2HLyorSbZQEKUXHFSrVDZJCtyHmPPljtkESudtk+WOaEVtHcedVsekgto4xX6E/BNfDB2UlSeH6qlwaiK3kaOnfFKXEMUI6ZL2r9ISldYyQFGaJT6zaq2OAdJRzTBQKFHEMkAKhUA62Ezcdo6OjpDtKr1p6KI4BUtiyBV8Ss/BesapQp8SUS5xyDJBwlZCroapi/YEB0iGfIm4/hVmPARKUdyz3ozSZY4B0JqNAKiGY9RgdkUdYu2jmGBujowMbCLdZtwjrGCCRmjYpfwVfil7LAOmofBqiqeE3tdKwHkDMplKKY4B04DeA8rDmK1ljnIGBVpK17BggxcmEAvCRWRXHAIlS7tgsSLYcl+7LGhPOj/dRttwxPjorc0XgKUFshYEr8RlrvyfOY4h0qCXssEKIe8wQiXqwgIqf4uH5B9Y2wFsYiBJITX9gbaEDmxx/u97H2sYuj09syOtxjJKogSaa1JRZc4ySDtgURK4Q0zFKIvmPGbcUTT2GSIdMaO2ReqTxEblykLoVmfdjfHRiCoVdw83LexsckX9UKFlSIsMxOjrgCab3zJtYyzAG8dRWlSh0jI7weNXMEOC9jY7OEXCm2oP3Njo65Oxhlg/b9TE6imEuArFKujsXHfFTHKQbpz3ibjEZT8rI06+HxTHbNk+suVWdi5DiCou1YjzOvbJ8hcKkjpdTt9oWx0YOd4mYmc4FSdCLlspzBPnOBUmULlG2AY7n1xckhfiQPhwg7JI8nouTyDEgS58g8Z3ZwxrDsMA6ENHEGdY4Hsuh6eu3ausMK83pivBR0aQf1rgAlZqoi+4TrDFkHVwrw29lpUkdjHHAYYDYSoOty1GKLdx4VrocFdvhd8v7TOtdCf/GR1NS/plWmkxt4v3novozrXScRyjDxELeK9a76vSxqPK4D7HeVCTH74ZcNGdabzLiyJ+TI/tMK11xYEz8MXzmaY2pM6ACcKdq1lix2ALVJMtlWePcTTnL8SbL6jaYVQ5hc/3a6lJfVcgA+yS2ro2lTOmPJtyyoo288S0XPWJr2XCsxRjUJbG1hJJgKN9a97aWYVKoMVCMXOO4rChBlQLklxVZVjTmJ8g+1EW8rWgguqq8Sa2vbUUJ6Q8tM4mtqI4pWFJmzbaeAREgSIWwFrH17MpaP0CQ/KDbqgIDcYkPT49tbSmsUR03h76zrS2GrpJ4rK1nW1Xytojuqn7ybKuKvz12mSMnxTlWVVnKsR+52v4ca0uBqtKktckca0uBXXo8RPJodQfnUuU28+rH6lJVSnGfavXOsa6T+lROlbJrx4pOjjLifrwG7FhX6nOUWnQ5286xujgzFp7KJJ20uuKkib35iBDr+6xv1kwdhcjE4/R9VhgKQDB0u7MnLlnpSXJfAMpPrFvfZ61jpm3mbrnpFXHJmpNNsCGOKKKy/qw6NG0cyZPx7fus+yLoG+ZNdT94lC2H9bLLBSe59VZRiKi28/dWnMQRNsukjvuKFccBXDiwXbm1BsszVZWiGnKrzIzBCohyFyek5fGV1wf3h96/WF8cDa2JMPaOXrHKmyAd2LXlI6wyURqF5kXe+BWrDKvYIICVQ1qs8lYyIbvKJdn+irVW2tbcRYdAsv2vPD4LDLtxVNcjqrUmKa5T/S5Oyq9a64NIOe2XNfCrVvxw3qe0d+2rYLXusZ0Kp6zlSVWte2wjRHlikmq4qnWPObupgM7pWa06vsoAOUcJaOTTWn5I+YHIwKN7UZaCD3BSficn1IVZ8kLE9gAS1ahfnAVhNryrlPMmj2q1vEMLw1y7dGvfBVvQA8T/Nvhd4m7xlFd1JRfdd9FWyGH+0xrTm164tcFlGEp8pZJfpYuSosiunynflgfcrhRBiAr1a9a4cL6sHJ/Mv9qtdAFxbvhGji9ZbxABQcHZUm69CwnUZF4czyrDL6wiJ5EqvyhZcJZvHTd2MfHhZwxWSlqjH+3kZxBG+TcRQBCML3kEOOcXgsFDI2kYFuY0IGfYrJHf0DgsPpJOm1Ol8+QgWk6M/8MmemQMxqACEVFKspx+hmJEj4tiiCLt/AzESuVsxg4jMsDPSKyQ5kIcvaSdMg6L7eAjFJClZeA7y2EsIuGuem0YiYXN7pmLON4lK95U2QiPoKyVsRgMZLE1Q/KktzUYC5zBKHDm862MxsjULioLmcOXrHsXwRohvbybddevcZOt6j+x+gENwoxSTSI1DcdCvyKilfKtO/KGZPibCMXjkPQlj0AnkRg2WXGXfsZl4CPyEJl6/hOPAOUpVLyKK4yErCsXidhW7pbkVn8oOxonRv7euhMhp5TjpN03PqOWPwb4azP3LQM0SK7gCskzlsbEIA16OgFAlVXlJes+si7w3O9lpFaY1qqv7pfJ9DNUw7ZXAvvFDJKf4ZrIPT8AQN7NeA0K3AWFZpLgfgZshTpNEge+5u9o0IZblFSLsXJpG7aJK07B7XyCtZ9ZQTO+FFvzKdaaRtjgqmHQBghlNU5FzEJuzeksADFMOf60Rm6FmHCBczuXkKEbpJyxdBt+C5FNW+2liiSlVEtutYmq6EpOEUM3MaBlxXH+3joTxyMtG76teyvrjXMFb/fOWWIAV9hxYx+GekNya70rZi62r+ZZYggHez40GO3aOAO4WJsgYvy4GlsjuNgeqWPCKyNWaiO4sL3QQjA5RHht+EYFHeGaT76JYt5wuLHgTP2wvZcj2/BNhzri7kqaLSYPJ6XuEJCA6OQ2HDF8IxeGTNAqVrFiBvGQUzm5yN7aklvrI0Z66gGab2XF6bag2X6fbsWP+DhFLXz/xCCu0O8jDGCsJutiHIfVH8pwmN1/VX2JPCjODwJB5hQPudIKAsrLZJhVnJs0gogYTd9q+NIglQJKYb2zoVyFNoVoxpf85IZyVbgCAoh7n205qDOw674kg8X84uI1woszd7k4yxzjRHcxJvgLm+TWvTSl4H2igDfDeIjZ7SqgKQnWrTc5VFTifSt/b71jObON7WQtNsl45jFAbaAvawQXCzg2iDj+J2oxy7jqsQn1bHXiKKYZh1STnYEcRH0F47fYj1XnmY0FionGyZiLrUadHCS2rpX9kl4QMhKmGg/5xHeMo1ivY+wG7xU0j0Wur2Ka8S2a6yHOA72OwVslOMT9a0u51SX+AdlQfV/M+C1Od2D1pchVfmdDuNpEsQQ5T8qtNM0RGnVHzX9iCEcDENKMx8qPbPxWyT/4KDvRZm3WceYvHn1mbMqteGcOkZE5kzLfiuO+7NT6T319Izfqc7B2Izc+045vcjJ5W5UEpuKGbbXDiHGI0uarWuuY2l009mkkDNtirgCYyC7Wqxq2xeYRqBTfU05UY7YqbtmtIb+jZNhWoQbjLPAZ6JqBHAcgKFh5QP4r6w4P9mH/yudY9aHWFvJtSm7VIbs/0Jl3DYmBWx2yUGxK+XvrTf14wRuaehu1xT64GKQtzGQS8hAXdhdcD7qNEZvYJmOfKNkXwWitKszJKhcHt2nI0xMUFrGWVNZQrdKUZJOfnxPGUI3YKuk2dVw3aTET+ebQEjtUzzTmYh5ysBjQc448bJuIHK+nAk1ZQ1zMRA6VCImKRY64fCvjNBJmCk5n+bOL+cgJeW5CDJ1E0nwrQ7WqtB6gSVoOQzUR70HekxPZSK2yZcYeTx8T38mqb3EAkTMyfMmqkxmMZuu+l1VnOCj0Kjf9rJihnNgVteU724MUU5RTN6q0lJG0/iYpZ3uGeLDKJ5i3MlKDWR7EIhrqe8naB/qglACOtfvOBmuxB/M21KpO/5UHgUwBNtHbvMKIjaTNqdCVUIh5yzeU/6IiWTvf2eofEkhio1gr5dYdvx7WqzbvkYZrldwANvVmb4CJy5Xu3ojNKfegmLmcYkpyYfsquUKM2GK4yLYOG6kPb8AWhwkxDvf1eUgM2Bpno488sp13GpaTskPx8/aMNGZTqG3gfMo2H8tiHSYI2urrGq9BUj44Ac36Hn58Car2TQlZtgax2oWkCPhZ1enDiI1YGH6hlocDU5hDqNvUk202t3UzYqNaksLQTac1qWEq8602N1WlSCm35kUh/LZE0FfMZL45r9JTruz7dOsd+zTp0zXJ8c1lvpNOjlBJU1MRw7WWdMm8ktqHGKuJc5uQVr0FYsWM5kTLSKAIXWRXTWkecnAkeS/7TirTmm/qwkleIN3Xd7PiTeXHNTvMmdqcrkvyFSUBYzG3+VZrBlj9dn4kQzVandWqwJL0NlSLH8fWwDnypH7Wu0Fe1bWU7xsZp5G6wzyJOaVHGKfFSUw1U6PmqxqoNcoo6S6X+4yJzjcsoZ0Tr0LkxUznm4CACAWXm6eY7ZwGLJTEU12v9jFGayhHTtIe95WsdRfh7v6Uf1RMeL6BRYSzm+h2ixnPlZ67SZNQQlgx5XnI8fngR8nnGq7REhCOUbJxJLfKsOHBtwdoThWM2DhNDrGqz5Rba6pIjuJRelUjtjby/EbSn+RWecBMQe+14lEyYoMLoum8fLYvWfEJ1UmAy9dSyCzoG+57ubdqNvIxYuMh8LcWkQ0Xk6DjJlJ3ppauJbOgQx9HgzPRCNxpbtAG6wDJFmPl5zBogxOMvXRO95AxF3qYUsXVcStuX/IIyOV11NnJlzwC+PuqSMFtSIze2qIEUAzRUt/orZG/CJ4s+W5Gb40yMlBJmx4xAzjolzOp7pZzFNOjswNsUr+WkqKK+dGBPSRfx1tXmw2jN4KxkF1VEU8Vk6QzGzmiB7LL97L2cCmR6/L97mTtcUg3eFHUHctM6WQK01bgj7POdOnZbDIL0zXLDOLEa0YQ+Zv+MsZxcbCk3aFqeSS36gde+JOFP8Ws6eQDqJ0bUdL7voZyUI3D1UNiseTW/KjyOQzJJXMuJlCHjZ7vQMKLJp+hXIwSU190OJJf1eEtxdLdjjjmUA95pcA70FrR743jOsEO+mGKMa2YRZ0UPzKd9sxzlWnUtxol5Eh5yRnHdeDFB8eVvIDmUqcZxlDacbX7ynzqBFS2KPq2zuEmVKejSxgUjkoGSyZV30rVim2CBelL1p09Mz4kGEBy617EsIhjw9PBWK4r85PaueGRN5YDZ/QuJ60ml4EcRX9wxtZtz5dp1tVzaEJVVdOCGMXBM5updDmYRnGdYkjc9V+uBKO4LpKFnQm79xFWn5LReK2532Aay2E8K30WulaicRzsFPDXhJHSnQziIIGGmnSkY8qc65RLKnEZ57Tk1pvEupiXtjNGcVQuscVkB9xi2vWQd7mkdvbbMe868S0+GXRLWk7Gb9AVUJXAVJHcGsPOepin9/5Wl6lO510VsRYTr+O7pqsZKXZqJWb01uleC27NlkjmXSef5qtirpY70cTrm4Sfrn5ieh8zr0NCDt0FCeLZUM36EjzTnLl8VsXc68pAIXc2LKh6oRm7QdPLoRiqG8mtMiDlsC68eZmBnRpiukBgefJW1jrMikqfFKcv5mAXUQFZOTEo13qah32rUQUBvJNPN3yjzo/+sNnoL//EukNZRoXD+LJrnHXXWRCipe89xbpPldzjeMgXs+4zGXqpZ7nDZQgH1ejA26787WI69pDPru6fzSde87FTZLHpr1KVl1lMyB7yo36LdKa9TzGK65BakQjV81ZGcV2FuxT8ZGc8ozhKIDjCfcqFK+Zl35Awwz41xBNSTMwecvVchKOu+NHWnfL/gUdL8TCzs1MQ0j8SXafdSWZop4pdVd5r2Btilvad3pjYI2d+emO5vpPvAUpld+2z7sCNw/x26NFc7XFJDW5or5h3s/qcT8UVs/NWVp+9FlreI++HudrZHuJDDWWSS27dqXOFNahmX0BjOVqK8cIUDEhuxY/IAKF69kc3kAvrSLeMkp1IiznbcZQQ9SJzRK9qIEfHKo6c38pXMpCjsgZS2X3k9TVvO+kTEPkT8/YXNJCD8JXKHZruuu/h8CUciV+8ttIBzN7OsKrE6LufyRBOa3woS6f4VtuXeADt2m5maTGN+x7i4pFnVbobxdF2gj5nSXtXTOQO+QnUFHo9yavlHN/EherhNYSDWgZqDRbRVd8Qjj2RvqGBsfMp1r3A+6p6JImtOg54QuY9P5TxWywxGBEgz9RQGb+RrYEhJV4luZXGNwbddXVAw2zuSjGnlQLETZJbb/ywbDbKdiwmc9+kbhLQJdQtuZWG2qIR6d0ecqM3sjzUWS4baRq8YYs7x2y1oC/mcycrQrj5ywajJnSnAd2i8yw+FMmtdCNQq3402RnTSsPwTkuh7cC+Od037OrEEY4yoYtJ3VksKnAfosApZnXfI5NeY2bmGjNyG7QOoBLkTFtJg7fRlWAEJZS0MHJjh+gUVInYppjZHV8SlXpC8Xf8jNyIj4uRUR14isndKV8jEAzvkRQ3bIMzhgDAWY5KmuJdPx6YypJGyphN2TZsggRkbs9Q684Oj0em+aRqoneViNLQqN39xrCNCAVMGfWk7oZtJJEsCCC73aLmet/UpJOft9bwSBq5kXmC86rs7K1q2MbxlY3lm3bMm/R9ww5Cs9Pe3/o3esMpA6T/5vBfGcAN8u7xNWbSgdnfQz7gsqRiXybAAI7IAkeDfu7vrT4dRI5aYNj8GcNBpx4TtxFYldzqr29yTmyZj2T+dximw/yolYbmvDEcZMiEkgky+xHWnajw51iCGeAhTVIifp+XWK2YBX7TOLLCc3ucumUaeM4fhOJJsK2SW3Vl5OI3sUExETxRW+hdIKRRm1ZjOWod5MRKB7Op4OniWEgWHUq2LOaCp+s8CWj4rKffytrTXp25HTbeT7f2WzEnAJca1lr7Td0CQT+d3c0ITwEl1Bf7pHPLlPB7KLGSGSQbZE54pUB1MV+XCw3MC7+hkNOZVvzHxcTwdKOBFlJ8wZJbbyrLuuoFl29l1ekssSlcy29oHKcmSvQcylamJognPZm8Yp1q1Y/3s7zh0SJQIy2M4CgVpKI628hmC9/qS+RrkCkss2+iePb+ggfgE0liMVM8UWL6n4hMzbcavnTERMtMkfwqTtNv2l6V3A/MFh/yOtXvZ9+C/2K6eEotKcqeWaZezBe/4XJhAMvItzWCU9sngs5r37OuSeM3nTaSmUi7jlnjiV4zzXuy/RdzxosxgpLqkacrk8bToBsXLDzTeX9rjcsSBNVyGhi+iak61h8RbMmtNVEwiOX2Ld0sJo4nKWJAjHzUtaeYOR76+lPF5WLvndnjw0pQUDdkH9xr2Yo3uqYSq5L/2hTyW5C5slnuvJUVl5eVE6qsmxnktzZ5Wvik48MU8iEncZ+ddeX9rbg6RdPawCmV5pHHCUXq28gsNvPIU1xc5IBX37FiFnn5OwgCL3eYKaaSj0vkm8ApqiCGueQ3fvE4+2h1Sm6lRTMCNpfP1HTyWwycDOtwgMyU8nEJsiyO0/nBDd0gpaH7Rzz8nsfMK5/l0LD7nW/6klXnDEHTp33l1p3AoFrDdX9Agzi8qTiHWTFqi23dCX/G3gwt5P0Tg7gpovKj0iBf8ghMJlDHhBZf8iCQhs3xruXCNY7Dk1sgxUiIbL55uhw2XMrUkd1BM5YjZArZUWb+mnAeS0zIirlV/RceAIXOIRSw19rE81vEkhQidjnGzTxPr3hyqslt1vsazVEneJpSFbNhuFUnk7aJsMJPN6AjobURO8w+7iagh4ZtUUPxatuKSegJpECk3bLBTDEL/WYjAOzb0BjNwSjDbgmY9a2sO6kmZEN9aWsM6JQkSaVwEdw3Df2mywNpKbjoJLfiVBgcWQF9WEM5kWsUfRNvqYZy8C0Cy/o3bFOM5uhHUaYYT/MpVjz2ePHglze7jeYC5UAHBmFByq079ZTqoKUhMZLTIRjcWWfqZ705uuNXVwTSdPSq3YVoqqS/1Hz0BBM+tgPvXcZvixqhxVHDnk/T0W99VLYiOtjdLvHdl2ILx2148qUM4eC/pur3D/gwiiMcS9r7cGlRMTk95QOiNWrnew/avnS0ssbLhTRLPQX27ElJn3xb1X++JE6FwAD26ZitfgNUmXu3vbe56ul1RwPrfhMlTFa/kwWnKM7/3UsehEJxsSim1M3eYA7fl1z4NRvUG8xRQE9B3Y38mbOeIgXqYinp3X6E1Wex0XTYPRmKiespCsYFe26eiZnrQw4H0if8ef/EgA5KCTylNw/P9PVkmp2pbrfals1fT0YCzkoCcXphozn1ySTVvzvb3yz2NNEritO0+Z5u9VUsrPVwj1Gmst86/pIamUn05rLfnENhSCYzUnLr3rSjUqqiRxjTyel3utguJbfiNIOr1Fo4/8+U9uyJJEf1m7JtTnuOYiL7vOcdk9qTRMmhrrMD+VbWHbIR7NGZ+SdWvBMfxwmtegYT2281O4fyp+78vbWmdqmpmWm+krWGxmpzmtbXMJ6jEJbMmNh79DoGcysrSSd88pJbYzXXwXWvsTaWo2Cgsp6q86lMbC9PuTLIXyqJye23Dk5UydSacutMbtYQ3Ws+xTqDkPCFqJtDMbM91L+kjhP80NQ0nCOohk+lp8PP5PbY6iVUU25BWDHDPZ5DtWOjxaTk1hs6H7rOixepmOOe/TRAwCfWi6ud4dzKVpdnyYzkU6z4UoomfY7yxaw4IwINHJD53s2662/ADy3l1h1uEepainOSzHpPhwMQIF1gNVyGdNQrUYc30rlo3vutxjmM5MxhNKRbClRQJpcr2ZBuKY+YZy+bHkM6yGCIEJUvp5UhnRhPaIl0HDk1Af6WNTgakvwTKy5GeAx1z99bcbEYTFGZSW6tycuo4jKS3GCOGn1yPkP1lFtrStCpj0x3nAnw6VpDNzaSgjV6xnCLsyhF5Zk6ZA584Ca59/CGXiBjHnzl9KrLbR7ETYRPfduhB51qsnIAjeNUVYiDJoPCZsOnZIWuwcSyNQ+N4AR9Ks6pnJ9GcKSl9Wzwq/sYwVEy1MhX7MZKJsXfJMo3NedNU2EEt/HOsTJdvF7MjK8clqa2gUosNDV+yIXGRxJIFHPjA7eOAvR9532sdREDHE078vfWuqqIj00jtbDWFQ7JQ4nv3eBNjo+zghMTqXR6JSO4TAk9I3kniunxt/oaETn8qr+FEZxYzjhP6VRtfnz4f3AITFgH/BfWmzh4B7sqAGOS/E3KFMGZ3/nSRPkkLDQ47NdK+28EpzwaMjZzthnAkU0yVvYevA83iCOdYlJCV3MQDeI2RKx6Lbm8zZQPTwHtyeHJth4GcYo409qw59ON4GKcikJF27FX8+VvgpRbpCupnxGcIFih18AzlEZwxLGOmk2vfDGrzhkOet5MajJvPmkfSmegADHkJs7f1CfDXBCDfyS34rRJjUWnWlM92tT5pINAs6SUNV+y7gP/Wef8uSW37pASHOaiS5jMoU+N2Rwqu0ixVadYRVDh5HtZbwpi4GArdhaZRV99efETrIzYmEZfmQmH5pqZEGQe/c1RlaYXbV1CgGIufWLCRQmuWaZkMv1Nb5YqsuT6+U+sOl3cyQYXm3BesvZLrVi02Uhu1UlVrZTNrbulmll/A6AWPAhqg1tMrb9F9bVoJdhTF+uu3DMoT0bz062+GmIr7KdbGbphrOukKWIOi6HbFqk/lMdObjLLPjT6UznbuQmaZp9qVxq/Ey3LW1lxEouxcWpMVsyyD7Ur8cfJ4VZya81ibxQ+az2bZ58+g6uKyjZfx0of8uXjn8PbuLn2YRCgNIQWVJruhm70MIN6bmSWgNn2aQxDVs9JIuViuv0NaQo5V7XOlFvjo/gLLV0u6jbhPq9C31Oq7/wpjN0ExjklPX+tafeJslLHDnOO57UR3PlIhqHqMz+UEdxRueAQOJf8WM7CgdnBMWYT8LMxMqq0t56+VHwJumR6IylvyxT8jHHYDNrczpQ3yytdccimS3m3XBmjrZd8K8M3jubwzpFEcRU0gqMfAHML3OFL1r2oEQ7NtFNu3Yt2o/qJVLCYjx9P5FE1jdgfign5YXujn2+j3Z7k1lrJSZ1zvWa04VtMnxrjRLps/t5aq1flR3WAtDN2S45cimZcJWVafkgX1Fr1LjNDt3iXeIhIFvNO1phvqsb3+0Iic/Nvbf+LgNeXt7LSscQ+iLGu4TN6I7k8tqiOu+HeygCOemBWDvUtkltvYk4NKsRcagZwsFpRqjXu+jCAgyO0oYs4g4v5+Tf1gRyb+OCSW2tyYuiHWx0pMkn/htw828PcV7XWXbWZqiGQ3FrH+RlUNXK+GryxuZNHd1r+3OCNPDTAHhlckltj+IBi8Ah53jcyeDuq9/4gWffLGrxRx4MzTe2Lirn68brGAo8dYOX+Z+x21NEHNoJ8V6tMxTSev25nran6KQciwZUck+JLVlyhV4beuXsm7AerVMWx72QzgCMBIgx8xWfpP7H+NJafUMTk5DGAO2ocAmGhwLR5+zdVV2SWxiqXLoZvRESOikwdfDZ5P4n7ZCiLKlFyq69+8sR604QYvh1NnUPb2LyPFYeqJdt0yqgbvB3YwQ6kkDk5Dd7EHEWp3O/7Gb8dqqWayuvyVtYawAf16x1Ag7cDY1Us1q/nfDZyy9aPYZ9X8ewxeDsgcHaHkQNu5EaqIJHgmQmy5vLfqoQCzs5cekZuB1ukxuPK6DebP01a8BuHHrqP6fzJCe44HmPaFsmt8qGlDu1eZOpM6J8kkVDmiIK0mM6feQLVABT3S/JUmS2FaUrcJOXT8jrVCr2dlC/L4fQix0trxYT+JIizgulFlnody+lxQw2DMZYp/Y/6CTIS03Fe0/rjmCAfmdV/ncmm9hc3AGTTKzO7zO1Pm1Y1p4bZ0XfrvoS3VefWz3ez+uxSNECQ09gc/wfncqcKU4TWxST/ISe/iTBkzYdbe8JsJNNkdac5/gMGkIUQ3/aROZjpPy5VahnwHutW1apDpYb6VR4bc/2rOVndSi2+1sV8/zRdpiybPKrip1h1GlJ3ComcrGDSf6VWLxZNM+gx8T/Ev+pm/o18NWvPPCQHdDjN1eT/lCnK8dXG/RMPQFPruoB0Ob2atW+KoF7/kB7ePACwuXOsV8+Q4iYAyuepma98F6cbASiGAMTOFpfFnQBIOiYcTIp3Pt2qd2ihj9KpJbfeNCX/2Alu18riZgC07YQ6lGfqszQrTp52HPEo5fJbWXdlr00QhAe4W33Cc5R53OHq1l3UI6IJqP4Tqz/UymfDMyO5dSdqhftNLbSK2wLAPjBF1fTd+1j3OA0XUnQzDcmNAYgikrd0Mmyff2Ldp4acZkX5ttadTXOSmZk2pVtxnOGNElWdUdwfAI7DDmaWHcqxGlackiHqFkqKrbSCPUPMbZJb6ZUdTaq4SotbBByipa1/AlySW2n6OlES9ipi3CSAVBqwLM1CPa2G9WYEYXR+eapuE3BE8B+YUo2U7w2tPcSZNEuL97t/NT0AhBQ4zrdc89Paq9q3yVBJbvUpc1iyUTJD0+qTTMZzdZ51r4CjoB0Zl7Plz639Vj9wkum92Ka1Z3uepLMpjOl+AbSUoFgbc6XpPq33oW8NaRGXK6+4YwCBFDxD8Ve5QpaVhg01e4nq98tKH5HxbVX65a2W9RaN41RbLMmv3orjbSVyapwuflPjBFwOraTiF8DRmRnKU1I4/CkuhlN/QWY4teF++vIlnJicEnOFXBAHC3KDvl19ke6fHF/CcUew6dnSC+I4cEEdsXPpXAin2tI80g5vixfCHcruyYP0X1h3YtWBl1qm6LqlwOHwQrEX0Xc/2uozY6h2TN+j+wocscxTppXTZ1vvqmZpqpTwO1l1doMxoXvRAG/rzekGz1nPdXisdBV7GC0jQRK6ZM0r7Y8pgFPekBsMEHPA80ntpabPsd6VnVV5WhJb7Sa/OBnhKbfO7GeEncDt90+sNszGvM/M1XesN16WIsIKm/BjvRvM8kQY5bZ2twFOxcQVVMKbT3HHgaNsIrx/TXbaLQdI9ocroylT7f6JVed8D7eDFo57DhzSa8Lo46S538N9B6CZnuoHlql7bjwAr6+aMzW1VSpuOwDtNT0wydBcklt1UQp/eGi65NabiqiqNNP8vfXGj0hwt+q44KYD5H3CB4wb79pXNx44hCVgAj1qIlTceeDgu40rmriSW2vOQp8aSUpsjSfZgIQuBCTceODgGSO8DEms5NYYXzaURV1JOO47oHx8+ul+X2pmBMfhmNSBX0mGOw+Izbcqy0Z3MoDjmIEb4DKIufUABlscztfJ7MYDJC1ClKnmL5Jb4dh1SeCKU8j14rj7wGEj7FPdtfR5DN2w0/BS0NJEcitNXxQqvdXfqrgBwRG7BuXZw7kZbkIgj4w8lxlXcBcCSOpgCZ/rucTcieCQskvvZhq0+pJ1J5uWDicJuNyOAMoDwjIU6727Wf2tdLeeidduRgDzBfQ7ZIo3/4W1P2KCH305i8cdCci0VHLFybpk9yQIeQA+ETzfdhDFfQmO3IrjJBvbveQxUGYZXm45Qt2cgFw6kGJVr+vi5gQccAYEADQ/krxaHv8tvLBmX3CHgrikHaVd/he3KBBJVtFmbaojtymISxPPEMkuHkpDuCrCYCqRtA26WQGHEuIIR21m759c7UUNy2GXCvT7oONLEF91BTeRG8XR2X0So0z/lNsWHHWFlsM3DZ8xHHsAUaiivozFjQuO0pEqkeuZcuvOWYoszUw8cuuCwyQRQWOesdy74NB0DqLAXu59rDXkKmE7aXR8tTZ6q+RuwYH0OSDvDgaHak8aSQCVkBu60VGJ9sD3IOMeBgeCnUpgped9DN0qJ15YSeTccBeDEFN3Tj7kyttbaWJ4pAPlr61ym9rx2QmuCgZuOEBh/flyUI3byECA74+CV8mtcRedK/Sj1ti4DccvPTLXq3F2QwN6GEPRB2+qpqehW6BVlBYWlNxKk4WDi+PICeBuBtyDKm4crP4Uhm5k9saQ0HY4H23VqWaB8r07WOa2BjhQcGNRbKdladxGqgtJUPsR27m3wSFhX0X33edw9zegnQx5Y6R52DQYutWb2f19qb7BW5XjiC6sJeVWH0BHS+8kBHWfA9IP1FpmZlTMjQ4OHYW3Ov6s92irT1NoxY0cXnS3g6NYwGz3NCFdjOCgmCEiSc605FafRk9Fzen0vQzf8InHk9elX3DXg0PFM20T9qNFcecD+mwMBcHVFLG49QGpgjEoBMe6R9gIrmrfIeLtYIhbIOBnh3VJ3f0kt/oU1S21Z7XFMoqjSm0Dro4gpzshkEkWcwvPhHz8boUQ8imOlZIuHvdCoC0E3SA/FbFrhN0PQR0vCJ1/L8zvnggqLu/Qc0+lULgpQsgrochR1Q26uCsCXZ/RbXwvEd+tEQgkMHUI7uatrDsZShRaJ9Z2c4SjFq3w3mR43K0RqOgJMECtus9R7o2AIz8z3xRRy0vHl6pQB8nlyI3kMGeifJgKxbg9AnRkEFC0kYcG90cgNbVxxMH430cYyfGdCIIz9a/uRnMNolcSIIuDtW6UIExF95ueVSxukwCjAFUp9SYOu0kCp3p189YZ/d7K6hMPo5NBfhPjOZG5LC1tqW5A1xIlsBtKRQO6Rj0uvQoT6LlRAuckqopj+FU44FYJIcdjT+GWgvPulRByzvj02pGTw50SQr6IGijLR3JrTCgUVq0MlbhRwlHJYIeI6Xuvao1JjV3jDp2xXFMj7QZgQmwcBykLJDzZIqi4WQI7YxHPbEbF3C1B8aqqVoQ5NYzgiNyBE/DBSW59u/iiyzXtbpigZLejsk9tse6YQNsXEXTQefZ+SeO3rPn+RHV4Z5nxW1L9kRSVX8HgjZxHmsTpWODOCaorhubzS4oVt044cAQTUmrH8N/tEwjH4QePDXd6rhq+NY49UPtrV8m/svL4laks3fvd0PqTIh3WndQq39BDkDVDM1uhF3dSEDs0xupU1567mwJUkvivYFqfvpuHAPKqqo3PDzKIa1CaNXK73wI0jmtqv1pUsHKfZSjH7YjyoJrkHod5cJmukvFYd1YQ6VUTuZ7Mu/sqEPwg1Zld3O9sNAffwEfX1THeO3sQqNom6lTtjnN3BWr7KG+lJ5vWg9Ec/kylbWctv/srKF7a6EX4aOzcYEGdPHFdru1iQTdZOCpEmBxQd97N6lN6SxL3nWwGdeLzxmmTHjG3V4CKGVY3vosWnjFd47jK3vP8je6xQC5KVRlns5vZfRYOvArii/zuW1n3A/ClSCvfyqCuEW1cOmbL/BnUhWkioEQsPH9vrQ8hv44x1f0N6jrVw1W9uvy2BnWUYA4MyHYhtpsuUAc1xJ22Rj59Wj5keGfmULvtwumi5RHltb6sEV0XmSekHPM94vhSPI3tvqZdM5zrlGSQcP5iw+6+gE8W4if6lV+84Q4M8nQuGIWv9TSo66SVQdJ30u4Y1InemScVY3Z3YTjKJdIJRtEj92DgRDOIJs8M2roJA7/DtUgKRD7aunMoHuLH1ZgYznU4h8jobflcwzncS5BAwA8uubVWtR9cvnodQ7ke9g5/auAPaWYcR8Mr7CnMWHf8jON6AxjBELPzVtYYJwFULl97f2KldSrb2S26uBlDMhErWGW+Z3djONQ3wED6ZTa72zGEyQ1MRlmhEj+r2zGQil1O9gFvklttSE3oXiWyz+pGDCGnC6eaAy/JrTdE4rRpUBJxdRcGSic4xoGhiuRWWvH0qtiXVKhuxKCmgbAs4TCT3FoPdQ3rTUGZ6kYMcJhSYYWzZUpuleGbqSqH38iN3sAvWOOljrHVjRgOUWX2z7Fu7+vqXgyHwwr4UI0g7iUrTkMHnDit5FOsOCFy2HvkZazuxQAPN+xyajTqW1lxMC1nhHNfzIpPKp0XrUyH/8S68xdkgZa7Jqs7MlC8imHN7mvVDRmAp1X/Nb2u8VssLSpDzv4ueKhuyQCjGoHLutQhr7ofAyWTR32XT9HUMYSDGZ9uXFPH+upODMyBj4MPxwY/wprTTjj27tgd9WmN4uDwhU9IjFX3T6w59dIknJVLe1XdkIG9vKoltxosVjdkUIN1MQjOnBDGchB7TLVaIt+ruiEDpGVso6Rel/t0wzmq88gvjWev+3QjOra4Tj7CSbG1h25tQkTRNEsN6OTzpTpn5PwxmqOWOY5lYJ28z9Wbal4SCda4b3Qsr1BGMIElN5ijY5Pqj7/jhWY8N74hOkOSPiWvlkN0TsVL1Qc0khuKCHFMvttJdUMGaEYmRW/lrkHDuEEcr8J5sPVhjeGSrI+uPW/8DONg0IFOHrgsuRUnlYWu6kL61a0YOCCqzS8DeN/KAI5zu9KQ7Las7sYAx9qkPOVc+2b0NuSTgnC66oWN3tTd/Yjw05PXAA7iDRxDmGM/xepX9RwgaTLvZvWFtqCmP5pxRm+kVjdqCHZaS0O3OLGr9FzcV/fpVr/h06vUM9kCGMCJZIMsR1XhVDdkOEJ1nNFL97AYvdEsbakuKM2D0RsVZToVqGFydTeGwymETr5dzvfqbgyy0jgpk5mhuhXDgUmDGEL25qzuwwDxCo50PddaWHf8nKTpr/4uWXcCaPpmRwoavVGiO8QbNzXsRm+DyEy2/9BbGb3R9Q47CgGs5NaaigRoaR2ArO7GQJFIXIk/LJeNu7obg3JqlSZabkV+dTcGghc4GiA90qwzgBtMeM6Y6lVQ3YpBjSEHTKf1bUkGcGPSwI1deuuLGMBBIcKh6htpzIzewlouAoS9p1E0dIMdf7D9f7lPGLrRhpYGqKqJqu7DQBMc2jx3+pPdNzJygwImvvmioarkVhpOBnGSvD3K4A2XN0xxNf/AWpOmLV7aos9q6AaxhZKlZvNoGL0NlUpkvNyXrDiEInj8wTL5eIM4WkjHOZcWQzJ0BnHqA1nkkZLyRnADusGadDe+lZU/melZa04hIzgwBccbxl9yaw6YZ3+raeWM38gBBLreJWv4Rhch0uabKPKqezGoe7EiRypYru7FgGsebzXB9muq3Y4BBgRIYDmWbMmb5Y0smTZ1rK7uxXDUYxxnW708S9W9GAgKLeXuasTdioFmo9R9tGr6lepuDEeUFORVr5EPv2pPdV2H1uyep6u7MdASXf2VtnoAVbdioBWT+osGvu6SW3UMOwmnuRW5CQOVfzj8w8I1vZIBHLwTlV5e/r31ZjQniRp5e+tMHjmMeeUSPFT3YDg0Wec0PVWnWN2DIf4d81zNu5c/hvEbLmJqVr8cc2M3CCYmhIwlH27wNuGMJZNd4aDq/guHYxywuYrJqboBwyGzoeGar9pn3IABQhTCaWQf600N3XBlc5YoNV/T0G1yeoeQRfXv1S0YjlKV1Ju95ntaY/YkKunOJRqv7sJw4MM9JBGIi766C8NR/CQ2BhIakRu0kaRAe/Ui5qfqNgwUHFDsBRmMVDNoo8ZzqlFFDqkR2wQ3wNRcby/X6k4MZBCHnQvrpfbq1Z0YVAVFaAwEJLm1HmSkVCp47o7kTgyw6fNt8HR4sRi4zZFWvJVb01jdjEFEvDoWTgExd2IIeSUIxiE65dZ99qTrXNou3IlBjMVwVwbg0BgauIX9rbjsam/+HAZulCGQLQPBgeTWnUZdJISupuE1cNPuAnW5CEGrOzHQ7mbCPr5Xfj6jNipboKLf6qpX3YlBfTUaE+mTZkZslO41aDTazYSt7sWgHEG8olQDSm6l1WWINIsb661uxAALP8lvSoWV3Epv0eXiKMlbWWkRBJCpeL2Y1Z0YDrU+TLapUsTqTgwhV1W7YKnk1pt+4K3nRnHfyqoTI6Uet+S0Mlxjb8a6oKLkVlx2ViTu+XsrTtI4WVDTMM4dGci3qSoRXG/9GbEt0WdXpkI+ZViuXGKKLSWeFnct/1gLy3davgR2qKSD+1sZs9GZW12WRAVf3ZZBvZrJbpkidtSAGbPRlYlM+jHTtBmzLSjYm0ikNeGM2eBYoNyY7guSN8sHGd/Qq2q0DNig6oL6djhxq7opgxoBqqGi+zVUN2XILtL6xaWnqO7LEJfkR8INmy9m3ZVcOekTqAE2YIPUGxqH7+5XBmywHHDWoX7jPsKYjZIRzkJV72TEFhYMGszGAf++rkEbqIXS8Coe4epmDAcyIqIYIGw/w8oTG4CY0KWN1S0ZcJBgqVQYJ7k1bwrDqCW65NY8plRVtzX7KdyS4axOv5gpNwZy47alrXeUZHOv7sdAfLhRkTNEzl3dj+HcdCjScDV7jNgIg8p99r3lZtC2lKTYWKP5aCs+xGpOHC9vZa0HdRJkyR5/coM2SsKoaioq8anuyEAGDNVcHDbz0dZ64D6HPeWmo1d3ZCDeR8SfhMopuRUP1VBdBYb3T6w7BPp4YfDx60HuygANL20llnqF3EtWX7wThHGlprsyqOCEyUl4XXKrjxFUo7J8uFVfdLebxDzzfa36kndmbrMXVPdlOMlFSzzypgxWt2Y4VAtzZAa9+pIHIF6MA0GVGXBnBjqqkslFBUOT3Jrz2E7ro3xfo7dstkr1s3cF92U45JfRSO+o00h1Xwb+CccU+D7lVh2ak6NDuMTWHFACA0miBrdlCHlmkEBsfHUzfGPZTJLw1Hi9ui1DyGt6F3vTmxq+4ZuBWeUTo211WwZiqZUc5imKs+q2DLQYg/UId4M0MHyjnR4Osy83KfdkIGJHbwiyQ/L+y/LKsZfNWaoZu236ksWSheJB8mP5VL/ytfOjGbvRVIu3rCoxr+7JoCDx5Iza8wsYu+2StYNhKPSexm4QybMxbhF+VzdkwANPDQZ9o/T+Bm4kRhCE6/Imuh8DHNe9qGnGpZSp7sdAhgmgfn35B9a3qi5qJhtpdR+Go5ZhNNsSM1F1H4ajVliHgCpRo+o+DCQ4qZHl2JfvqroVw1EHIxXbVq8fozZ68jT1y+le70Ztu+GHW/Js3Tlm4Aaq4pAQxllja+BGp4MG9nBrk+pWDIdeGFSGZPu26j4MdMJV8hdpRv4Tj0AT4xtUDncPcjcG+EBpgAQthl7A+A36eSKWZJNI7hHoUKqF3fvZAuM30tVJy58qCa/uwwBBOv23Tp4I3YaBXTEAFCxTK39u1cV5TGfC/IzGbrD7KkOs5bIwdqMomXK4ljuGOzCQb/+pcXqdkhu44Z3HpzZm2iADN5wn5JBMRXar2y8c6CVJX69fTn+jNrwRixC60nermy+EHKSMTy2nlSEbdmmwu3xby9SYDT444hLfyOVrwMbyAdxC1CK59aVhdewTa+VWYLRGnhJpE3hdkRuqbQWFKWMTwnHnBdIL4dqL6bQ9l43WyPSAIzxLqqs7L9Cz+ZAIv/I44c4LB7oVpSHMtMWGahwj1lGrcH0C47StflMcAe59rDLOnzBnPTd5N1ygd4NgJe4wya3yzoYhr6tCdcMFDDSViixk/YlBGuXiQ0ml01obqcEJIwa1dLW428JRnx3INMbx5mSkpgJZ2mfX/AvrzW6qXP6VL2W9jwLo0PFLfNWm6r71pCiQfFtO+4UG5ml+8PElemnBC5p7ihEatU40lC7pEXazhUPhD3a3rW61DdKOctbUG91oxDjtiHUKB5TCh265wBwYsFXAgyD5sJxOWguXvAbdII2AgpiadypuhEaKMvCf+SC5FSfhaZHRkuNnhHaqGpXMrq6a/Im7LhxyY0mDoR2v5FY8Bii2dmbokNxaV/yWotPsklvlmNQi1RLtZ3XXBRJA4SkLw1eGH22t8XipzqRJbKXBLdT8fI5Cuu/CUR7RBxXJzpey3uIK5Q9v0+DqvgtxCXogMQgjNjQjmbpBY/XdxJvqtgvgLAVOW5WdcNuFQ6x9qBPnG0TDs6NeFySw9ryVle+ymZR65++tucKTtCkVzHTPBZKdQQFUJ3Y/wqrDNY9LRMzC1T0XSPImJwnmiSW59Yb2gsJKlWdUN1w46e2PQ6j6c1d3W4DhvgoUOzxf3XDhyCG8VAerMTQ+w2dKegVHV/+JFZ+sMRqupeKGaGHumKNUPFX/iXWfbJrUD+58ihUnYaGKElgKGqVxkqQKO0ycJ5aBGmd2ePezp3h1wwVCjcw+fPn6vYEaSFaVyd3nCndbOEr7n3AJlLyVdV/qzaEOB1cRwzUgM2TFnDx8yeorJvL1bNhZ3XOBQm18Rvgzql/A6kPW/lX4IfS9DNqO2M+3apv8FKsvAkC6Ncn77LYLpH6qyI7aA8mt/hE/E2X6+XvrfrJTI+0XJbfuBxtN1UzOdsO1owjTJINaYiuND0FFMF8+1krzPlXhba+nhGrqzQiXa+bA3UvblzhozFVEwlRvvwXkxABVXKGnJ04rutMQqXMOUuI05At7CmiR0onTkMuX1NZKLRKkYSPwA6m83wYjcRr/AgNPhYUkH5Y3PCc0afP6SKzGJdjmOajcrKh6ey6Iy7/SLfxzOl69bRe4pHODYuCSW3eCodg28ZrW23OhaKjYt+DwlNy6UxoAALj3n9adVoIQ5Kkiod6eC0WjKhfnzledVpyiKtipX77IbboAsQw1G+qVko+24iRl0OFVlOP1Nl1A3mQ0biT1Nl3IdkCQJXHm9yOsNSGFLUMjrZe1hvt00LjtpNxas3cUEWZcv83tu8AlaiiKWqVIbsUJWSislytjWXFI53Blz/toay0ikFhKbjdcb98FLqmQdqkPfL09F0IcmIqqXlIO7kRYVn0olXZ/5y2CZdXhkYUnZGmfv20XkMNtQMck4cDbdgE58VNRX6Xceg9K1+CaTuu2rTd06yp9zSW7rTfJLpmIkHLrTX8C+Ba+me9jpSGGxsuUeOe2Wigqu8QDEmtQE3lbZQ5uYb5Gz81pW9+VqWgxoSQ/1heGVupCxrObxypDNEFOTZqDY41xKkER8CVMOdaY1wFWpP/o9lhATp6pMgiOn2Cl6TW6yMG5L2Wl1ZZXvXo1OY6VpvMVZZPXkh8rvaeadB4l89fbYAH5AgnXHLvbYAHx6aoQrbdRbr0NFgjR06slgNm0P/w2WOCSfMKanJJb7yP/DVw0W3LrzWIkkDhH/t5K492Z+F8u4329DRaUIDAx21vM9vU2WKDVLnW7yRAu+ba8qpngyf3itlZATpYEZfvKTbm9FZDfzi95WLq9FZDHrorXdeuQc3srINdhmBvpfcpVmQb0Dab/LefqbayAvNH4jsYWef9hObEmWOe91d/eCmKLwm+1FJW5l6w11aFCkSXl1pocTdwt9WpnrQmqHDFxaJSqtVaL3UZq2EUTt71CUeLFWnL65p9YcQiFccG5lqje9gpcolsmNMh2g98OC/TtYdl3ilI1XNXqtyJqOtoQ3y9erX5TM3FRnkhu3UmhJ7NpyK192yuoNRBUF2Ri5++te6PDjWIzfqtm9WMGN6UKOO3pdljgEnUH4orQCzerTz8B0uXyEHQ7LCBXEweKxfRWzYqLV5D+nDKOt8OCeAQwL2qVK7m1jvMxbdFn+kFuhwUVqLIPUlHvpdGs+CD1fRFW8zxp1p2GBZSH5F90602iYKdYQQHL210BOQ51PKk5rbqV5u3xw4+ecisNm4XKK+wgvg0WioI3kHW1PLHdBgvIuU9TNrnk1nsuZgf9YzRzDdagZdJ5ZW2Nk5EaBYl4iMkll9waQ0Rd5On2YBisUR9CJJqsH8mt9VLbXjVLkdxa489pVBr63NeN1yjsGXl21gAarBFBJbGmfLcAtnbjNVK455bzVC9ssEYtrjpN1iXDYKRWsskHpTAaEMM0NYOf+CHv7604bGHyEl+SwNqN1JgzSkOuzhPuBmtK51dHAHl/u8EaFSGwgdRlh2I3XisqfyAVoHtYDNnIc4c1h/Ipya37waPZoP/UcBmvkdFLAthxz57aDdmYOWIudvOz2o3a8PVOCMUyibEbsqmx7qEmO2evIRvuCdHEZcJHN2SratROBMEulm7Ihj+/iMlN0KwbspHXUNUcsaW8W07aKNWNaSwN2YjaqkmHu+rWbshGiJCU6zHzOxqzEZBaRX1kbF+N2TibQHo8RFJTuwGbSAo3vbj0c+M1nLq4iUjsktx6V3Lhm/K27hMM2XBlUStT09XQDdnwnwz6tJ38gIZsVZ3jaZmuk3g3ZONYiMe1ikysdkM2Ths0Ufv6vY+VhgR5q+u7V61RG+iqdbWQ1Nc2amNLp/jiiPe9dqM2NpAJP+1wZLcbtWG4WDqw0klurWM50NhdTXXz6UZuNdGQbLLkVpyjBIDS3TdqN3LjdDAIFZT7J9Z9VNXkxdLR1zNyA1Hhzq5qgFa7kRspgJTW75VG2sgNJ19g3S+ph+owdOOhgOpr7IdxG/2IaOWVnVLrMGhTJg89PNz2rQ7jtkrlv4ozZCmHcVtVxdZWXY//xFpDrb3o0rGOL1lxKCHwgox8L+u9xJLAJ0m59RbtPGWhJ/Wz3nglYRw4Qr7DyI1kf5ibdyakDiM3dWmAVGXeznl1GLzRXYiZK/d4jpbxG0F8+g5Rwy+5VcfFSYg504WG8RtpKNQ1TNVg1mHwBvsGmTYkA0turaEt5enlPtdaHxH+Uvr3XsmKU+9NFVC6OIbBW8U9RI7UfYSRWz2iX1Zs8ypu8FaJ9dKGreadrLTYHLCQ2pSHURvpt4Md6yXvDwO3Jnxd1KC+DmM2hdRYPeIHrcOYjfN6J+0jB9WQrX20f1s6+0t+LD+iraOy92pgyBamBv5f+EJ0K+O1piLD2MG38PswXmvK28e7n7PMeE2FzAvHu8Kkw3hNvQApiDpySw3jNXydJFa37byMYcjWdFximdnID6M2JhlVBve0NgzZQgFO7BzZNWuM1xqmOXah1fKtDNgahKXQ3mfcbxiw0eSMQwCRw/tWxmwN6hx1snKu3jBsI9+G+BiEL/eFDdtaU9HhKhnOG4ZtTYsFtKd6lGHYFsYG3if6jKTcisPoQ36aSuPqMGwTZ24j/bK8t7LusJmzOR1FxIZhG9OYtNMihDKM2tSgDAbnu5CM2mj2dWBmy+SLYcjWqIlgx949f2+NyeKkSLI5A2sYssHSXCiizuKcYciG14jgYFE/wToM2RqhA/YQNQCow5At7ow1JfvLa9uoTRXQqaKUNmRrbFPQap0v5daayie8nJlCMozXaMBNeSg92yW31lM0vzRAzPtYaxJpSYY5zZbcYI2WouoWX+6trDWFg0zEWfNW1noNEfFBk3+1M1LDz4lHGiMsubUOm8V/K3MXhpEarRaUHCHCjTqM1CBYIjICh899WyM1zgAVnP6lXTZS00Zfha9s/Q3WGkknasjb8ylWHFrWTqVPzmUjtQb3E8QOItKuw0iNcxXh6nXKeysrftTTgbHNP7HiENrA8H6XkaFaUzwbcixB2mGoRqorRYrsoJJXy6tqJGrWeg3jNNoEqNP5yq3COI2DHgQVW/2C6zBO66T/4gkbVz4tP2J+wRJLflXO6hka1DuOM4zTehEZGZF+fVPjNApkYsXPoVaxdRinQe2EA+h6oIZBGuyaMMCJYjsfYZzWqbdmtu3cLgzS5B4klqGQ/zBG63JaU0/wZo0xGhzIBAE5kdw5a5gmkh1iu1+aIcO0XjXBw2zm3DRM6zSoHliRno+w3g3mG9hdjeOnkVo8dfJeW6yDdRqpdXJIkjJbYqvdtJf3maf1aZQWyEldtr/cFKZRmspUJ10JVt7HSkMzTnHlO1JNQzTNetKOa8lHWOmOD5dpe/JWVppmCtA3ZOLbNEbrhKzYRDPdchqjhbKQvghq3kcbptFkN2uS5SOcxmgdc6l8/8slWacxGs1tlWQ27KSchmmdMpw+VcMruXWnFTk5gZ894dNIrVOfRInt84RPg7VOTyORp+73II8AE1ot6G5hf53Ga5SgwrijerO8ZMgGhQQdXOBekdyDQNwZgDGF0afxGhRnBfz9adOaBmwxYDSamWqSlu9szCYCoHUy2f9e8iDQ8wiilrTs06gNCEnS9hLZcJ1GbZ2bbNHqaZ4atok/vSmkqIln2EbqEEljUNYhN2YjJZDsjP57W8O2TnduWAWG3DjTsA1/zCDfNEuhp2EbvIIkzkM071tZccpJyc3N3IFp5AbCY3XKOZCfw8gNbhDcFWPl+1pvsvD4r9x2B3UauA1F/OAsn/m+x3KOwpxUBdymgRuf7qi3u06v08CN+AetG1u696dR21BGCGhVXoFpyDZEg8CkLZ5ThmwDnPBl4OsOiVHbSE5L6Hb1YY3acKCWImwq8bJ4dhVkfLf7Wp3GbUPNXtq5+fPToI1AOzCVyqf7J8Ztg8xYAvjNibvT2I2+DFMxdtnYaezGh4IVqGZcYBq7DT734Dsq1DiN3QYpvsSXv2fRjN0CENCPEM9X8yVr33CrTvF4+8U8ArS1JyC45d+ZRnCcPNV5UIR3dRq+EW6hE2TNBPpp+EZ6BL31GDjJrXiHOna1OowEpxEcXBEQbH9qlVenEdyAHoEAZcsZZwSn45paluZMMXwbXalSJCdZOyM44CyZELcMYBrBBaZWbjDlmJJb61CPw9B81TbTCC4WwWDP7arImwZwTLWilrC5VRnAjSHWXkJd+XsrPdXzD1wh5YzehgJvvc3U2chtoDGTut6fW2e6FNC172H4afBGOdCh805WDEyDt0G+3hE1nxQzclPRvUiM8kWt72piuzjFoY1p7EbqffyLjmd6KWM3GBII8bWVW5GxGxBd1LczTYKx24D5gze9S8zYjR1tpgNFpsXYjU69nQLW7nLfafhGySmFRyd3E6M3KBNUU9bvk60zTr8Kt5eLS6fRGxzem+z+rLOZRm/sYLEBMTn1CKO3AdNBsodpuA3dxhHBHul6+XsrjaNM1CAr73+Vxu6KqjQTJaaB25Qzu4hUSPJpeVOD1C/xi0EbhQAQlO+74xm0TdL8FfvZ+ftjuRrpEE3k98uILawu4WEizl3yYjn2jlOo1vkyZJswSBIq6t7xllHbVNCkilxBcmtc1NaR6EjeyhrjVKepW9cRYBmyMcqBU8WqKrlVVukMtPYrf2+VcSh14oOaFMuQbTIq9EJsrrZbRm0TciJKidXbpy5DNioowQpNfGR1GbJNeYNxbtwmhXUZspFlH5vGl8T5dRmvTXJpPwppHfFdhmyTpnXQpGWEZxmvzaZOMO2om2tdBmuTbH4Rqbt8ZRms0cgR0pVAGfkn1h28Ct1iFmgvw7RJjPg0ZdFJbsXJFWYbaO+zGqlNYsFqxGSzuwzWkgGLurB8upFabG84ysAgHi4jtSlDupNNqi4DNQAnfhAx/NznW3uIRmErzhWwjNViPKD5LnlkWoZq6vBTlVd5QdEyWoN3B3bimekfy1CNzBaiH3BU3IcbrU0lxLJdCmcsozW4WJpi+t/7Eyu/KBnuMERLRaO1iU8utkliT5Jb9UVpGZWNt8FuXYZrlCkLGmRAeBmrTRIcJgXBXz7CuqtzDR0ulHy6jNVwCE4OmJkfsozVqEJZ0HZ/Slxaxmr4UZe48XLxG6tNTSgmr7DrMlATPyLk52rXXpdRmlwIo5dszVqXURp5orjiIYiQ3PryY7wP6ZZaxmg0mobtWWnX+U0N06aylvEMtItol2Ea5Ql0bl3ayZchmo4wZPWOVM4QjSw13LWj5PcxRFsYkoq3xTHGZZQWJkiljJQK+NLwpbPj6ZDU6VMYopFLxBFufjmhjM/UEY+pkcW5y/iMgkWapARGshkxRFtFJGs0WtQsMERbkIMWPLfHo2WUtqrIWzItehmgiTxgMYr6qsZnsG/ToqH3/BrGZzTBIUP3m/c2VpnFroa1aXMMzqhIJMc7dgG9v8EZ2zIscqRpXNWMz8AkA89fhsCWwRnLYTI9xvLXNkBbhOtoBZpfz/hMFCfwzB0j/2WIxkmzqLtofiJDtAXbnDL6nvUyTKPwMEzhvjQ9yzANvrIF+VhWxi9jtMXOkxmf0sMYjdqc22VZQ2WMBpsQLs02qofEOC3mI/2ElZB238o4jTbLGKrPzcvrMlSL+aU+3f3kSjNUW+oJC0N97rGGamyXFT51tYury1CNtowDCJnR9GWotsABZI322/C0LkM1NqxDM4eau5yxGoalqLPZeH9i9akLOuIGyLe17ktcdKRQaBiN1ZYyGSHC3PeUtAzXFvuJ0oNyMhquqV/cCIO6Pm8PRmyLztbsWFmyt4zY6FMST6YKNuXWfeMGIolKh45lxEYhS0xG8ijz/lZ80++X3f3LV7XWkHSQFFSc3L2M2qhEI+/jSwfgNmoLNWMq0t9OuTfbqG0po1+x9Cm5tT7qXAL/Yd7HKpPaDXaQ0dlGbExaErqyW3LdRmysb3iERpbxbyO2rfZJNG2591mW4+sisVuHo23Etj+122DvLpIfy3GxiFJYcsO1rSzUrUb0OULbiC2590kG0kfYRmz0GY5DBP6y/H2zfCTQSeu/DdeA6YuM3Xeq3oZrMCbQBIrGvpJba9hRJqBC3vZtuLaptIGsIMmjtrHaFjIO41HPe4QVr6rD/X+mzi3ZVtwIonPxtz826D3/iZmVpXWuwx1uuzgbKBBSqh6ZlKbmroRrO+28EDkEAGzh2kZDIgRAV+To3cK1qNBOGvxOnUrHWyse1drQb7Eam2PYFCDtus9WrMa1U1K9LmPmu8Vrm0W6ozqWbNoWrKGsSgrw90fHtMVr6Nosijyf39+FdL+TM2TGqGEuYCPxjswxC0Xsul9V2B+SS5hui9aYH5ib/lWObwEbVZwT+rpev9B7AMcOAVD9ua4THUjzYhJhW7AGNQOFcKeaBbdIbcM7T9T5lYpuC9Yi0AtX0F51CZ2eJBdnZvZ7s+K1D5uQSp9vESRs8dqmnoEOnETXt3BtV69Bg3Uqdn0mwIyQk6IF7xax8c2EPXK4mmxBG+n976tat6BxC9pC9j3Jzxlt3OK2HSmn76OqpPkWtzFXoN6xen3PgrYQmaPFk8z1FrBFj/oJcWzMek1XCF2XU5KJLWbbaTbs0e2JXc/Z53bCfdnEbwHbZgtD7uw17L0FbNEmQL/t/fukxGxUDiPlu/7657ewDYHJATF8OL3fLWwj1UxU8xQR5haz0WrBkkhb+L0BYdtJ2dZK50Psj/YQJ3gmQdtJWIX6npoaRG18RpBEjfudi9poUedjP9kCbEHbCUk1wbp66II2VIAgZvlQ9fZGl4cGz5V6lzwLQRs18fTLE36NXZ/pIJ8RZ9BnQRtSHI11oJLEW9RGd933zPhw8iyEbGAJ8jkMh9h1Gki6osBSf6/TrF1waFfUbovX+EizsLe/aUrIBrf5ZElu5o+3qA1ab2IDszoktqgNEmskI6lTj13H6bQgR/cGUGzxGhWiP2q2qm1iC9a+pepHpSOFUfeuxGsnBSCbZa1OpeO0pVNbWlUKW7xGbR7Ked8PHLJCNmjF0tlYdHZbvIbuAYXM/1o2t5CNPgEYD3iA95kI2QAWVEDeatUtZDsJr0YvNTcsZKO7PhqrW76wLWQ74/IHtaH7orYDUwNZoV1PWMh2sitimSwcJGSDtAlmjRbxyXcL2ViUWawoILmOiNoSs4fm/a01RdR2or0IEBOdbYHbB55om+ooucSu7/CQkEt67Sc4AjeaFQYkU390LkfsVswTk6TpiF3fd9jVAI87dn1HTTUtkVa5HfEbKBoQcYr974jfDpgOrvf9+/uJ7n8fADvit9Uv9J4+FKJCj7neI4ijtDX5i1VmnWcAk78cmR2OGO5AOTBTZtpj123KXRlZ0bx5jwAubW5I27QM0yuJ8KQDbVJjSkfkqUt0D5FmIxw76xJDe2dvnXRA7FM7MHRSGzFjX9o3NWcwzuVhXABXLRmJrzQfxgVwHEgr3XezufQFcKnRX8DQara/ggiRZeIzg0HqTq9XE4FDbLYSOnOIvPoO+zwh05WSvCuLEO0IWLchr8gDeXU8WOzbh7VVV9dxqgLD6HCV+96rjPCkpjGS7bVru7IIUeALEzkBXu9K31uWnN+ujN8VR8D+JqvBRvNepek+2UTqll4ze1cigUP00sJSFPx6JRKeKpVBrrwKb69EAlTWFOunZThPvul7iNnQ7xivl9B9uCkoX6zt5JVIeJJj/xDTZkTFru+oqLCiV7vX1Ud4koCFpua2pV6FhCdZSHjhmK9j12sor2gqCEy76giYUYpddIjXafSYbj+iUS0NAlcX4UlWY8Nu2hP3uaIIVKWB3Topd7/urscEsOAta/fSeky5AURkmT6vIALmlB2dW5dx1RCeBAxBbr+q0bpSCHTyUB+5kx28z3roM12IVFxVy/3VQXgq+kJl1Ujv5dVBwM4qQLwm3INXB+HJ7nxMqtbqQxo6HUUiKsLdvlwdhIeN2yzVC6uYrg7Ck10PDQkFO64GwlPbgV7sQ/qh6yDNaGAmyXBlEJ5AyqxCSzrXK4PwPNG0XEB/sd6VQXgCQGicnMX7eWUQnizORPz6qDPpPJ1PEI7e73jqPFFMqiWO0ZcrhPA8aWqESKrm84vdnpSKUyF0yvOL3fJNtHRyZl9zFRCejJwWmfga+he45eEC41CFjf36nEmY99Esh7kiCBxiGaPu5m+QXPhGtcBGs50qguvHRXBPel7TvVZz90Vwz3O3TuSjYtdvpsjvW1q1R7oiCOwqHl7DSc/OlUDA2ijsTZdI7LpNLfIH9rb6fO+VQODQymQI337sev4G248/Jar36h/gHeB+Rowmdt1uRGiIFNn2eiUQONSRbFjk7GPX7cZagjBwc4RuPW90GKFxWtPw1vOeSo1Fg4I/0X0KySiLaM/f2XwCVDXDzn9quj26jzIDMGyarbhaCBza4Qxb8/075BMoshYo1TLsjk8AbnxYOe8wPbofgSwKMO2QvnoIHKJ7YBQL4pVCyChB/4FiMp08+j+gdf12wUcOpSuH8CDUYQVrXUPngRGLajkyme3KITxpW4SxcieH3q4cAnYK9WESuBixXUUEDhHCmxQovbHreeKPhIdvV3W7oghPtt5RkWJkt6uJgLmnr2DbUtSuJkK+BRpbaFUeHtL7lR5BeGzLruvE5iJod1kN21VG4BCt7WS478NvVxyBQ52sEhoL8/7q8RmU5A46FjN2H0B0A0aWq9h9AEzXSBymQKL9BHGITFEvv6OD0X6COIqAW55kPUhBHHxdUe6+d6rfEWV+SG0371TXiXqwY1i3w6X9hHHUEELYRIDyui6Sg8L/Sd3Y4wkFc/DAf/sGXlhuWSQH5V6UztrJcBHGpYxsUOLc6zzXddiLAR/fIMubF8aFJyR1HXcEt59IDvoLirW/LVhdemlHcIPS/Vtr2n4iOZgax4Jj7+7A2k8kF4YIPqTwC7WfSA6uuEP18m/5WERyb8o9IzZWP9F3kmy05oz6c10nlAYYTpKt/URxEOXAybbu2fWcDgSYd1uZ9Zpt9QrrSV1Urzl3KFHvzehyC0qA0CJjUwBHMzm9QGywsAvgyN7CQvWkJbv9BHBUV32rBfqkuR8RHD2PYAmaC2PXW1QBNh/GW+fXWyr3esTHfaGCOPpyxhO+IQenII4yNaLmLYTo7SeIoxOA0RFug/sTHScuQBKPfG37ieOoSUbyvqehuP3EceQziB+FoKnOJI5j9qbEgqLSOwSEctTM8XV/X1TuSyhHTmpReb7//cQHMMPM3yvx0H6iOYo9UuO77p62/URz1AqsJ9ePL0I5ssoRRGo1ZsVyKZ2HeiSJ1vYTyJHTmpTc/5pjWSz3prv7u+VnecNiOeLo0Ny0louL44jBTurSbRNuP6EcEwwBwFPfuFAO5AC1EhIXXkPnCSqn3aXHE6FcmEaJ9TFa70V0/kpUPaFlaD/h3Fs9NVDK1v3qPMyXpEt29+oiOhZM9BeO9aftJ6hjsiWy13YNbxEdHySfdri02080x+tkv9SyjWo/oVyjsBe2q9mceERzLYEsSqjyvQnmGqAmkmiPL0Q8R1cUBQujb6djQR15NLjs5q6VRVBHKw9A6Ozuuiaoo6VmgP6p8b2HdP417Hg3GO0nrkPwlwKDnf1f+4nrqMnLc14tL1JQ11hTH3gkXx+xuK4Rhxtg1F2n8glwjwdFhZqhBHUt/UrRfqrz6HurlksEBH41xYroWqOs8g2xHXYRHe+PGPNSyK39RHQwVDekhUamTdFco8mAcoUzy67fyc9R0Dr8tAR09AFRh/kkMdl+ojkkBtm67fDatJ94LnUb6S++TN/tJ55r4eDa6//giXiu0SDfaBrJJy+cQzoEMjSKtuoXj4iuhcM87bwzdj2fv9CoLcV+2yOiS2NTEgK3K6g9gjqEttnDtOidtEdE16gfCvdqRuQjpGvQgbDoT7aB7RHPhXi4JYxY59f1RZaS4oZVt6TfiFWFgaCc0G9EEjs83yQi2yOKa+mOo6TrMp22RxTXVoiux4o+UXtEcSicleDor/5ejyErm6Hgi2eiOEokaMUe9zQ6vKHUpHSw504FcfCI0Tlyzt8bEsgh20fn9vep5xmJ4qgwgzivyyHSHlEcMDxhqd/xDYniGOYrOZj8QgTXTq6SVeSeTBAH5cFOxdyVtWyPOK5HBBM2dLIU7RHH9UiPs/rnjoVxdFVHNHC6uj7CuF6XoHM+A0cY19OqT6iIbXl7xHAs9QTSUQuO/WjvED3PrGJ1CTEc5D27kfbLL8RvHR3plW9/+gs9j4ojMbzMPY8YjhcbhbJew0oMh5AgDUunpsNHEJe+o0VZYw1PUVzHBxDNmGXXaSBECGJHnV+nKS6nU+7fSxLIIZIHwKN5o6a9RyxHqSqsDic9bu0Ry3VUlJAE7fXIxXJoZ6JxtFsNUbEcJ+nUy703utYe4RzTXsIREVNrj1iOvGSREa2y6zhN/yQ0o4vRHoFc4lhwjqYFoz2iuE588Jeq3rquXjPd0U31fbT33Ynkom733S78Gx7S8UF2N2VOubowjokupMVn66BIDrZYxFR2mvjaI4xjt93I6M9dl9DxmR6EnsD7PZW+f7PgBpqForU9wjiEaCKKtHqdSt/T/UnpQvNbFsl1Jink5Fb2GI8wjj6hQ5iy1+sQw1Wm7IQJ896VOK4DCtAGScNZewRxNI3AjfIk6NweURyBEXrIW70oEVwyQRTRvi6ljyCukwMlwpxa9/aI4Pou9vvHqFh7BHF0BIUkbmxfrziuCs5BVIKSRxwXLaEW3jnnRXEcdaGfk1UZXScUypGmQ3uwKj7bI5YbCa6/Ua6MvWsna5yO0u1Vhoe+fRb9wvvKmLdHPId03KJz8NQ3J5gbpWUVorTY7xMY3z89OaAn404kNxAJbPSh5PSiuBT1IPaW5tv2COEI2vzCnfw38QrhqBw/EAXfkS2EA4oRRTzPkzsSwlWHMvygl/S6PUI4eAYGfXXtNjK1RxQ3KJWlNfqtmVQUx8yeqq+nZkBRHAPuTd9X4PsjhGPKSLlfAa9HCDfQFCdlv7fvXAhHIA02NJSzY9fxhqLh8IsWwoUTAfniXz1x8dugs3PQ4dcccEK4z2vawyny8rMSxY0ePbAOGL8PXhRHz0SP8Gw2D48QDv5KOn17L4gjhhsJ4U3EOLixVwBHt05CVb9bndteMRyV5qSt378Q0CuGQ4SNAu2W8qX2CuAGKeMewPb3E58A5Tq/hARb7LpPqgSJh7brxvR9hlAYIuK6Kx2HUgoKwEjGtlcMl0IrypT2b+iIvi+gxz6vtRjtFcrRrXCo4bDjq71CuUEKjaZM9bjbK5obkRQ4xMjKrvthoAfY/z1MAR1VugTslnrT7RXUsZRBKfWkvre9grqxq5gOuWB/4kMg/T27AZxXUDfAf8Sq+/17nwAtADQ5J4b4iuYgTXmQ5P1RJtxe4dw4+UKB3HknYrkwq6ciPNGyVyAHPyIhmOet5yGQI0ZASGlHV629Irl52+kgD4p9ak9Bai914vYK48g7DMq5jhPQK5KjiYGyUEo6PXQ8RLYQTd6Av1ckRy0ECOWtufoVyqFoAcN0P83BK5SbLC8Q/Kfgvr1CucmOE46I3yU0b69ojm4b6oBnykTaK5qjI5C9J0K7/kT36RSg5it6lu0V0BGbRocosfB7Y7oPKqL57n49ArqJgM33iZRyXXtFc2hX7J3GW8eUgO4bB7SIhBDMQ7oPawHKq/UpCumSRzg9PHmx6zo8Hp2yrunrEtLNiiKSA/CBieq+50QSYvZ9z6b334XPE5GkuCiqS43fBiXNOo+uR+D0QKhwJ/NXVAdTVSgkKtL2CunQFZuQRvX6nIR0M7lU2JnrEuK5SbMcEGZnN/6K56AmosL7g1R56uK5CbVd8iEzL1YwR70mneKtpkSx3KQDcUN79dbp9XiRiCV95ab6FctNegC59JNQ+SuWgwyHbonZciah3ATKfV5ECLW9wrgZGWbiFVk3X2EcJD+pw/rbsr8iubnD8wJSdsoTzU2KOqE6KFTyCuXmhhUJJbKa74RykfSG3l8W8vYK5eYJd9x3z8/ykJ7Ts9ijvXRh9yuUg96Jsj1o7u+vhHIRiN7o6NW9ieM4BSl9ik5jb9rRukJ2rJ6YOG5RJhHKi5opBXE0vbQqq67rTu3IIKMomY3nK4LL5P+tzS1dcO0Vwa2E8Ef0jGI/2mmkoOBT0PCK4hbfykgpjV4L5BYuoxuUBq72iuIQSUkTwPpbIAVysA5tws29PgGB3HoTZg/vV+w6XvVDCDjUpXWc5G1U5gsxCOFK7AL2+frqhXArhUi4npzQK4SLoNapFhbsQjiquKCIYK6KXZcbdbep0Mh9it9SPsFw/t1q3PaK4RaEHvCOpoKmvWI4CM5WsZ87rYnhMjSok7T0rr1iOAq5QTiwLXshfR/RNSCJ6dAVxrH5ACOR5vKQTwC9HCgaftkENJHcIsqL+ESYIloTxi1qFUZCRzt2n8BEaJC2nrfOo/szfAWTYvPYdR8hRwr5o5/emgAOvo/EM3ddVr9pUoty6qVKaE0It2hZZddXILkJ4WhHgSXiafuO3CaEo2fuR8FMIYMmfiMPRznGY4l9a+I3+ilO6gFH2fUbWYZfmAfKrt+b+yU8kk+5idz4LFr0fXv9vX5Dav8BXVSPY9fxjUpQpDLrVvWaAlSIeMftQm1N2BbSo+ROTl1ar2G1QY5o5uNr4jY4HRkfRdfRmriN1WFHHTO5nCZuo66AafH93b9v2uER7Kkyi71rn1CkUy53I0VN6LbTqJs4WczX6R0Cr4fesjrT0k6fEgg781oTtu3S/0X/sk5/tNM1jWJw5scmZiObPXl2ihu0JmyjOpgywJ72u9bEbDTHf6vxm/rPet7Cth0mNRRR/l6FsG3T8N8JUO+/C+k65cH01bb6YIRtaRxL7+itk2pN5EYggUb577PJ4xK2sdXjrdA2E7vuf0vpWun+8AsQuZG8bxSgHSMGTeSGuikihDQl+CsfAkE/WmNDntua0G0TlEGCsBtpaaK3bylPtJq0dOy6D1ECJTX7Uim0JnRjM0af8x+JT1NSgSVtwJP7vDW0RW97ZEOYGFvsPgHIEVLDlq2BegqfnboYWBENPimpkMIJUkXrd/sgm6oKD01HFAq/KQVRVCH8qvBOQI7sL/SeMiqYkdN32hRVYMUmjTXgf/Aner9ouKdZvl6yMG4vuG2oYX7+fqL3ny8oRZ1hYk5RBUh8iRRAmJkHI5JDIbWl6PNvPhXNIWcB8c9IHW5TVwF6hhHd81ArNHUVPjuMt9+cuWsyFcvt8EzCdfQ2L6H7h4g4/Fv3rvQd7jAkcmPU8ROm/v22mjFFceEGXawJp06iy5Sg802Muh/x2wlbAQQUwy9Y/EaioVXdTi4tfjuhdyHRHOisogLLfADyrJ2oigoP5COs59QgXpeFcAhPtR6mwu7Vp4eI3hU5ZuxL+0gr96RH6/5ke4j2CugMWl3laI/eGpGLDFFRHKSv8JiNNZ0JRHGHxFrURq1NUVjhSYiDFbfvv0M+ARrv+Ijy6IVxxFJ6SE13/bXOs/fdIY6ua+v5N02kO6Kt+ns9h8aYZGT2GQorhHgQoj96APRCxzvMBON77zUFCuRQl+hk+Ov2xXGHoD9Sc7WYC+NogaLWr0UdNBcQxoW5m7SQYtFNdYWHHnUCrE+qMpvSCs9JrzixYMPCqit8h0bIK0YFNFVXoHqKGtlFr64/0fkPfjCB9PP+HdL5SYSUnH0CkYosMApntLv/wsKKLDyIX//CcWJhiyIL3yGa6n4w5b+x+wRIRVCsRdfJrw75BBbbJRpOW53KJ8B2Gt7KkSejyAKRLmKYaNau2HV/7eLPOleFtKmz8IBR4Omaqads6ix8djjzF5sUvnZ1FvgOYAIMoVTsOv7NVlSIlRhZU2cBFbJFjPJXNTDqLDyZTGgi/bkYKbWQmiA0kNPBcw/pOFyoNA6/WfWUWqBKNWJX4y8nr9QCU1KmjRn+gKbUArCBmnW2Hb6pC+je6M1AKqV0VVNwAf3KDqE9XBn3VxfWvVEPIcJUc4SCCy8pdNhweXSxt2sHIZKJqg22UgsvzRRsxglEeInhIUAarIt/93yhXUk0E5aq4IhqCy+EgdXvnVlbtQWgDkW1zPJ/Puo+QgOJG2fTqNrCG1rpb3jtqnZTaiFdw6jXlEJUU2ohhBsE0merW206zlY36312y0otUHqISBp9jXcqV20BSvVfi8hAmXUatIVK5XMc102/kdqBA7+CnYot0C3xLc6sbq3+XqfJalCqOes8Xaf7YrXYKJPcS3T9hg4xXGstg7HrN2s2uZb3bzB2XR9UC4J36xF2XadnEBDyijQUXCDinwWcqvj7VLruzxC7Uz+RB9n1na00Ja/TUiplF0hwEtsb7ANi1/1Jkf5MqT32ofufcSMmGl68puYCXy0CvCw/F+cou/CGWiHEwlZfKbsALQfF4+DQOpvu116TVvO7CCi7cDtGMhWVXd9TYIaq7Kkb1ne6V2GwXKsuoePsTDYx7po5ho7TkjWjfBv71HE6YSK4F+Sr4AJFrSevdiYkpeACuUM6yde/gLGCC2wyiYuhRvZ6SMfZhDJhv/WpXSD3RlwKHpu96upT+xvNwLn+XWV5qFMn0U9tYlRbeGlnIRXx9nqAF869qff47nFX0YVqC+hPMOTIr+bvL5ZDM47N2vfy6roXy8FaSEUeXBd5ERfLvcRU2DlQgnBv9cK5N+v0IhpqDlHBhbdKekcETu5IWPpOnzjUK8OMq5oLCGPQFjZRKIpd31mN4Nq8L33pO1We8AxInd8UXWAHnrBAJMmbmgsQ1FK3QPC/7HrfwpfzPfh7Gr2nou/HdtiNkJoLqX7rv5DIZbrcuo6mNF96mk2amgsvlbIU4JUSS1NzgdQt+4xvDRn19zr9QbxJTCLc5E3BBRrXB7n8fr+ko8fAi++JjlMI4OjyCAMe4V1X6KPXY0UgM9S/TbEF9lds7ugcaP5Cp+cb4emttGNTb+ElERGC14p8qbdAwVEPT6pS703JBcYIek6EBuqWdR3NsGjU1RX0PLthIqGJUqq4wB2BDsLXXjel6AJBeqrEiuA7F1d3gd4PKG52EKaSCy+xEmIPvyx39QN9Z8+U2MNVtGiqLrxspNn3PqvMup4wFv0as+z6DVZGje6xjELVhbSfkTOpwhJFF0CvVEHsVYNB0QVGfqdlpvaiai6AUQY50F5ZHAUXKMxhASbZVadp2qFB6HCErdi7drglafVLgF61BdAepWadcpr7xC+EQy/zjdhyTawKLiCIQ3Msxfp16a2dWOZ8/xWzKbgAN/2iLnJXAlTBBXq7SWqsPxrypuZC2j1pD/1VzYGCC9UQvtl6Dd+d+A3pCyqi2bDFru/s635Qjd42r6boAiLyk5KCVvs7ZReipL4b2iLvz6voPteYkETtsus+r/4ADVMwqPQCUjJvGMFbUKi6C29U2ZmM7GhqSi+8EdRFoG8YNFF9ARcX7cPQRnlI95N+YVuXBVIBhqjrfMP5m0ATVlCAASKF73tLEUXerxiOME5iBE0kofoCIsJ9Z2+YzJvqC1l8e8LZZi4VYEDucZPYR2vwHhLJwXJN9Ov3q1EhjGO6oMISdrp7AyI5mG0/LPp05Lzu2XQfJZVBwUBmTQUYaCiaP4Rt5ym77kcbhJ6XLFEKMLxp4aNHgSnoXl33Fxn1TtVwXVr3iQhNFNL/PiJhHLX9ZG8IAN4bFsm9qYNB8qrMek9OECb/qn5WhoGRSgfWXlUgqAxDmv13GDZS7acMA9pbhGvZbGQ4iN9oYWbFo+k+dv1Gm4kHe2cO8Ru9jN+ShYJMxrX4DXeeFXXi+vvrcUu4HH2c+nDFb7StjMnEbp2fGgyBzFGG3Lt+8monFUquIlhXDQZY6OHKIIvtTCN+S+9MWFhO2Yd2WJ2fdFrHPrWjhP5LCjr2pf2Eo3BUMagCDJBCUzSBgGH9vV5Drt+Z+v6+APEb2eaFXvP8Gx1COPZd39igdzRXEcKRVQIRPW8NNCFcSykqFPhBHgow0CNCvQY58YxlwRsxxBnCu+SkFGCgYxCSbqhB6+/1umcphwX5eKs63tNm2H8RYWoKMMDPDQ3nfMNA0BRgQBx4EcKpDt6mAAOY+zBnoR97H5TQjcn/gfRwlNdCNz5/9mhFhNXUYIDyusMrUVy0TQ0GJLFIeHf2SrHr9QzjE1qJfotCNxpKYBl5qiJODQZU2cCsT7HfNzUYyPK0FFDOGgZCtzbp8SMKFeikBgMAgTAmcnVxQdzGjol8NOrKsevyt4cmnUGvS+y6DFnHZhdihasKDIy/QQUSUdTrncAtizsaE9vybEUYqCch0p+1JnYdJ9WeJa2ercgNNLlIzq5Em1RggBv723nR5BTgpAIDixySf6OIYpoSDGS32M2t75t/Ytdxwl+Ejn82y6jCQDDwpZl2l7hrDg0PIadJXDkJC1UYOAtVS4RX/36yPFSspSFwvBfaHiIqiOjAqrNd33v1cFJqG9+Fbv3Jp5EKgtgf7fS70w557jqmFsMbQcUdEoEZe9MOngzxS11C36nRZ82X8L8pxBDtkE3JVvRRmyoMbyRWUcXslzynqcKAwudKXKpiDkowION5QuU3jeorwYA+ScjnaY3BLoJLOQUtK09WV/UXgCnEqPPFxa7jNH/wwN5ECdRfoKSXgCUVq/fbVH8B4oCkQEryqSm+gNIlzRiQd/l4hW9QDVB3NuTbaUowQBJAh9p5dz154VsnNFQZt+4N6PtgEvgwqtL1TSEGuBwiEgw/U+y6PxD1OejO5OrCNzghyC+vbnxMIQb6AWBtn08YtJsqDISJ0ejbAaL36j4BiHR3Amg+NEFcX79USZ1oNzSVGEAE37uHmfOy4TWVGGga/b52IHGrn+h+oAv1Fsk4qMSAWiL5gLcYyJtKDCgURnOLkGfs+k7JE9G/X00FAjc0JtBu/U1Xc5UY0CxkHCQjfR0UvoWFHG7cs+tsOp7q6Q55iK9e+NaDQqMEHrN+Q0ZJxGKYoFWMgZFAfymUsz5g0RtFGIjCU94f+6OdihGoXMpL4dv4VUi2V2ZIJQZU+vjqaLE/lWxQjAFBPvQYgqFjH9qhLj5t1XMXwKXJjeBReNCaEgwo5X3fT7aKv1pmVGEoAnPoln91T9ftAch5YWev+UEIR/nhoB/jpPpAEQYEh1KoEz2/8kEIR+0Lu91voctNCeFoHWaReU/NseI3tMMoIVqho2+KMCBjcTKiRvCYCgy0FZHR4Lus8+t0gwx7I1BZ96PHnQJIyqLrmYrfiKJTgVjlV8ovwGIU7YSnggvKL6T9k/QTuY/YdXdEaQGwXnbdHYzK78OrrmD1Fwi9/uC7e0OQ2tRfIJOE8iG/qfvRXYR1H4QC6lsUuAHDH1Is1fuq+AKyZYjt0GdRf6+7AKSFYlOC7kovIDTWi2k5gFTpBXihvo8Sve26rpBtrDDaj1MdKUovUHn3JFY9Uqqk9AJSXwQqYeS7DVOqLyDp9SE+aJjc2qm+8Cbb+e1yTlSv61c6DgPBgLF51YV0HMlV+IXvRyJw+5DdyE5k1WcocEM49vO209sVu45HzhcWxlouBG5op6BYtE+NL4Hbt+ygT7VDYtlUX2DdoMKPmTfPVdA2sz0DDNX4ErFNdo0UQoRlvim/kOI1Zp4Wju36yfbQt0GEKX7VFyVimyEK/GBLQVIVGN6w1EF7D9dTTqUIAyJPdJ3RKf/E/mqHKpWlM1s+FRiI1lOosor7sanAwHfw0LlJyWrses3yg+x3eNubCgxsAVFBRvnjxK7Xb2iweq+yfRUYElbssu01BRggO6Y9PfAAuziNLWynZzmaE031BfrCd2ZfIEA9CXEa3UGdcpgIMDXVF5AXahH2rh5F1RdoWowEWuZThRdgLw2XJ+8hdv0lkjHhac1sofACnEPQC9KZnucvPiPPQMx0VfhF1QWijLxFiLNiF5wBrgm9tEqAqrpAIjOxxrcalpRcgI0TlXSa5cd9EOKzKJnS4z0TW1NyIdL10EPSyhC7LsM2z3fcZl1Cl1d46NkZ5YEKy/IRZBedNywqI6gSxZ616vR6TL1mlUfliYrHoNqFQLXdJy0e+yYsePFJOOWJise+2YdV4r27V3UWUHiBpYba6YtJ1FlAyWVBovO9u1HLqVILb8qt2fs9mRSUWkCEBQayt8hOmzoLRKaIuYT4PXa9Pih4wVSbYl11FlBJwQGIoXO3IjH0QokMUdIV+6N9zJK5r+9YJLbC/f1Njr96SiIxEiQIqpHBuF6LxFa2OQCM+jSFYYsfEGGvQhilFt68ZsQl3mxklFpIxzYcIAVLVVpguWfVT3I1dj1GUis9ERSe5kwCsHSgRlSzzPoM4OjRM88VxF/QqM2gjnM8k27XJgLQelGmSguwV4WIm/1C7LqdSptwwGcYi8HS69KIjWeeV2YBJmL2zXD5OmjEYJGqpxX7V2Y97zR2UIhfdjEYW2+yRugR3jMJw6DWeZODqYcoBqOWDUH1X9EDKLQQLEVZ2anKXYUWoMOJ7inSml5Cv9OyhCxbKl/VWkDToT8RCC+/hWErU983zqukTaEFRBqowQDQ5XkLw+CAIWGKf/fSQjGaxaGkfFdNrkKxxZuAzqpKb5RZQAwBwM362j2VjqcjndKVMuv3N5Bh1G1Vs6/KAtFdXhz8NXl+gjEYv79x21fRdamyEB5d1hK2FbHrNJWAfEFV7KvEAiIBTLnsveYdmuIxumjYlZxin1FfAdL/CSXlW4wROaTfFG+9acjNcxKSbUQJSDlUCkuJBaYreJX5gMs+tI8sb0917quvAJs+KX1S7mW/Xu8I3Q6m5hvNUl8Bdnxaf1CQjeOCsbTyUzAYZsqmvgKU9sQo2iUyUVyBOFzYI75pOS9CMLYJjgzklEmK1E/0mnG54FqqpVRAtsP5h/JZouyKK1B3uuinJ8cRu16TvlrR83JgisnY0NMyfXln1FeA1P1Dod+8PN+6hF7zYJ6QcvDAFVdIGJpB28N+2RRXgOuHlnPCuyt2vWZVpAinrDrMzp9S7GLMUFuBrAkbOSI3LXYdHknrtlOwUW0FOM3hl4Spru5Gb7O/ieLKjl1vB0e+We3Nwq62AnneHRbQkJg2tRWSd4O2pFcbgMIKMISjecl91t/r7Yy89qQvJXb9XcmEfqgucQCFFeDuZjmnt6Ps+ruoTSXgXmbdhVkC5lMqUu4d6TGIN7Lfs36ix4Ar2mBmEjiKKkCS/X3lCCIm1quoAkw7VGxFSDt2PYYQlkD5yLSjokLyOnT3VZYjtyQa25GNXHAH5aWJxqBn5duH0KxGqaIKEEtXvPo1b6qowpsEXBQMdt3A0k7I/P3dXIqKCvA9k4OglKnu6minPQyeogTqlFOAoxkGYqIldxFXUQE6ZrBogGLsr3YQN6EDv2gVFaBRJidFZPP1UPcQCjnw+WdCVlUBIoGN178oDtZP9J0M0BPt1zxJoRnxrl2KojHrOosEV36ui7oOISF5siiSNRUVoBfuFB5WA7GCCqTgYHulzTBXFZidNN4ukGIek8CMPpfvA+jhCG+qKaRa8ldCJ/Xn+tsJiP8o6ym7ziJ/RrahBrKY7JBNpdkxUudNGQXahigu/Qb+U3+vs+AJIsE14amjQAKRFChFFXn8QjJ0W3qIZpbflqishGfRhqpvSEiW6CmlvvcBicfoDkJ57fUSejxRjaLWPmoqOaTT35+SQ9x/6WxVFG51z0kxe+w6vnp0v3qVbqqiANvrYIO3i9RSCQXYzegA+M1aNJRQgEwy8oAwu8Su19AAT8ic8rzFY4c5dIT/tU6j02S4GJr3NgVjqOUU211NxYIxinHJT7IOxK67B5W/v9ZqBRTCwMZHSAQpdt1FAZxWzJEghOoJhGCoP6TWM+e5SAwmUeJMwOuMl4vEiKtvmudbbTdVTwhPUsgd7vi6OCzy30RiK1WreAK0JztFX63GyoVhsMSlgaqdersXhkG8ifxJ37O+jgvDkp+G78z19MIw2BFI0qGImetu3aXEDlHBVm5t3QUAEtO7U8rWXa78DYlVZAJqJtB4NsARZPbvGN16THEZnUhUad6z6TXbeXZdlYxSNgGGg5EOtJ36IjUTII1kMO63gh8KJkAC+WZnXIBHwQRoHmG/ROkk9qPXHWW9F9B8Q98KJsDVUvx31amnWkKLqG+SAr1OpeNELekcqD4V1RLgTAzMeIuTR7UEiBHh96N/3Kdx9HoSZoKgZNQt6TUF2EWT8ne3Og6jLrwMhWOOfpMd4PTVUaxSAqid/OG5TUHKJPDa6MbgYxux6/SKqPqucL8qCfAqdAD0qsZnJRIoTqIlk4B82fWZuCuFH8+9rA5vcD58GvYiqJEQyPNtZ8midg/pM004zOctGXBFEqDMG9RrtsrKKZIALx5kmbzV/P2j0yddpb9RIEqRBKpEBz1rkFDG3rRnraXnKg/1grEWwekeWaM6/9Cehq7vYWTGUyGhRYZhUEZWp7keFwMrH26v29nav3PTelhBfdURKGL6pbyiJiTVEWBsCxSaVWKsOgK8bIv01A5ldU716vGb6Pe8mEdpBKjU+HQhCBv+RKffdH8T2D6x63RLoXi08GLXaVrj+D6jJ9uURoDQ7CAOdNsYlEaAoCx84LuiqOoiQEE2YYcc0Tpt6iJAKfbLLJpe6/yk6TitOOx5RjYHiiLQAsTOAw3i+nu9hmiuFUqLXZcJikdCod5/02WmC+r2ftZUKYoAExfdML/QR9aDajo+Qs/Eolt2HYdWJAyRve5Kx2ePhvLbXj+Iru+Tt30iARu7jhOEIFf41rPqOg4mTNA/a4HaCBBUkej6/e476jq+ZkK2PMTYdZzvNsBz+sy7jm+EGiBJJ7dZh3QccsrvBk5Vf6iPAOcT2JeuvLq6jtOuhLh34Qz1ERj4pKyo8cozH3qNSi2zTVWvKI5AHVICUTQT31saOk5eAwa8wizqI0CURFocxdi69HWcdhaCVrPqVhVHiEhcBbiDcFVGYHpGeIU2jbrVrZ0CkkV/e17QhWLZ5BA8OhVqVxehhbjsRwlZ8j6KIlC21WEEop4n9lf7rq1fdfOriNAqIQy3e7LxSiLA3TPJtlNpGbv+Rj8H+tkk2tRDgHCHiyVrE7v+snAkoenmTk0EWHIgKmJ/l1cwdZnaPvTP3/q4hGM0477QFxW5pZoIfATQAk8+vNh1uScHvy5CUA0BsplvkSMzXa4Jx4iNwx75qxyfUggwx8Boy2Qc18RjL0Sph3ax+nM9JpdKQ1gFb9RCgL7lewCIVcy6rO4OCvmoiqhpUjhGFmqtDJe4KxwjoENz7qoCNVUQ4E9BenFXTkkRBIrov68dDelaiIVikLWy8PTKjKqAQCxqpcQoiTrVD+iCCSEv4yJ2veXDTw6qxr8wjPAZglMl99TUPSACjVAXkYm8dGHYW6zwAJ6LhdQ9qL9vecUZosKw2p+j1lyLvDAMUR0ye3ckisLITAw01IuUW8GDlt0O4b4TmKzkAcQZv3CJPPUFC8HoiGWFqQynWgfwYKQF/1cEJmodtAJaPTPqf//T1TogdcYmdaEEH/v1tqVNDTpDFoOu0EF64aGY7f0SiXa1DtjpIFhJ6XuLvWuP/gA5qHqmXbEDKCFgjepEY2PX6XxM1HEzfXRlDiBygCSQjqXh1XWcQBAELA+Rha7MQaS+Wl7mE7sYDGIEgoEnwYuuwEGYwHpkGHa8EIMVXd0b5b7Y9bpHp5JCl7ggBqMNEPqsmg66AgcQFaBETIV9zHqMimGH2rjXafR4JC/JXiXuisEohF953teuu4NNT6dqNrcpBmvpZaFhuud2xGDEs0lkQksTu+5SFppCzJn7FIBRrAPl9QnZaVfUgK56vnFqEvOYRV/k0snLv/lquooGtMJ/oOWXIHbs+ht+V1Jv9XxEX+QsYCucv5URIfoi9LxfOFvrOYi+iCceuJ7o9qlBJ/oi/hOV3lNvWPTFjp4mJFoLYtdlRBlpdUyDV1fMIEI6VD2R54pdlwkejYjx5laFXixMUJaQeYtdl7/Z7QQw9bwCcRdjMit4psaunAGN0yPcgs+T+xF0fWsDjF4fDq1XJujq0WPpcKXnOQi6ejSMWxqmY2/aYUokfFTfsaALTXvK5UlXxT60U3RPKLBemYgLZS4ywzvdSF0hA+JzxGyJ9tR19TdVSiM1I7HrL4v22re+uCtjQF8uBKVJ98auv6xxTNQJaHQFDLLBpWEVzsY7JIRbCD5QowRTeOy6zELFME1dTVfAgFZXssbU+9d5dLmTRJ4oicc14RaNuDTljDSZd9ULaD8daRcJmVxXvaCFoJ9j787XJNz69qZ8irufmuSEW9+cspE1+v6d8wi3emoimYrf+nv9ndRGA/ZP2fV39pCFfXcbf4VbH3IdCLl+i33Z9TfZefrs8/GJtjpwHmmN0/z4RFuwtrBBTmH6PaTTdHTQTbnrexJwsdH84XPo3rp6BfQmQq1ODa2nEnPB84QCG3N/4F5XtoDIT8R1T790oV3lAjoIacyCqKl+ovcnQrp0LuVpibxgYPxtNpb1VoVe6MUxQmifiV3fUbuh7/qMfBBCrzTrLFaSGshCr0GpIOTSkQjqahXQPUd1CBnmvA2hF3MOiADYeh+I8IsOylBQpCuoDnUPAZLCF5S7EoEh20c479knXgjBBlE7xCXfGiNCMPhtwcTzrWlACDbelLMRla7z6zU1nUTuWiEPIRihCzoQdpi6uioF2QVAH0R8M3a9hsySgAcRyXrXQrDB2Cmu8rwgMdgAWwKTfl1EIgwjDUftwvnVpCsMG5Q+sAZFgKgrUxAGSYgRGVS/e0jHs75BufdkmAnF0Egi8rAj+NcVKaAliabScVI8v3NI37/JFSmRJ73KXZECdpor2qC/eyodH1RLweab1VWFAlqAvqUGfheyel2FAgq1oOymCad5aR2foZfcqTbI96JOAd04P1hZWNli1/FF41S7dQBdoQL6ar49NAm83KxIbKyUfVGNnT8XiRGqZij3yGN3RQrobWnZOaVAvStSwEJDDUKKM2PX6VD/sDfPeqlKAV0nMJKSAqrr6vGJBNBbgL4rUdBCc8NznauKALoqBbR+sCgvuIxi1+NvjaAv9fOk358IyMBd3NROlqGrUUBrBvNx2oVif7WT3YZusNXfN+0E++kOzRysOgHtEgsG1TdwVXUCEswv6w/O3NcjJJvQlqEqcPKhqk5Avf8D3cupRU11AlLGE/nUGZqMrjoBTQbcU4SXr9OiMjhbEo3fNS6FZMlwTyhGs66pTUDhP6HGVOx5Kv2mL5TtTrR6uvIEhAvYq/dZQFd5ghYN2BTn1HMSlcFeQb0oNLGx63UPLfipAvKuPAEV8SwFtKXU3+s1dftUSSXM2BUmoIKdSS71n7HrMhQqM3K8MesxfYKdb73nvQnKEIBEW2+FI70rSkCNAVs3WrjLrruz1NVGrSmKElD5HTn4UzsuRQmo5E7MrKfguytKQMU2kXU4X/I4BWUkAEPwPOs+BWUECQF8ZCZi190PJowsNVlblSOgRHqn6xi2w3rDgrIP0rB4U8JWp9LlD3fRFr/Sx9+VI6BImd5b+NjrlnSZx/+Cacqsx3BXURu0VjwTk6FXvyIoXi9YTJZxSLK11fQiJkPRIAIlqz5kMdmK0DudbDWmxWQIQULMTf72foHCMhRd6YKcszwWloUCaaDo+boyiMxWxOy4/iz71P5hSx7fjBMiM+oEF+nbp+Y2YVlN/Ygn17MTkyHrCtCGUAq7mGxFFGBUTKsrPUDdKQ8bWRV9E5Itsu0fUn9rv630AAOaMMns9/UIxhZ4vVN9EKvuMipC/pvdvJID1GyigcJl8xkIxXgtZ1G4fO36++EzCj1aDTmR2CoiNbr5c5MisW8pQ0mY2S5/LxJb6Wf+VuHzt24KxuhZTalZUuddyQFqF2kDfStT1ZUcYN2P9uAE+99T6TSrNrR3b/u7in5PbpKSpUBTJQeoFISeubfEt7qSA+yivwG9aaMqR3R8hdESwfg8J8EYRSxh0ezduxKPLdrWqH+aNeGJx1BCoXQ5zLT3J/rOQrKygYlZ10nG0Wn4zrq4ftMKRGRv1BwmFlvfhpxyxl/t+RUboHBtJBP31BwmECM3uAnxRsGsKzZAtRkNYzRV8SoUG6B0jO4ECLV67NdjGtkgFH6T9+rKDFD0RcjwV4QjXZkBirvICp7qzOpqDBDKSXsHEYjYr79s6CdNQnuWfWpnp4cEdmYYNQaopqKxgwrHsm/t53uVkPO+dZ7r736jiEBRB89TdQG2PHRcfV9bhqTSAlQsXUmtTBbqClCBFG2RSVK4KytAlRFZXMgXLj5SVoBCAvqokWq7G0JlBVq0oSlR39lOKCuQXeLKDv9KnHVlBajrQfXghQ4wdv3u7JFGiH4Li6ssQE3OoK3glzbErrRAdtKHOX2WWc/T2ktBcHCKygIteBThi1+NDEHYpsHnl2h2nUe/GY8EmVNZ3lUWoGSFFsaErmLXaUKAkTN87rejuADBKWpA02IUu07zRYM0w6vQlRWgTIS+g3RyYxeCbaZElCIjDpNTicJ2aalSepm7EoVBGELVwDcrZnwLwSirDLH4r74fIRj8sxSd5/L3Ejq+WVsnldwZsqIwaozYEaDoF7teM4z7SldDV04AzMxCcwKv7wV0m70KhI89C4eKAhQiMMGQpHVwisTOB9AiEDxqmAvFQkcCiUuWDuUEqBXYiKG+yWZ35QQIKdCP+43MUX9/XYZUmPVkp/6lKyRA9JCkDzdW51naeaPkyLJdUUiANDuEodvZRyQGjAk6+F2O3K6QALnxDxhO2vp0WjxGSRcprB0B9q6WAGntkdcUsv+ulgA5aoKg4w2LYFdLIHWyAw7pkKV2tQTCtk+9TsSZulIC4WD5hcTqlF2nmV2I3O1gOrUEyPjOHrLhGgGCMUJRK/Gn+p4FYzQIJPqShr2ukgA5V1Rvn4g915MQjx2yjgNx6noPgjEoJFaI7ObfT3R6BCFQ2ZaHJxg7cCnCVrVbXV2vZ7otfvBF3c9aQEa0obizW9l1nPrJTVnBr+5Kxym8g/MaRsO6KzEZEcOJIlPFhRURSKlxKsuf+qxFZMnC0nsKTd09lb7vN8StpQPY1REgPfej2un+tW6TRYZrLwVwXRUBsmpPpNyeXmfRZwpZqESoqKoqAuTCWKE+B+759TkeAB1qibioLOtCmLbuunhRGfuIndLuXw2OC8lIOxF1YkyVvWmnoDAUlXmdF5KRK2KG2lXF0BUPICcE4yzopK47taMp0DLZxL60U2hGZdF743LqB5CfGbSXQQwU+9FOUQ6XdpuuhACplW84oaSdbbcSAqRKHnod3laD8ug1qT92uaemt6PXZNMmvMW1Bh29jlgmrdh5SEenWcShm5j/7ki/CfZBrbprgB39Zr6iiIKEQr3So9/QnTHr0IJxD+l6p0aelTdnUziA+D61gswqJ3b9JvjW00xVBadd7QDi8vQ5IY61Y9f1Afkc9auz7LoO2kGxL1UOXe0A4ubEEdGhX7HrOAj4W4NaTfkqB/QINk40R35l1+vFVo3+42wvlA0gOH2yIkfRtCsbkFqc54RqLffz6DJV8PByRLKkqxkA+uEjOaX+2NUMINZLJfoP9BW7/kJeMiOxlufw6C8Vv9SbvbcwpSsbQDiWzNpM4U1XNYDQagsErgf06PBhlw0BzrpxeEUDCIfCWfC72RtFA4htMsJ/nDL2RzvbZgreAu4VDSAamez2zRopGtDz+dCUcOrdXEjWo2XObBWsq2BAjzhgUoyj7FP7Ys4gz/xcDy4i68Xh+6NZPU/1IjJCdj30XKDLenoXlBGGI0EO9UScazpNExj13yFa7ooG9NSPoeBYmQdFA3o0hvlMs2QpGNATVAfpVkhDtYCenRf5uFbPruk0SciWOE7M+swkwRSUFq+uTADBpW8h+SDLUzejv7C9gT9XNoKqBCQ/8aSDrZzqOjvCbQIyzd10nYXZiJbnykcqDkBkBsqE1upFdp2l0wVqhNQPd4UBiKbwwPlu6jQ6S8kAktzpXOmqAhADQbMLads6j96uJ11wJ6VWXUkAIhfRdpurnk7X3ZUieuQl8/dDd2kXmCuND7Hr7g4cSid37LpLBVMEP2tAD/1FOfqc0I7Hrr/shtGCvh/G0N8DWxLFEvXnuptcPEGa+lSH7qJXW/2UMevtN6+vhKtqaroAjE0x4DE0C9gvAGOTO+i0ekNM1CX/76G5pm6ndjyS/7M5nQh0oZEV+/X2LSa/960RfpEXO8od8fox6rJD+2oRO78f1kVebAAT7Fxe9nrLRgq2Lth172d9kRebNBiYvyn8XkKPX+ot+OrKvvSYsQAaiwR8l/uf7dNuxcYZF5Yew7wXopyE2eX+7xF5IBP8XBmBLv0/u5iB3MRe9bCXXvdIlh5mutj1Gv3aGa03vVs6DnSYCJK+26voeNinyGj2OpuOoy8A1pnZ9Mr93zNLI2j0ZFso8X8PGcQm81yrn/ArukeglAoxS/nfIxSPosWz6vx6DUlcT5ynzq/Xk+j1c0tbu6T/PfRqT3BD2XWZYBeJsrtair2+95kO7B2hlC7lP7iTXhw6E/KBC7yCr5jyCzSIu0jPolhAU3PsuhtVIfLmv5u7kPMfmAdRSF547Hp8GC7BDWXXY1hIOHPdqLiLxhnWyvfCDHEXm26cXVWjI9M/uIjiaLrA8uJFXHQYpJohDWldmn/wzBpQEIRdpcvxDz4hN03kr8f+aqdFKn1sb+xNe6l39go6yu4PTICBLHyKsV93oYuhcrTXZlB2f9b2IIyRQuQuu3+PDm9ayEb9vf7ShYmmXGWVpPZnef3lopGO6VL7s45+awF/l82p1P4sjJS+EtnKeYRbCEgsmGPShd2l9mdF6wg9USoUu/7iyg7xSp6zcCufF6TgIwNUUn+WFvhdo8MSu/4OmL54+m+dX39JRn/gGUq0+jZk9Geap3IUtrdcQrRF5pLmReS4YtdlRGwQFaxdgFz+TMS09qHYW3+vyxCkEy6LUX+/cU/Sskhzuyz+TIXklNkD5LmJtWAPgFxsRku1S+HP5PWdZVLrXjejvwh2ktB7apyIsmiFpM3+Dh9BFlG6FTXp7Aak72dCeEGW8KTFrq+H1sYPjVb4U/p+PuP+TZTojuZ2RFmENk7a1XZdV3ejtA3pfb1eYRY1hN+KO4qWpcvc39PpxVXSItxl7mfwjDdM+NmmytzPeE2nZKscjcz9PdiVDviaBqTtDyN5J3iS+JWs/Qy7dOGQGo29aT80H44nBKldyn7GBOrbFLXl9sVZRLI2LFGjhpo4K93ii4W41+3obkvD/Y+u/9h1F8HHD07swlky9ffIC7EXqC2ITP08v52IbdU8yNTP84BVCs71G42UqR8f2emm1jt2XaaeKluE+nM9Zu0kyf/WRyHS+m7hg5stMoOx6/GA/fdbvVo9CaEWqu3pJKxUsRT9/I/FMlW5+Tqk06joQBKSTIIk/QTHEFuBuzevXrTFhAJCY0qJXYe/7VhLoGPVeXSYRmzSJDXSRVuQAkOC2OsNCLbogycZ2lJU3SXn77TGpk1g1p/rLnkr9mesKFkI5eZHVgt4dtpdMcRakG5EhK5KIuXm73BV/FrlnWPXX8jsv1dPiCB2/YWhEihXkWu5+TsT4QpLdnkg0KIS60DG80vsQVZ+miAJYRDwLvvU/u17RhSI6rpL+64J986IQixIcYkQkbOI/WgnEzComMjfC7G+dZkc6KjQpGT8ZAh/K+5e/Z0uH3+HF/OHREfIMbt8/J+dZY+C3poMBFkjfM1QRvzKrsdpQ31OygiyiZWP/xvVsGMOEpV1szpNfGi3ZNr8iX7DSPP5VuWGMvJ/H9aPlTg8rdhFWqRHgbzrzoxCLTTIF5x3VSQtHT/MHL+UoO4aRuIs2L5TRrDqsYqzCo6w/yqzPsPrRHfkrz4+cRad9BQwnPD9dFn4+YyflDr9/ga2UAud8F967eoZCbUg7qaSYRVUkYm/U0oFTWTJj3Rp+OFEXqn4rTC9HPxpyevkJtgY5FlLxN8p9Kaw6bvtuoROo1fCIv3rZddrCvnA+Cvbejn40Rs71ChRlha7XtPQyPfTRl1Xlw+055QjvGXXZbgW4IOqKLAM/Cz+nIsm3Rm7Lkc9e6XzNPbrMi18VBsSiIu9aSd3yDq26jxde3Kakyhk7EM7qTQCXHU71136SlI8NvaF6zLwM/cequpnRQhk4KeIdkCUWsajkUzWm7gEdpEWpIbkRemajP3RjsYhQrL1mEVaM4TpEEfV+UVaJI1DsV8JLln3v6n8rTaR6luQcp+OGOYCIuJ5LYKtSQKfugkkAWoEibfCjBoti1a3qr/sFGjfL/mFHNLrTlMuLbDlhZhrphKXxHvegZBrwoHHdu2+YyFXGNcWquCtTqPTVIYhrhkqny7XPqEuZDuoEKi/1+n5pJSlrfv3Oh3ic3jnaowKuRgQ2clVuYxE+1AjJhD9G9nDy7JPgRB6Db8B234NFlHXDCsFLaTZ1MiyT58mLRsQNuSWhF1z/+Co/VEmGLsufxt0WDh2FUvIr9/ZoRz6n6qRR359tG8ifPJUd4H8+uyfv5noqT201PodMbCZQPG9Gx2mVSrt0rvOosOHmCIp1/p7QRet7JQmzshAdln1Pzvx21+cjv3VDmCnv+fU3zftJ20H47mUpl1i/Z6iV/TjTyJTEuszXa2WEt+6o6mZRZ0isd+NvkqtT7U+tTq9pEu61PoQZBbVUE0gYq5FGB3KhNqNy6wPpe+P+oVTJVfS6lOFGx3hW5YirX4qZGcKrGtuF3Qtaj2ZhpLhk1KfAnni0N/6HowjpT4VZqnebDWuBF3kOuHbGxXPk1E/3abnzWuOs0IuxA6oSviFOKjLqN/RpaFv4ldFLNLpU0UMzyXO5u+FXGvk/qHCu/kg6fR7ymNXybfFrsMpGmFpn3UJPc5njwhDuzXUMuoTYiDQAHde8yo6TrUcy9WooS32WtAQ9TAWxnGxV7ieyF/v+pbFXovdCnvXQGsJ9RkkVBGsUaNR6LUgQKXjoMo/JdPv8MCnu/VXL1nc9X0zdKxQP5FnIe4KCRlbnipkk0wfikvexHMRqGT6QOsemlqSYPeWrsNAQFoainqpS6b/2d8FjEb6MfajfbB6Et+/2wz59DsxEari6Na/VxF7IVb4K36ijAOxF4kFBJohiom9aU898UITN/auHR70kwobL3F9T+iThre3pjbxF6Ri8BxQDRK7jsMbSV3UufRLXT59CiXDDbwq9yCfPrE+lDEoOOXv5dPvJZr2fRLRiO3y6XcIbcNqV+BIPv0P6P5CfXjD3/Lpd8jnkef6luUTu17z2cMH9ray6/J3BbZpyIDHrsshiQ1RUp1flwcz26EVp+5Tfzk9FN3vtesvTKUpXwyKkEMfDnAC5jT1PrHr7+xJebPq1Kcoh34vudhwtuSWxF/MVogqfNvZsusy1bhwKY2stRLos7VD84LCtRG7LkOQPPN2LgCTQJ9O+NS3fKtNnUqvNxtHmsFXeafXRJ8fZrJ62mKwjbsfSqWWPXa9DrHpM1B0iF2XDx3DsIbU2xGDobWy05SZL0vqfGp5woD2FIqXOj+7VsJXuwCkvPl0cVEmSiVC/BKAQT4DpBqV5ZA0nyGaMMAbJpguY/5nfylSeOieqw9BxvzaPEbIswaqCIwFnpTPiDZllzEfhb5DAnhFECJvQRB2ouhxqGSvn3TtBFizeuRpCMJOMgzfXNJ2nUevWyJNUGlkgAnCKDRGdbRHXr5LlM+68KOsi5qf2PU62JVMcmZuifJ7mMgHPV5J5UqUT9cNSAsu0dyPCOwk8I0wZfklAoO0Ds0KyujuUxWEnei8UoCWDa0s+SmD2tT5rPpzPR5kNwZlXS12PSaq86Zxsq6sx3ThwyQyM3vJj9/DGTbAkvVERWHMB2h1z6p6khwfpn0iBUgA5vyisJSdwddWgWXJ8TsZWXIKv2yvJcZP1PgXoop7Gr2lBGFQFlKTiBCM+mIWsGj8dInxmWzSQvrciUL4dei3eRC1qblL/HUoj1wnAovYxV+Qj6K26fsVf0F3Q2Vo8YZ2OfGJmp18auHh6nLiD8qDRqi9nzp/177S5dxriZcTHw6W7ECh47yfxgVhg7jcTse/deAy448UBYE6CvHKjE9XCJWTz6qp4sKwQT83XWiw+2O/MAyWlUlh7ajmBpnxPzv1G9xJ7nXp8xuHZxHgd4nxB7qgNLu81TooMT7ZHPAutKRxbOlzWyXR14NpJcbn66Jwkex0nvXS22T5vuXqPHdjJDf+dwixAXRzaj1Yegx8ILbf6vVsPR58R6mMya1uPQby02lbb2fr8YfDyQt+UCQebz0eiAlnRS27HlOCC2r+1cq+9RhZdnZAiWrLiR8ZKCR03l4AYevwt/otYMaoT2nrLcEcKDhUnO5y4uMWGgTk+W9AWlr8QYSMOg3EHWPXZ2BlNLdr6jo6zXxGgVv1D0uL/9k/BDCyGrggHP3+FsFv/f0m/FGX0O/DFDiJNP38ib5TbksNZuUZZccfVPdwA7PwvNT41AwR/GT+j/n6/UDocMDn+Z5lxkd24wkfUl9lf7QvxA72LxSqXVr88QCBYXYbFpPLjE//NhMz+ckVe9c++WtkV2MemkO+3W/lr8T4UEV+4waCuFiXVkqfI2T9xL61E0KNROOtRpYaH75b9uU/NLCxP7r8bYAfGntPNlVS44N+CX6fWTE3efFpB4sG44mEdpcXH9Ii9mBRJItdf8llImkGy0g9okefAZk04lUZjOT4AwB2kkPJZyg5/uA/UPPsynZJjg8v/hsN25B9dcnxR0qXYVYspCs5fgrq6YQkrlwzg/z4A91ahN8IDcSu1xOhakq564G/eo0oAqxUa5ddr78XGPrMk1i25PhhYTzV8112XV7pnDt8D7Hr8iJS1yGOK7sus4YT32m7XNPlHQ2CQYk29qbLm75nqHAyN8iOP5hcqHuLVFW9nabLZLGJuJGCuIf0mhjkN/Q+6Jyn1PT67FSRMmhiv16XHjuLfK+/n9ppvUdyb4/7Ii4CGxHODm9/EJUE+QMxaNi0q5hbfnzk41bEPCsUJT8+sxs7rl9x+nX58UlNoOBOWqDsr3Z0f4D/mXPlx6dkGz09+ofyXC/6oqGc6goINsuuxwQ5v+dDSPk+vK7TLfPbqhiS9PgobxLvBSTFrL/pCuWV5qvq+kteFuqWk82U1PiDesJDa1VPRFxu/FGSWT3Rmdj1lyc7Rqo4Y9dfiOaJn1dEQ1b8gT8fvEh0PXb9pWAg1U0J/ciKD4MGYgVz1homKz7J9avO2suuuzPyc0lZxa6/oIp0CdREOPWXfplDFXw9h6m/C3mASVbkbu3lxKenn0YVOqpyq2IwaOMhG0FGInZd3iCPDvFDXrEYjH0O+pUj/MFdQvxB7gdWQILWsesyLNC0pParHtHlxB/Q6S0CbXVD+nx6EVJVuEs6/JGJfKWsqez6TF1I+hH+viYxGBEWnhHRgNibdoSoP+hdkTz58GGwP6GHqWVQCPbhBzRLvvnub1SLwlo0iHZ6kQtkSIo/YO0D5T/P9WNrp+MDmoY0VEiKD51nGLrYQ2AXhTUyK/Ro7npOojCg3C/MB2XWZ54H3ZWn3ziuhPijBf2FdLl5SM/RdkUD+7S/X+k9uZ3v0BM+1i4tfmkLI56837LrdxGBf1NWzQ3iMRSdKViblVKUEx+dqzdCeJUlkhOfRgEoWdkJeEuCMW72e6ywa9/Micz4sJZTnPTcTJG0+KDMlna9Kp2VFh/hcXqEKbatS+j1jKYmge/mJXQc7Mbmat2f6DhJGVKwlXeQFp/gzzcUaNPP5k1afCSYyVGwD7lfhsz4TJMz9NHDIJDk+PTApn+qCtjlxieLQAwd1dvjyXQ9ZIm/VgpQXYL8QXsfgkVvBN26BPk0xQ0U2naxLUmQDy8HzMng0DqPflPqRhbozLrT6zcYngadWU0gEuQPqkGAxxVLlB9/RGZ90xyTnJf8+PT7sX8nxFT2VzspvjfLeOxN+yDs/n0a+4JTKfIHvb4whdbIlCF/pPNpUf711p9P7WlAgUij7Es7HW7vG2q2ewV9Juq50rJSl9DnkBxuYs034itLfnhFfgn6JZIhSz6cUCSUZlScuyT5I0VI33bldqjLkD+oggo5X7tqYl2SfBi8id3CE3Q/F0nyQQKUCSHM+8au60Az5CoSapYgfwASYWvY9cc6PZie3qsJ2aXHp+4SvWtKo+OZqIxw2rfkDqrtY9fjCZEX5NhP/b0uT+Ddh+RCs98lxh+hdOrZkmUkicfARxSFEL69/grJWJcWsYsiTZAVn4jXIPHcK04jK37EUVAhmNWCKC0+VPnUkXzT1q/Or8vpYkIGJ3tjafEHGzeK3547lARkhNxo2B+ZraTFp4kJYRGW6zwJ8RjcLZRTPNUjIS9++JVRRimy0i4vPms0qcH9K+oLefFBPnAbMyDqdq67g9jsImi+y761f6svRBoVzJcYn0+G9EyQbs3RcuMjTjNSZvjagyE9PuKipMrPL6yuXW78MSI4u2FTzssRlUVCE2LXCo3IjT8CCaK19tT59RqKvY2EUoaLoGyEgx6C58RuJcUf6LmO7O5m2XU6vILPGlG/7ZLiwwQ0Q1JVqEJSfLTg6MiCzr7sukvsP1NDu/BBXnziAygb0aScWxWU0YJHXG8HY9dPdHqkIvj31GoiNz5anvBGw6J298DS4w94szb7zMq6So/PgD/JjkXOp0uPP8L53UIjErN+wz32PeRdrdSy49MzArcL1AI3KidB/ndokaX9zfuFCswogh5MWTBKlX9iM6gH2ejTwRy7flNisMEpNbMKzthFM9FQNOKp9Ju+R6QkQ/7d5clPBz6EFuOc5g3rOrvLH3hn11X0/cAvQU98rcaCs0kOAkL8YpiSKv+zj1A3tOLGkSp/EJejz55a79iv13AFsU6TmY+9aw+ZDvxgcU1QhrgQDFFsna8L4rLvTlIp3/8Yj6TKJ/J7UtVZ4WWp8kfYU8JjkgidVPmRt6FY6btW7EIzqC0JVX3PO+cXlyEHAZfUOfXlCcpoWCTaNuuv9Tnt7hSN1bMTktGMQutyi1Z7lyV/QF7+nfy9+Uwp8ikneFA3qkCrDPm0AUGwnAbE2HUWorIRUsqY9ZUvCDHbx5Z5GfKzLnxjiwDtjF13aadYpRIZu+7ONAX8brmxFPmfHc3672yvCXtZ8gfqYD1Zll12fV4pTpolmNdlySdQQ86HUtK6VZ2mxq+xWX3rlnSaAUTVfVWNy4//2cO2QwfWjQlJkQ98IrX/AzXHrtdsXyiMqYZZKfIBXU/yJcVGIkU+1BLRP2yFb6TIp51m5Z32Vue5LlOyPpO5anU/U3uyfeHyin1pn+SxSCuXfWs/FMKhj1Dnvy6TDy+qupxeGLZSXdWDTe6TEIlRUktFcGEAGfI/mPd7Wf1+lfWXIR/4RzUyhRYXgMqQn04FupR2dZbJkB9RWRhXZ3EzyZAPriKXzaYmz1QcBjXPDJH0qkvrM8mC51An+dMJ3Y54b8+6fO9KPJb4Nan3nEs0RukszDoj/MZdinx2V+B3mpgylERjqYVlo/M+d96RJX+ED5Gqk6L0kyWfko8Tcm64Ru496TlpMJbOagSWIn/Q4jfpr+/ZVUuRP6hgOVGvfepudRu01MOrnfMLyL6FCZEaWujy9wIyxPW+qaoXJYT0+MQPZxoOhpwdMuR/h05kCEvDtC6i36BHZt1KtEuSD30rtRkho/Vs+v0tAjthg+y2Zcin8XaHhyZSfV2G/AHBJw3YiPx6dV3/phSkQJ6qhJAkvxqQKBAcLr7y5A96ad/UdPzK/mrnb9KKWKdq2hfyUO1Wg0uST+U4PID9VNOfJPn0jNEV9vm+yz61TwKNvBMfr+gMKp0TeYCsBvLkI7tGTyRiQHWqo50wGRvJpInkyQ+sOHBO/rWtSZVPcysNvpSB3QiSbPkDQuu7wNRPdDyJ+O8ltu4zFKARm6Y2rVWTnYT53xoC5GghK4pd33uRzdNAFbuOE56FyeV+l6Izqg8AQ6O6cWXLHxkBYM9K0suWz5+eaGm0a9drcs/RW67BKTaDGecX5sJAF9nyaSOqBo9ej0hgBp8MA7b0Zrps+eCx9J0/FXuVLZ+C44Oi86yUj3T5RA8/gE8LT2CndPmfHT1BmNNr8hCSZXPMx9UlO5Ixf8AiS4nVCxvdPaTX1CtAQTFP2fWa1zhKqiF2vaavIXuo3JS4jHaDWRyHeWniMnbT8OKRKI79Ok2GG5dW1YbKmv/ZKaxCubQetoiMmoGoARUbj6z5rB5RbZ9VwyprPhVS5HaoI8tgFJGl/6Ty/rl/ERlJDJiY7j5YynyKdlCkp/En5q4ZUtWxbqO9lPmEYglNM4TzLoVkB4Uw2heqlFHK/O+jiCb1nsXyLGc+HwuBj5U6nXph4jLWhkhKND6zIW0+Aksk0n9FZzikzR+RgktT91t/r8dkjOHDfm9H7pA2/zsEqSxTPlPPkDY/Dd0IEXwfyM+f6DjKFNGMJfg5pM3/7HSakx8Dfw1p84G/yOURza/z6DgydMjuJQY35MwflDc9yWi0nEdQBqpY36L8TaG5rqDsUMX/RmozZp2mNw8yCQSL6/kJyw59YN/iRf3bdU5klgIa+n/2v1/pN0Uxb2SVRuz6DfPMSMF03Zd+p8+WGkDG2ZA8H5o71mJiq0/s+l0B1BfanXtpARqbDYSm23vt5TqMIz82gazQsb/akV162ALmEheewda5VsiST9XQDyn0E65CTrbot4YU+h+SZz+K0tuO1xeeIYDSCBIGYQ4Z9CdsVjjyZpUbMuhP6CjpmqNq6j7yi87YRsI6RYkd5ovMJr0wK+1Z1Izk1Tb</v>
       </c>
     </row>
-    <row r="148" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D148" t="str">
         <v>2025-11-02T00:00:00Z</v>
       </c>
@@ -25893,7 +26135,7 @@
         <v>H4sIAOW5B2kC/z1RW4rEMAy7S75LsC0/52rL3n3lDmwhUCxZUpSfo+cz1+f/a+t+jmHHyAqTiEofL447XzYmtTwUJop6jla9dBORsQj1HDwHKjvWzgnylytDOmJe+oh3QxwaZpzT63xUrolLiPSCI7TN8i8Aa6/s4onW51BvlZJsAWrcynQDqTQ39AIUcYTuErCIxvlE97qUUkgYwAjAeTnvuhZloVRq9wV6tZB2y2uYlZqVK9XOlhBxO0aSkSg4XyRqEVwaGCTGVSxYqxm1bJzVJtLDW/nHSsTobpq3UCwPwyex5kp6v5fXqwzHCnufKIioYGiTuNISNqJjKfb7B8P8vLvUAQAA</v>
       </c>
     </row>
-    <row r="149" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D149" t="str">
         <v>2025-11-03T00:00:00Z</v>
       </c>
@@ -25904,7 +26146,7 @@
         <v>H4sIAOW5B2kC/z1QN24AMQz7i+eDoUaV+1qQv4e6Id5MSmL5OXreuTH/r637OeYL62BG1RDuY/GczoUFIRKKSkQGYa06b9/x3W93ZIrXc9x75z/A+IE2ZnHMd6c4n9ROKHqek/25sQ8flwi0P6fEzqtyvaInugwSpVhiPoLw9JCluLXRkLSQ0csw5mGqGdBNQIZe1WHXJFBmVHbwmLr27ijITHYPSr8YWnutDbeQ3pXJWmSPtYKEzKUuh4tbEF3CZgm/yditYwXH9ordQMcNZ7tpLRCjY2OC88YI0yOD0WkaxfR0ztbN6mapl7Qx59cL3eUWEEpjPloBSe2o3z8Bg6yb1wEAAA==</v>
       </c>
     </row>
-    <row r="150" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D150" t="str">
         <v>2025-11-04T00:00:00Z</v>
       </c>
@@ -25915,7 +26157,7 @@
         <v>H4sIAOW5B2kC/0VRuZEkMQzLpe2pLv4gJrWtzf0gnbHyRBGvfh5/vnzt76TZfJ7A8913u2YDIC3S4/PQzhjZPrZDbo3V53HUmXcIXwI5ZyCWLB52397MJWrXqHH3XWdnVdcycdkHe9YRaz4Mw3QUPg9srmyIxujWnRmSRciO22tL8SfaaN4uP9ZzhSeZB9Ngu5hcLxcypX0T0MiWtMcqsfvrDupSpnSVe7Jt/YcAGDazIlAHA+7FIE0dyapPww5mr4y/m1RNUTFuHFmOumz5elEmw+Fqs1svnOMg1CK2O5rjsBNzKsQWeENFqMAxlVDeJ6dqfb7QT02UJ5k5Gf37D93nLwDXAQAA</v>
       </c>
     </row>
-    <row r="151" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D151" t="str">
         <v>2025-11-06T00:00:00Z</v>
       </c>
@@ -25926,7 +26168,7 @@
         <v>H4sIAOW5B2kC/0WRS24AMQhD75L1aMTXhrla1bsXsmk2kXAwz+Tn6Pnqjf4/9OeYbVUoXlVIKCl8TuWWFUFliLMaWs9R9H2uDqpEVTM8nuN5zV2TJjCW1lTHbKtt5Yigezl7ZqLkfP3aWAMy6oye55RrkiEiRhfJuYal+8JIV2tBEylsDIxErE+BrtY5rAMz/mqG86m8xun1dh0ut1Vovi0gUtvcN3jECs7bUgqOkIMKvZG5U0ZpT4h0AsltsVgvtVkeR+nyQbDqUVp2vr8Gd0VWGUxkzDCLOJ/xrWEd3ooyp+aGmazni83f8wcG7l74+wfPZvbKuAEAAA==</v>
       </c>
     </row>
-    <row r="152" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D152" t="str">
         <v>2025-11-07T00:00:00Z</v>
       </c>
@@ -25937,7 +26179,7 @@
         <v>H4sIAOW5B2kC/0WQSRIdMQxC7+J1V5cGhKR/tVTuHtybeOdnDEh/jp9fv/v/EIXnRH+YXpEzuYNlP2ftwzMTG6wpkPscH7nM66ZTSHag/DkZH7aadG9rH1sfcezlGZJnWzHCls+p6cu79dHNWeIjH/bnw1S9bi8WGoptz08vOWwNXbN2W7JuTeZcm4RFw6PU01oJq+Sgcg3GD/vyYqyqjOpiplxbcG5++tQ9lmTmxZrl/NzemEQgZL/A3AfH+cmX39C1GekIrTOvUdLxBrU7ONxHI8S0otOsZRYJRkdVaogbpZBkveg1I1XTceMtcBcFvEqC5HANkn//AUPInEvNAQAA</v>
       </c>
     </row>
-    <row r="153" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D153" t="str">
         <v>2025-11-08T00:00:00Z</v>
       </c>
@@ -25948,7 +26190,7 @@
         <v>H4sIAOW5B2kC/zVRS64EQQi6S607Fb+oc7XJu/vDTqaWCAjW9+j51K2Y3+tWf47FwkhUZ6WpCaaf0/Wy03MMo+GYjOdo9eLt1GtkTXRqPccDi08JXyqAxoB4+ovDutpTptybPpnk9w1xd3qqpFjSh6LF3WmjOeAeBePUxuyLUGm1hBojkD9OHLertMASLZltzCnxGg1di4IwKakdKPJ85pIgVlbV4prJAWCraJGGo0o4EeygsIrOmA7TTbaVtWUWn2RVE/pGwdnNfJ1ULqTIJG5e05RYB5er3dgC2NsFXbkdLjyU4YpZcpOLyfZTMeX2iAvwD0wnVXsk//4Bjw0UtNABAAA=</v>
       </c>
     </row>
-    <row r="154" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D154" t="str">
         <v>2025-11-09T00:00:00Z</v>
       </c>
@@ -25959,7 +26201,7 @@
         <v>H4sIAOW5B2kC/zVRyY3EMAzrxe/AkESd09pge18qwORJMuLh79HzqVs+v69b8Rzrhb0rZKQ0oRb6nHnV0Sauo/BwRz5HKxZPndBAQWPSKIfZ4o3KblKd7k49HK++JBtt1mMh8Zww3ukL86pSKNmBPycHi0car6gXwmPxsjfPQDQz3FJCZBhTXj1qQqqlR1q8mFP0NWixkulhsHDZAuxyPnNFlVQxEViCDtt8iWQpbA125I9LeLxE9wDpLIDy2C2ql6jJHDU6es4YJ8WeUrkeJkXbKbihd2ylu+oVqcoRygEJBk4rLmh6Jxye4h7cYh+IVZoBQq9GlNBVndn07x9yIMJF0gEAAA==</v>
       </c>
     </row>
-    <row r="155" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D155" t="str">
         <v>2025-12-02T00:00:00Z</v>
       </c>
@@ -25970,7 +26212,7 @@
         <v>H4sIAOW5B2kC/z2RS44EMQhD75J1KQLMt682mruPqZYmiyxs8gDn5+j5zPX5P23dzzF7ZcmyyVYTs4nndKyMyUzhbYHseo5WvrpIxgDdY+rPgczKqtZaPVC4KOGI/mI83LPFtOGkh7Je5WpNu0SZiLTiOVn4GgPztBkdH7HnlLykBFylm+UdQpKqFF/ohYUMVZ+orNdRP5+UulAtUZQlhigOx+VCcEUqhT1Eae2TXhjKmYdx5FgZuoYzJmRdZubLgtj4GpFr+A3uIsm8GGFhc7VlsUuNMdVMA7eNDcvY3ww3Q6Hl6Vq6tPR+1/eL4F8ELyumzz77CdwmrlR5pLHUfPD7Bwvw6ozXAQAA</v>
       </c>
     </row>
-    <row r="156" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D156" t="str">
         <v>2025-12-03T00:00:00Z</v>
       </c>
@@ -25981,7 +26223,7 @@
         <v>H4sIAOW5B2kC/z2QS44EMQhD75J1KQLz76u15u5jatFZGnDs9z16PnN9fq/R/RxgZWiUtZZCKrOe07GypJghHZXVxm2tPJ++g1bkeEp12DzHrF6bLDGXsJZSC+rRr4+LiGe5ZNr4c7Ll3bfNoYMUCfDbEqZUufRzV0mtRsTq/epeiI4wjbTsZCCp4UQvKjQx0QNGjp00s6pV3nn/rXYO98a09sbispmGocVbt92atcsNNnN4jbpu7VbnAH7NiSMjg7DWihA50L6CMREQI5YfYi9i/PbLtJSglghm+LkPIXKl6KI9RiIeRA7TS+8WdncLYHuwKeO6XxB7TC8WQP/+AUWy1AbTAQAA</v>
       </c>
     </row>
-    <row r="157" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D157" t="str">
         <v>2025-12-05T00:00:00Z</v>
       </c>
@@ -25992,7 +26234,7 @@
         <v>H4sIAOW5B2kC/0VQuXEEMQzrZeMdDcGf15rnejcoB1Yk4RPInwfPZ478HxPJ91F/Pn1cvURbKgMof5+uC1tYerWLdYe9DwqLGywzVLPhIfo+hr7pqAKxoYMs8bCrr5nx9kntJMzMlSeYPVkgmUO4YtVpVE8HdG+Ee1Y9zeiKW2aEHSF69THRCoCpkMQSxakgJzqjWD0nJ5gEjSSBI/Q4OsGPYx21RekQTmLNIp5dlstkXUuJRwHusBUsc3/BaRUkGImQMd2d3jQ7rONaqnQ0tMmM/RUYYpI1MK0pMhyVaRpHQzBQ426sLHYaE1bI5L60EXxHSXx/AU+Ho/7SAQAA</v>
       </c>
     </row>
-    <row r="158" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D158" t="str">
         <v>2025-12-06T00:00:00Z</v>
       </c>
@@ -26003,7 +26245,7 @@
         <v>H4sIAOW5B2kC/0WQS3IEMQhD7+J1lwvxZ66WmrtHdBbxUuAnoZ+D8+nr8//KnqO9qswI1Nsl0c+Zd1UcNpykVAzqOWhdHcJX7moWGK5byOraZLaHaqXkcxJ5PnMdYp1lguhwytEra9bktHiqjJBS8lLixYcGfSeDYcb/0jQNwSyteNOI24IYuhxt5TIaPAmqcT6QS0Yhq0C0Ozgp1f2SEWBaSKRVLKuMWYFLcnZEdDcavpN18SrhrxYr9FTxOvVlmZtdxaiaToRhKx2hv3bqtWFqpdrp24glYTDJ2+wWVdXy+gs745UyFwNWztDE4PsLDqtf17YBAAA=</v>
       </c>
     </row>
-    <row r="159" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D159" t="str">
         <v>2025-12-08T00:00:00Z</v>
       </c>
@@ -26014,7 +26256,7 @@
         <v>H4sIAOW5B2kC/zVQSY4gMQz6S86lyAve6mut/vvgGnVyCtgE+Dl63rqF+Tvd6s8x/2CBW3VZiUzqczoXzq4GVBsikvYcrfrGm2/HmHaMSjzHEUsMTNRdzGOyCYd9sHsLx9Nbs4lHcLyvdzq8UMUtwjn/YaqLGaIyAarXuuybVhGdQo0sjlP2vHlbIiW4tJl66FLw6YwW0EPWRtaOauK8c5nRFN7gZRMkMnU3ykNCETaGKSxRsRsdJrAuH7jqEi29xEQsNOyDn32FrpTKTYHSwWQKY/ITY5dkjLGZrMo0qbpiycbOa3GbDYT6lHdBY6OY0gBwlZajIL2Z+vcfsLdaEtABAAA=</v>
       </c>
     </row>
-    <row r="160" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D160" t="str">
         <v>2025-12-09T00:00:00Z</v>
       </c>
